--- a/balance/Spiria_Game_Balance_v1.0.xlsx
+++ b/balance/Spiria_Game_Balance_v1.0.xlsx
@@ -2540,7 +2540,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H100"/>
+  <dimension ref="A1:H101"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -2974,7 +2974,7 @@
         </is>
       </c>
       <c r="C12" s="63" t="n">
-        <v>0.06</v>
+        <v>0.08</v>
       </c>
       <c r="D12" s="20" t="inlineStr">
         <is>
@@ -3003,44 +3003,42 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="20" t="inlineStr">
-        <is>
-          <t>Map1</t>
-        </is>
-      </c>
-      <c r="B13" s="20" t="inlineStr">
-        <is>
-          <t>region_id</t>
-        </is>
-      </c>
-      <c r="C13" s="63" t="inlineStr">
-        <is>
-          <t>starlight_forest</t>
-        </is>
-      </c>
-      <c r="D13" s="20" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E13" s="20" t="inlineStr">
-        <is>
-          <t>현재 적용 지역 ID</t>
-        </is>
-      </c>
-      <c r="F13" s="20" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G13" s="20" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H13" s="20" t="inlineStr">
-        <is>
-          <t>src/data/regions.ts</t>
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>공통</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>mana_single_drop_chance_per_expedition</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>ratio</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>탐험 1회당 마나 단일 드랍 확률</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>마나 획득 빈도 증가</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>마나 획득 빈도 감소</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>src/data/drops.ts</t>
         </is>
       </c>
     </row>
@@ -3052,12 +3050,12 @@
       </c>
       <c r="B14" s="20" t="inlineStr">
         <is>
-          <t>region_name</t>
+          <t>region_id</t>
         </is>
       </c>
       <c r="C14" s="63" t="inlineStr">
         <is>
-          <t>별빛 숲속</t>
+          <t>starlight_forest</t>
         </is>
       </c>
       <c r="D14" s="20" t="inlineStr">
@@ -3067,7 +3065,7 @@
       </c>
       <c r="E14" s="20" t="inlineStr">
         <is>
-          <t>현재 적용 지역명</t>
+          <t>현재 적용 지역 ID</t>
         </is>
       </c>
       <c r="F14" s="20" t="inlineStr">
@@ -3094,30 +3092,32 @@
       </c>
       <c r="B15" s="20" t="inlineStr">
         <is>
-          <t>unlock_level</t>
-        </is>
-      </c>
-      <c r="C15" s="63" t="n">
-        <v>1</v>
+          <t>region_name</t>
+        </is>
+      </c>
+      <c r="C15" s="63" t="inlineStr">
+        <is>
+          <t>별빛 숲속</t>
+        </is>
       </c>
       <c r="D15" s="20" t="inlineStr">
         <is>
-          <t>level</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E15" s="20" t="inlineStr">
         <is>
-          <t>입장 레벨</t>
+          <t>현재 적용 지역명</t>
         </is>
       </c>
       <c r="F15" s="20" t="inlineStr">
         <is>
-          <t>해금 지연</t>
+          <t>-</t>
         </is>
       </c>
       <c r="G15" s="20" t="inlineStr">
         <is>
-          <t>해금 빨라짐</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H15" s="20" t="inlineStr">
@@ -3134,7 +3134,7 @@
       </c>
       <c r="B16" s="20" t="inlineStr">
         <is>
-          <t>recommended_level</t>
+          <t>unlock_level</t>
         </is>
       </c>
       <c r="C16" s="63" t="n">
@@ -3147,17 +3147,17 @@
       </c>
       <c r="E16" s="20" t="inlineStr">
         <is>
-          <t>권장 레벨</t>
+          <t>입장 레벨</t>
         </is>
       </c>
       <c r="F16" s="20" t="inlineStr">
         <is>
-          <t>권장치 상승</t>
+          <t>해금 지연</t>
         </is>
       </c>
       <c r="G16" s="20" t="inlineStr">
         <is>
-          <t>권장치 하락</t>
+          <t>해금 빨라짐</t>
         </is>
       </c>
       <c r="H16" s="20" t="inlineStr">
@@ -3174,30 +3174,30 @@
       </c>
       <c r="B17" s="20" t="inlineStr">
         <is>
-          <t>weight_material</t>
+          <t>recommended_level</t>
         </is>
       </c>
       <c r="C17" s="63" t="n">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="D17" s="20" t="inlineStr">
         <is>
-          <t>weight</t>
+          <t>level</t>
         </is>
       </c>
       <c r="E17" s="20" t="inlineStr">
         <is>
-          <t>탐색률 재료 기여</t>
+          <t>권장 레벨</t>
         </is>
       </c>
       <c r="F17" s="20" t="inlineStr">
         <is>
-          <t>탐색률 해당 항목 비중↑</t>
+          <t>권장치 상승</t>
         </is>
       </c>
       <c r="G17" s="20" t="inlineStr">
         <is>
-          <t>비중↓</t>
+          <t>권장치 하락</t>
         </is>
       </c>
       <c r="H17" s="20" t="inlineStr">
@@ -3214,7 +3214,7 @@
       </c>
       <c r="B18" s="20" t="inlineStr">
         <is>
-          <t>weight_spirit</t>
+          <t>weight_material</t>
         </is>
       </c>
       <c r="C18" s="63" t="n">
@@ -3227,7 +3227,7 @@
       </c>
       <c r="E18" s="20" t="inlineStr">
         <is>
-          <t>탐색률 정령 기여</t>
+          <t>탐색률 재료 기여</t>
         </is>
       </c>
       <c r="F18" s="20" t="inlineStr">
@@ -3254,7 +3254,7 @@
       </c>
       <c r="B19" s="20" t="inlineStr">
         <is>
-          <t>weight_regional</t>
+          <t>weight_spirit</t>
         </is>
       </c>
       <c r="C19" s="63" t="n">
@@ -3267,7 +3267,7 @@
       </c>
       <c r="E19" s="20" t="inlineStr">
         <is>
-          <t>탐색률 지역 기여</t>
+          <t>탐색률 정령 기여</t>
         </is>
       </c>
       <c r="F19" s="20" t="inlineStr">
@@ -3294,11 +3294,11 @@
       </c>
       <c r="B20" s="20" t="inlineStr">
         <is>
-          <t>weight_treasure</t>
+          <t>weight_regional</t>
         </is>
       </c>
       <c r="C20" s="63" t="n">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="D20" s="20" t="inlineStr">
         <is>
@@ -3307,7 +3307,7 @@
       </c>
       <c r="E20" s="20" t="inlineStr">
         <is>
-          <t>탐색률 보물 기여</t>
+          <t>탐색률 지역 기여</t>
         </is>
       </c>
       <c r="F20" s="20" t="inlineStr">
@@ -3334,30 +3334,30 @@
       </c>
       <c r="B21" s="20" t="inlineStr">
         <is>
-          <t>total_material_discovery</t>
+          <t>weight_treasure</t>
         </is>
       </c>
       <c r="C21" s="63" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="D21" s="20" t="inlineStr">
         <is>
-          <t>count</t>
+          <t>weight</t>
         </is>
       </c>
       <c r="E21" s="20" t="inlineStr">
         <is>
-          <t>재료 발견 총량</t>
+          <t>탐색률 보물 기여</t>
         </is>
       </c>
       <c r="F21" s="20" t="inlineStr">
         <is>
-          <t>완료 난이도↑</t>
+          <t>탐색률 해당 항목 비중↑</t>
         </is>
       </c>
       <c r="G21" s="20" t="inlineStr">
         <is>
-          <t>완료 난이도↓</t>
+          <t>비중↓</t>
         </is>
       </c>
       <c r="H21" s="20" t="inlineStr">
@@ -3374,11 +3374,11 @@
       </c>
       <c r="B22" s="20" t="inlineStr">
         <is>
-          <t>total_spirit_discovery</t>
+          <t>total_material_discovery</t>
         </is>
       </c>
       <c r="C22" s="63" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="D22" s="20" t="inlineStr">
         <is>
@@ -3387,7 +3387,7 @@
       </c>
       <c r="E22" s="20" t="inlineStr">
         <is>
-          <t>정령 발견 총량</t>
+          <t>재료 발견 총량</t>
         </is>
       </c>
       <c r="F22" s="20" t="inlineStr">
@@ -3414,11 +3414,11 @@
       </c>
       <c r="B23" s="20" t="inlineStr">
         <is>
-          <t>total_regional_discovery</t>
+          <t>total_spirit_discovery</t>
         </is>
       </c>
       <c r="C23" s="63" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D23" s="20" t="inlineStr">
         <is>
@@ -3427,7 +3427,7 @@
       </c>
       <c r="E23" s="20" t="inlineStr">
         <is>
-          <t>지역 발견 총량</t>
+          <t>정령 발견 총량</t>
         </is>
       </c>
       <c r="F23" s="20" t="inlineStr">
@@ -3454,75 +3454,73 @@
       </c>
       <c r="B24" s="20" t="inlineStr">
         <is>
+          <t>total_regional_discovery</t>
+        </is>
+      </c>
+      <c r="C24" s="63" t="n">
+        <v>4</v>
+      </c>
+      <c r="D24" s="20" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="E24" s="20" t="inlineStr">
+        <is>
+          <t>지역 발견 총량</t>
+        </is>
+      </c>
+      <c r="F24" s="20" t="inlineStr">
+        <is>
+          <t>완료 난이도↑</t>
+        </is>
+      </c>
+      <c r="G24" s="20" t="inlineStr">
+        <is>
+          <t>완료 난이도↓</t>
+        </is>
+      </c>
+      <c r="H24" s="20" t="inlineStr">
+        <is>
+          <t>src/data/regions.ts</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="20" t="inlineStr">
+        <is>
+          <t>Map1</t>
+        </is>
+      </c>
+      <c r="B25" s="20" t="inlineStr">
+        <is>
           <t>total_treasure_discovery</t>
         </is>
       </c>
-      <c r="C24" s="63" t="n">
-        <v>1</v>
-      </c>
-      <c r="D24" s="20" t="inlineStr">
+      <c r="C25" s="63" t="n">
+        <v>1</v>
+      </c>
+      <c r="D25" s="20" t="inlineStr">
         <is>
           <t>count</t>
         </is>
       </c>
-      <c r="E24" s="20" t="inlineStr">
+      <c r="E25" s="20" t="inlineStr">
         <is>
           <t>보물 발견 총량</t>
         </is>
       </c>
-      <c r="F24" s="20" t="inlineStr">
+      <c r="F25" s="20" t="inlineStr">
         <is>
           <t>완료 난이도↑</t>
         </is>
       </c>
-      <c r="G24" s="20" t="inlineStr">
+      <c r="G25" s="20" t="inlineStr">
         <is>
           <t>완료 난이도↓</t>
         </is>
       </c>
-      <c r="H24" s="20" t="inlineStr">
-        <is>
-          <t>src/data/regions.ts</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>Map2</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>region_id</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>wind_canyon</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>현재 적용 지역 ID</t>
-        </is>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H25" t="inlineStr">
+      <c r="H25" s="20" t="inlineStr">
         <is>
           <t>src/data/regions.ts</t>
         </is>
@@ -3536,12 +3534,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>region_name</t>
+          <t>region_id</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>바람의 협곡</t>
+          <t>wind_canyon</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3551,7 +3549,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>현재 적용 지역명</t>
+          <t>현재 적용 지역 ID</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -3578,30 +3576,32 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>unlock_level</t>
-        </is>
-      </c>
-      <c r="C27" t="n">
-        <v>10</v>
+          <t>region_name</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>바람의 협곡</t>
+        </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>level</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>입장 레벨</t>
+          <t>현재 적용 지역명</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>해금 지연</t>
+          <t>-</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>해금 빨라짐</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -3618,7 +3618,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>recommended_level</t>
+          <t>unlock_level</t>
         </is>
       </c>
       <c r="C28" t="n">
@@ -3631,17 +3631,17 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>권장 레벨</t>
+          <t>입장 레벨</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>권장치 상승</t>
+          <t>해금 지연</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>권장치 하락</t>
+          <t>해금 빨라짐</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -3658,30 +3658,30 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>mana_cost</t>
+          <t>recommended_level</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>mana</t>
+          <t>level</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>탐사 1회 입장 소모 마나</t>
+          <t>권장 레벨</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>비용 증가</t>
+          <t>권장치 상승</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>비용 감소</t>
+          <t>권장치 하락</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -3698,30 +3698,30 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>explore_steps</t>
+          <t>mana_cost</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>count</t>
+          <t>mana</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>탐색 행동 횟수</t>
+          <t>탐사 1회 입장 소모 마나</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>탐험 길어짐</t>
+          <t>비용 증가</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>탐험 짧아짐</t>
+          <t>비용 감소</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -3738,32 +3738,30 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>trace_item_id</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>wind_trace</t>
-        </is>
+          <t>explore_steps</t>
+        </is>
+      </c>
+      <c r="C31" t="n">
+        <v>10</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>count</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>지역 흔적 아이템 ID</t>
+          <t>탐색 행동 횟수</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>탐험 길어짐</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>탐험 짧아짐</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -3780,12 +3778,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>trace_name</t>
+          <t>trace_item_id</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>바람의 메아리</t>
+          <t>wind_trace</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -3795,7 +3793,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>지역 흔적 아이템명</t>
+          <t>지역 흔적 아이템 ID</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -3822,30 +3820,32 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>hidden_stage_required_amount</t>
-        </is>
-      </c>
-      <c r="C33" t="n">
-        <v>20</v>
+          <t>trace_name</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>바람의 메아리</t>
+        </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>count</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Hidden Stage 입장 흔적 수</t>
+          <t>지역 흔적 아이템명</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>입장 난이도↑</t>
+          <t>-</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>입장 난이도↓</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -3862,32 +3862,30 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>next_region_id</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>frozen_lake</t>
-        </is>
+          <t>hidden_stage_required_amount</t>
+        </is>
+      </c>
+      <c r="C34" t="n">
+        <v>20</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>count</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>다음 지역 ID</t>
+          <t>Hidden Stage 입장 흔적 수</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>입장 난이도↑</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>입장 난이도↓</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -3904,30 +3902,32 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>next_region_unlock_level</t>
-        </is>
-      </c>
-      <c r="C35" t="n">
-        <v>25</v>
+          <t>next_region_id</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>frozen_lake</t>
+        </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>level</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>다음 지역 해금 레벨</t>
+          <t>다음 지역 ID</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>해금 지연</t>
+          <t>-</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>해금 빨라짐</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -3944,30 +3944,30 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>weight_material</t>
+          <t>next_region_unlock_level</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>weight</t>
+          <t>level</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>탐색률 재료 기여</t>
+          <t>다음 지역 해금 레벨</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>비중↑</t>
+          <t>해금 지연</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>비중↓</t>
+          <t>해금 빨라짐</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -3984,7 +3984,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>weight_spirit</t>
+          <t>weight_material</t>
         </is>
       </c>
       <c r="C37" t="n">
@@ -3997,7 +3997,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>탐색률 정령 기여</t>
+          <t>탐색률 재료 기여</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -4024,7 +4024,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>weight_regional</t>
+          <t>weight_spirit</t>
         </is>
       </c>
       <c r="C38" t="n">
@@ -4037,7 +4037,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>탐색률 지역 기여</t>
+          <t>탐색률 정령 기여</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -4064,11 +4064,11 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>weight_treasure</t>
+          <t>weight_regional</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4077,7 +4077,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>탐색률 보물 기여</t>
+          <t>탐색률 지역 기여</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -4104,30 +4104,30 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>total_material_discovery</t>
+          <t>weight_treasure</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>count</t>
+          <t>weight</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>재료 발견 총량</t>
+          <t>탐색률 보물 기여</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>완료 난이도↑</t>
+          <t>비중↑</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>완료 난이도↓</t>
+          <t>비중↓</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -4144,11 +4144,11 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>total_spirit_discovery</t>
+          <t>total_material_discovery</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4157,7 +4157,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>정령 발견 총량</t>
+          <t>재료 발견 총량</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -4184,11 +4184,11 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>total_regional_discovery</t>
+          <t>total_spirit_discovery</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4197,7 +4197,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>지역 발견 총량</t>
+          <t>정령 발견 총량</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -4224,11 +4224,11 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>total_treasure_discovery</t>
+          <t>total_regional_discovery</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4237,7 +4237,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>보물 발견 총량</t>
+          <t>지역 발견 총량</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -4259,37 +4259,35 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Map3</t>
+          <t>Map2</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>region_id</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>frozen_lake</t>
-        </is>
+          <t>total_treasure_discovery</t>
+        </is>
+      </c>
+      <c r="C44" t="n">
+        <v>1</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>count</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>현재 적용 지역 ID</t>
+          <t>보물 발견 총량</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>완료 난이도↑</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>완료 난이도↓</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -4306,12 +4304,12 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>region_name</t>
+          <t>region_id</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>얼어붙은 설원</t>
+          <t>frozen_lake</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -4321,7 +4319,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>현재 적용 지역명</t>
+          <t>현재 적용 지역 ID</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -4348,30 +4346,32 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>unlock_level</t>
-        </is>
-      </c>
-      <c r="C46" t="n">
-        <v>25</v>
+          <t>region_name</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>얼어붙은 설원</t>
+        </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>level</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>입장 레벨</t>
+          <t>현재 적용 지역명</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>해금 지연</t>
+          <t>-</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>해금 빨라짐</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -4388,7 +4388,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>recommended_level</t>
+          <t>unlock_level</t>
         </is>
       </c>
       <c r="C47" t="n">
@@ -4401,17 +4401,17 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>권장 레벨</t>
+          <t>입장 레벨</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>권장치 상승</t>
+          <t>해금 지연</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>권장치 하락</t>
+          <t>해금 빨라짐</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -4428,30 +4428,30 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>mana_cost</t>
+          <t>recommended_level</t>
         </is>
       </c>
       <c r="C48" t="n">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>mana</t>
+          <t>level</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>탐사 1회 입장 소모 마나</t>
+          <t>권장 레벨</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>비용 증가</t>
+          <t>권장치 상승</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>비용 감소</t>
+          <t>권장치 하락</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
@@ -4468,30 +4468,30 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>explore_steps</t>
+          <t>mana_cost</t>
         </is>
       </c>
       <c r="C49" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>count</t>
+          <t>mana</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>탐색 행동 횟수</t>
+          <t>탐사 1회 입장 소모 마나</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>탐험 길어짐</t>
+          <t>비용 증가</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>탐험 짧아짐</t>
+          <t>비용 감소</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
@@ -4508,32 +4508,30 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>trace_item_id</t>
-        </is>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>lake_trace</t>
-        </is>
+          <t>explore_steps</t>
+        </is>
+      </c>
+      <c r="C50" t="n">
+        <v>10</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>count</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>지역 흔적 아이템 ID</t>
+          <t>탐색 행동 횟수</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>탐험 길어짐</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>탐험 짧아짐</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -4550,12 +4548,12 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>trace_name</t>
+          <t>trace_item_id</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>설원의 기억</t>
+          <t>lake_trace</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -4565,7 +4563,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>지역 흔적 아이템명</t>
+          <t>지역 흔적 아이템 ID</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -4592,30 +4590,32 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>hidden_stage_required_amount</t>
-        </is>
-      </c>
-      <c r="C52" t="n">
-        <v>20</v>
+          <t>trace_name</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>설원의 기억</t>
+        </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>count</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Hidden Stage 입장 흔적 수</t>
+          <t>지역 흔적 아이템명</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>입장 난이도↑</t>
+          <t>-</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>입장 난이도↓</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
@@ -4632,32 +4632,30 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>next_region_id</t>
-        </is>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>flame_ruins</t>
-        </is>
+          <t>hidden_stage_required_amount</t>
+        </is>
+      </c>
+      <c r="C53" t="n">
+        <v>20</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>count</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>다음 지역 ID</t>
+          <t>Hidden Stage 입장 흔적 수</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>입장 난이도↑</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>입장 난이도↓</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
@@ -4674,30 +4672,32 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>next_region_unlock_level</t>
-        </is>
-      </c>
-      <c r="C54" t="n">
-        <v>50</v>
+          <t>next_region_id</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>flame_ruins</t>
+        </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>level</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>다음 지역 해금 레벨</t>
+          <t>다음 지역 ID</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>해금 지연</t>
+          <t>-</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>해금 빨라짐</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
@@ -4714,30 +4714,30 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>weight_material</t>
+          <t>next_region_unlock_level</t>
         </is>
       </c>
       <c r="C55" t="n">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>weight</t>
+          <t>level</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>탐색률 재료 기여</t>
+          <t>다음 지역 해금 레벨</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>비중↑</t>
+          <t>해금 지연</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>비중↓</t>
+          <t>해금 빨라짐</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
@@ -4754,7 +4754,7 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>weight_spirit</t>
+          <t>weight_material</t>
         </is>
       </c>
       <c r="C56" t="n">
@@ -4767,7 +4767,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>탐색률 정령 기여</t>
+          <t>탐색률 재료 기여</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -4794,7 +4794,7 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>weight_regional</t>
+          <t>weight_spirit</t>
         </is>
       </c>
       <c r="C57" t="n">
@@ -4807,7 +4807,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>탐색률 지역 기여</t>
+          <t>탐색률 정령 기여</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -4834,11 +4834,11 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>weight_treasure</t>
+          <t>weight_regional</t>
         </is>
       </c>
       <c r="C58" t="n">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -4847,7 +4847,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>탐색률 보물 기여</t>
+          <t>탐색률 지역 기여</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -4874,30 +4874,30 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>total_material_discovery</t>
+          <t>weight_treasure</t>
         </is>
       </c>
       <c r="C59" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>count</t>
+          <t>weight</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>재료 발견 총량</t>
+          <t>탐색률 보물 기여</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>완료 난이도↑</t>
+          <t>비중↑</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>완료 난이도↓</t>
+          <t>비중↓</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
@@ -4914,11 +4914,11 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>total_spirit_discovery</t>
+          <t>total_material_discovery</t>
         </is>
       </c>
       <c r="C60" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -4927,7 +4927,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>정령 발견 총량</t>
+          <t>재료 발견 총량</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -4954,11 +4954,11 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>total_regional_discovery</t>
+          <t>total_spirit_discovery</t>
         </is>
       </c>
       <c r="C61" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -4967,7 +4967,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>지역 발견 총량</t>
+          <t>정령 발견 총량</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -4994,11 +4994,11 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>total_treasure_discovery</t>
+          <t>total_regional_discovery</t>
         </is>
       </c>
       <c r="C62" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -5007,7 +5007,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>보물 발견 총량</t>
+          <t>지역 발견 총량</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -5029,37 +5029,35 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Map4</t>
+          <t>Map3</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>region_id</t>
-        </is>
-      </c>
-      <c r="C63" t="inlineStr">
-        <is>
-          <t>flame_ruins</t>
-        </is>
+          <t>total_treasure_discovery</t>
+        </is>
+      </c>
+      <c r="C63" t="n">
+        <v>1</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>count</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>현재 적용 지역 ID</t>
+          <t>보물 발견 총량</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>완료 난이도↑</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>완료 난이도↓</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
@@ -5076,12 +5074,12 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>region_name</t>
+          <t>region_id</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>화염의 산맥</t>
+          <t>flame_ruins</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -5091,7 +5089,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>현재 적용 지역명</t>
+          <t>현재 적용 지역 ID</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -5118,30 +5116,32 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>unlock_level</t>
-        </is>
-      </c>
-      <c r="C65" t="n">
-        <v>50</v>
+          <t>region_name</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>화염의 산맥</t>
+        </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>level</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>입장 레벨</t>
+          <t>현재 적용 지역명</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>해금 지연</t>
+          <t>-</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>해금 빨라짐</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
@@ -5158,7 +5158,7 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>recommended_level</t>
+          <t>unlock_level</t>
         </is>
       </c>
       <c r="C66" t="n">
@@ -5171,17 +5171,17 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>권장 레벨</t>
+          <t>입장 레벨</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>권장치 상승</t>
+          <t>해금 지연</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>권장치 하락</t>
+          <t>해금 빨라짐</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
@@ -5198,30 +5198,30 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>mana_cost</t>
+          <t>recommended_level</t>
         </is>
       </c>
       <c r="C67" t="n">
-        <v>1</v>
+        <v>50</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>mana</t>
+          <t>level</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>탐사 1회 입장 소모 마나</t>
+          <t>권장 레벨</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>비용 증가</t>
+          <t>권장치 상승</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>비용 감소</t>
+          <t>권장치 하락</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
@@ -5238,30 +5238,30 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>explore_steps</t>
+          <t>mana_cost</t>
         </is>
       </c>
       <c r="C68" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>count</t>
+          <t>mana</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>탐색 행동 횟수</t>
+          <t>탐사 1회 입장 소모 마나</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>탐험 길어짐</t>
+          <t>비용 증가</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>탐험 짧아짐</t>
+          <t>비용 감소</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
@@ -5278,32 +5278,30 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>trace_item_id</t>
-        </is>
-      </c>
-      <c r="C69" t="inlineStr">
-        <is>
-          <t>ruins_trace</t>
-        </is>
+          <t>explore_steps</t>
+        </is>
+      </c>
+      <c r="C69" t="n">
+        <v>10</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>count</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>지역 흔적 아이템 ID</t>
+          <t>탐색 행동 횟수</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>탐험 길어짐</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>탐험 짧아짐</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
@@ -5320,12 +5318,12 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>trace_name</t>
+          <t>trace_item_id</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>화염의 잔재</t>
+          <t>ruins_trace</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -5335,7 +5333,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>지역 흔적 아이템명</t>
+          <t>지역 흔적 아이템 ID</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -5362,30 +5360,32 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>hidden_stage_required_amount</t>
-        </is>
-      </c>
-      <c r="C71" t="n">
-        <v>20</v>
+          <t>trace_name</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>화염의 잔재</t>
+        </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>count</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Hidden Stage 입장 흔적 수</t>
+          <t>지역 흔적 아이템명</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>입장 난이도↑</t>
+          <t>-</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>입장 난이도↓</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
@@ -5402,32 +5402,30 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>next_region_id</t>
-        </is>
-      </c>
-      <c r="C72" t="inlineStr">
-        <is>
-          <t>dark_swamp</t>
-        </is>
+          <t>hidden_stage_required_amount</t>
+        </is>
+      </c>
+      <c r="C72" t="n">
+        <v>20</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>count</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>다음 지역 ID</t>
+          <t>Hidden Stage 입장 흔적 수</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>입장 난이도↑</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>입장 난이도↓</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
@@ -5444,30 +5442,32 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>next_region_unlock_level</t>
-        </is>
-      </c>
-      <c r="C73" t="n">
-        <v>80</v>
+          <t>next_region_id</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>dark_swamp</t>
+        </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>level</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>다음 지역 해금 레벨</t>
+          <t>다음 지역 ID</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>해금 지연</t>
+          <t>-</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>해금 빨라짐</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
@@ -5484,30 +5484,30 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>weight_material</t>
+          <t>next_region_unlock_level</t>
         </is>
       </c>
       <c r="C74" t="n">
-        <v>30</v>
+        <v>80</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>weight</t>
+          <t>level</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>탐색률 재료 기여</t>
+          <t>다음 지역 해금 레벨</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>비중↑</t>
+          <t>해금 지연</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>비중↓</t>
+          <t>해금 빨라짐</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
@@ -5524,7 +5524,7 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>weight_spirit</t>
+          <t>weight_material</t>
         </is>
       </c>
       <c r="C75" t="n">
@@ -5537,7 +5537,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>탐색률 정령 기여</t>
+          <t>탐색률 재료 기여</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -5564,7 +5564,7 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>weight_regional</t>
+          <t>weight_spirit</t>
         </is>
       </c>
       <c r="C76" t="n">
@@ -5577,7 +5577,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>탐색률 지역 기여</t>
+          <t>탐색률 정령 기여</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -5604,11 +5604,11 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>weight_treasure</t>
+          <t>weight_regional</t>
         </is>
       </c>
       <c r="C77" t="n">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -5617,7 +5617,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>탐색률 보물 기여</t>
+          <t>탐색률 지역 기여</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -5644,30 +5644,30 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>total_material_discovery</t>
+          <t>weight_treasure</t>
         </is>
       </c>
       <c r="C78" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>count</t>
+          <t>weight</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>재료 발견 총량</t>
+          <t>탐색률 보물 기여</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>완료 난이도↑</t>
+          <t>비중↑</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>완료 난이도↓</t>
+          <t>비중↓</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
@@ -5684,11 +5684,11 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>total_spirit_discovery</t>
+          <t>total_material_discovery</t>
         </is>
       </c>
       <c r="C79" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -5697,7 +5697,7 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>정령 발견 총량</t>
+          <t>재료 발견 총량</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -5724,11 +5724,11 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>total_regional_discovery</t>
+          <t>total_spirit_discovery</t>
         </is>
       </c>
       <c r="C80" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -5737,7 +5737,7 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>지역 발견 총량</t>
+          <t>정령 발견 총량</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -5764,11 +5764,11 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>total_treasure_discovery</t>
+          <t>total_regional_discovery</t>
         </is>
       </c>
       <c r="C81" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -5777,7 +5777,7 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>보물 발견 총량</t>
+          <t>지역 발견 총량</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -5799,37 +5799,35 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Map5</t>
+          <t>Map4</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>region_id</t>
-        </is>
-      </c>
-      <c r="C82" t="inlineStr">
-        <is>
-          <t>dark_swamp</t>
-        </is>
+          <t>total_treasure_discovery</t>
+        </is>
+      </c>
+      <c r="C82" t="n">
+        <v>1</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>count</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>현재 적용 지역 ID</t>
+          <t>보물 발견 총량</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>완료 난이도↑</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>완료 난이도↓</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
@@ -5846,12 +5844,12 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>region_name</t>
+          <t>region_id</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>어둠의 습지</t>
+          <t>dark_swamp</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -5861,7 +5859,7 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>현재 적용 지역명</t>
+          <t>현재 적용 지역 ID</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -5888,30 +5886,32 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>unlock_level</t>
-        </is>
-      </c>
-      <c r="C84" t="n">
-        <v>80</v>
+          <t>region_name</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>어둠의 습지</t>
+        </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>level</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>입장 레벨</t>
+          <t>현재 적용 지역명</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>해금 지연</t>
+          <t>-</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>해금 빨라짐</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
@@ -5928,7 +5928,7 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>recommended_level</t>
+          <t>unlock_level</t>
         </is>
       </c>
       <c r="C85" t="n">
@@ -5941,17 +5941,17 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>권장 레벨</t>
+          <t>입장 레벨</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>권장치 상승</t>
+          <t>해금 지연</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>권장치 하락</t>
+          <t>해금 빨라짐</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
@@ -5968,30 +5968,30 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>mana_cost</t>
+          <t>recommended_level</t>
         </is>
       </c>
       <c r="C86" t="n">
-        <v>1</v>
+        <v>80</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>mana</t>
+          <t>level</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>탐사 1회 입장 소모 마나</t>
+          <t>권장 레벨</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>비용 증가</t>
+          <t>권장치 상승</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>비용 감소</t>
+          <t>권장치 하락</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
@@ -6008,30 +6008,30 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>explore_steps</t>
+          <t>mana_cost</t>
         </is>
       </c>
       <c r="C87" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>count</t>
+          <t>mana</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>탐색 행동 횟수</t>
+          <t>탐사 1회 입장 소모 마나</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>탐험 길어짐</t>
+          <t>비용 증가</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>탐험 짧아짐</t>
+          <t>비용 감소</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
@@ -6048,32 +6048,30 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>trace_item_id</t>
-        </is>
-      </c>
-      <c r="C88" t="inlineStr">
-        <is>
-          <t>final_trace</t>
-        </is>
+          <t>explore_steps</t>
+        </is>
+      </c>
+      <c r="C88" t="n">
+        <v>10</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>count</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>지역 흔적 아이템 ID</t>
+          <t>탐색 행동 횟수</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>탐험 길어짐</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>탐험 짧아짐</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
@@ -6090,12 +6088,12 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>trace_name</t>
+          <t>trace_item_id</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>어둠의 흔적</t>
+          <t>final_trace</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -6105,7 +6103,7 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>지역 흔적 아이템명</t>
+          <t>지역 흔적 아이템 ID</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -6132,30 +6130,32 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>hidden_stage_required_amount</t>
-        </is>
-      </c>
-      <c r="C90" t="n">
-        <v>20</v>
+          <t>trace_name</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>어둠의 흔적</t>
+        </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>count</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Hidden Stage 입장 흔적 수</t>
+          <t>지역 흔적 아이템명</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>입장 난이도↑</t>
+          <t>-</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>입장 난이도↓</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
@@ -6172,27 +6172,30 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>next_region_id</t>
-        </is>
+          <t>hidden_stage_required_amount</t>
+        </is>
+      </c>
+      <c r="C91" t="n">
+        <v>20</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>count</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>다음 지역 ID</t>
+          <t>Hidden Stage 입장 흔적 수</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>입장 난이도↑</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>입장 난이도↓</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
@@ -6209,30 +6212,27 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>next_region_unlock_level</t>
-        </is>
-      </c>
-      <c r="C92" t="n">
-        <v>0</v>
+          <t>next_region_id</t>
+        </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>level</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>다음 지역 해금 레벨</t>
+          <t>다음 지역 ID</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>해금 지연</t>
+          <t>-</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>해금 빨라짐</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
@@ -6249,30 +6249,30 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>weight_material</t>
+          <t>next_region_unlock_level</t>
         </is>
       </c>
       <c r="C93" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>weight</t>
+          <t>level</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>탐색률 재료 기여</t>
+          <t>다음 지역 해금 레벨</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>비중↑</t>
+          <t>해금 지연</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>비중↓</t>
+          <t>해금 빨라짐</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
@@ -6289,7 +6289,7 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>weight_spirit</t>
+          <t>weight_material</t>
         </is>
       </c>
       <c r="C94" t="n">
@@ -6302,7 +6302,7 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>탐색률 정령 기여</t>
+          <t>탐색률 재료 기여</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -6329,7 +6329,7 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>weight_regional</t>
+          <t>weight_spirit</t>
         </is>
       </c>
       <c r="C95" t="n">
@@ -6342,7 +6342,7 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>탐색률 지역 기여</t>
+          <t>탐색률 정령 기여</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -6369,11 +6369,11 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>weight_treasure</t>
+          <t>weight_regional</t>
         </is>
       </c>
       <c r="C96" t="n">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -6382,7 +6382,7 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>탐색률 보물 기여</t>
+          <t>탐색률 지역 기여</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -6409,30 +6409,30 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>total_material_discovery</t>
+          <t>weight_treasure</t>
         </is>
       </c>
       <c r="C97" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>count</t>
+          <t>weight</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>재료 발견 총량</t>
+          <t>탐색률 보물 기여</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>완료 난이도↑</t>
+          <t>비중↑</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>완료 난이도↓</t>
+          <t>비중↓</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
@@ -6449,11 +6449,11 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>total_spirit_discovery</t>
+          <t>total_material_discovery</t>
         </is>
       </c>
       <c r="C98" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -6462,7 +6462,7 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>정령 발견 총량</t>
+          <t>재료 발견 총량</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
@@ -6489,11 +6489,11 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>total_regional_discovery</t>
+          <t>total_spirit_discovery</t>
         </is>
       </c>
       <c r="C99" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -6502,7 +6502,7 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>지역 발견 총량</t>
+          <t>정령 발견 총량</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
@@ -6529,33 +6529,73 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
+          <t>total_regional_discovery</t>
+        </is>
+      </c>
+      <c r="C100" t="n">
+        <v>4</v>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>지역 발견 총량</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>완료 난이도↑</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>완료 난이도↓</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>src/data/regions.ts</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>Map5</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
           <t>total_treasure_discovery</t>
         </is>
       </c>
-      <c r="C100" t="n">
-        <v>1</v>
-      </c>
-      <c r="D100" t="inlineStr">
+      <c r="C101" t="n">
+        <v>1</v>
+      </c>
+      <c r="D101" t="inlineStr">
         <is>
           <t>count</t>
         </is>
       </c>
-      <c r="E100" t="inlineStr">
+      <c r="E101" t="inlineStr">
         <is>
           <t>보물 발견 총량</t>
         </is>
       </c>
-      <c r="F100" t="inlineStr">
+      <c r="F101" t="inlineStr">
         <is>
           <t>완료 난이도↑</t>
         </is>
       </c>
-      <c r="G100" t="inlineStr">
+      <c r="G101" t="inlineStr">
         <is>
           <t>완료 난이도↓</t>
         </is>
       </c>
-      <c r="H100" t="inlineStr">
+      <c r="H101" t="inlineStr">
         <is>
           <t>src/data/regions.ts</t>
         </is>

--- a/balance/Spiria_Game_Balance_v1.0.xlsx
+++ b/balance/Spiria_Game_Balance_v1.0.xlsx
@@ -2,9 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <workbookProtection/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="0" yWindow="880" windowWidth="34200" windowHeight="21360" tabRatio="600" firstSheet="0" activeTab="7" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet name="00_사용가이드" sheetId="1" state="visible" r:id="rId1"/>
@@ -14,56 +13,71 @@
     <sheet name="04_Quest" sheetId="5" state="visible" r:id="rId5"/>
     <sheet name="05_Item" sheetId="6" state="visible" r:id="rId6"/>
     <sheet name="06_Drop" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="07_Spirit" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="08_Recipe" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet name="09_Economy" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="09_Economy" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="191029" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="8">
+  <fonts count="7">
     <font>
-      <name val="Calibri"/>
+      <name val="맑은 고딕"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <name val="맑은 고딕"/>
+      <charset val="129"/>
+      <family val="2"/>
       <b val="1"/>
-      <color rgb="00FFFFFF"/>
+      <color rgb="FFFFFFFF"/>
+      <sz val="11"/>
     </font>
     <font>
+      <name val="맑은 고딕"/>
+      <charset val="129"/>
+      <family val="2"/>
       <b val="1"/>
+      <sz val="11"/>
     </font>
     <font>
+      <name val="맑은 고딕"/>
+      <charset val="129"/>
+      <family val="2"/>
       <b val="1"/>
-      <color rgb="00B91C1C"/>
+      <color rgb="FFB91C1C"/>
+      <sz val="11"/>
     </font>
     <font>
+      <name val="맑은 고딕"/>
+      <charset val="129"/>
+      <family val="2"/>
       <b val="1"/>
-      <color rgb="00FFFFFF"/>
-      <sz val="15"/>
-    </font>
-    <font>
-      <b val="1"/>
-      <color rgb="00B45309"/>
-    </font>
-    <font>
-      <b val="1"/>
-      <color rgb="00FFFFFF"/>
+      <color rgb="FFFFFFFF"/>
       <sz val="14"/>
     </font>
     <font>
-      <color rgb="00B91C1C"/>
+      <name val="맑은 고딕"/>
+      <charset val="129"/>
+      <family val="2"/>
+      <color rgb="FFB91C1C"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="맑은 고딕"/>
+      <charset val="129"/>
+      <family val="3"/>
+      <sz val="8"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="44">
+  <fills count="28">
     <fill>
       <patternFill/>
     </fill>
@@ -72,216 +86,136 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="001F2937"/>
+        <fgColor rgb="FF334155"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00E5E7EB"/>
+        <fgColor rgb="FF0F766E"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00DBEAFE"/>
+        <fgColor rgb="FF115E59"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FEF3C7"/>
+        <fgColor rgb="FF7C2D12"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FDE68A"/>
+        <fgColor rgb="FF9A3412"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FCE7F3"/>
+        <fgColor rgb="FF1D4ED8"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00DCFCE7"/>
+        <fgColor rgb="FF1E40AF"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00D1FAE5"/>
+        <fgColor rgb="FFB8BEC9"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00E9D5FF"/>
+        <fgColor rgb="FF79D8C6"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00EDE9FE"/>
+        <fgColor rgb="FF6EBEFF"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00F3F4F6"/>
+        <fgColor rgb="FF8ED46B"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FEE2E2"/>
+        <fgColor rgb="FFE5C46B"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00334155"/>
+        <fgColor rgb="FFA894FF"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="000F766E"/>
+        <fgColor rgb="FF866BFF"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00115E59"/>
+        <fgColor rgb="FF6A46E8"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="007C2D12"/>
+        <fgColor rgb="FF4E5EEA"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="009A3412"/>
+        <fgColor rgb="FFF6E7A8"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="001D4ED8"/>
+        <fgColor rgb="FF6D28D9"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="001E40AF"/>
+        <fgColor rgb="FF7C3AED"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00B8BEC9"/>
+        <fgColor rgb="FF0E7490"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="0079D8C6"/>
+        <fgColor rgb="FF155E75"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="006EBEFF"/>
+        <fgColor rgb="FF9F1239"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="008ED46B"/>
+        <fgColor rgb="FFBE123C"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00E5C46B"/>
+        <fgColor rgb="FF92400E"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00A894FF"/>
+        <fgColor rgb="FFB45309"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00866BFF"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="006A46E8"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="004E5EEA"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00F6E7A8"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="006D28D9"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="007C3AED"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="000E7490"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00155E75"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="009F1239"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00BE123C"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="004C1D95"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="005B21B6"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00365314"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="003F6212"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="0092400E"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00B45309"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="000F172A"/>
+        <fgColor rgb="FF0F172A"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="3">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -291,238 +225,115 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="002D3748"/>
+        <color rgb="FF334155"/>
       </left>
       <right style="thin">
-        <color rgb="002D3748"/>
+        <color rgb="FF334155"/>
       </right>
       <top style="thin">
-        <color rgb="002D3748"/>
+        <color rgb="FF334155"/>
       </top>
       <bottom style="thin">
-        <color rgb="002D3748"/>
+        <color rgb="FF334155"/>
       </bottom>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="00334155"/>
-      </left>
-      <right style="thin">
-        <color rgb="00334155"/>
-      </right>
-      <top style="thin">
-        <color rgb="00334155"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="00334155"/>
-      </bottom>
+      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="72">
+  <cellXfs count="32">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="12" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="13" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="14" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="15" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="14" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="16" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="15" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="17" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="16" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="18" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="17" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="15" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="16" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="19" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="20" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="21" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="22" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="23" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="24" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="25" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="26" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="27" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="28" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="29" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="30" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="18" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="17" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="20" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="22" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="24" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="26" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="27" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="18" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="31" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="32" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="33" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="19" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="34" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="21" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="35" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="23" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="36" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="25" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="37" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="38" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="39" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="40" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="41" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="42" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="43" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="14" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="16" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="20" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="18" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="32" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="34" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="36" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="38" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="40" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="42" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="표준" xfId="0" builtinId="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
@@ -886,802 +697,402 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:H11"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="17"/>
   <cols>
-    <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="24" customWidth="1" min="3" max="3"/>
-    <col width="22" customWidth="1" min="4" max="4"/>
-    <col width="28" customWidth="1" min="5" max="5"/>
-    <col width="28" customWidth="1" min="6" max="6"/>
-    <col width="20" customWidth="1" min="7" max="7"/>
-    <col width="10" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" style="24" min="1" max="2"/>
+    <col width="24" customWidth="1" style="24" min="3" max="3"/>
+    <col width="22" customWidth="1" style="24" min="4" max="4"/>
+    <col width="28" customWidth="1" style="24" min="5" max="6"/>
+    <col width="20" customWidth="1" style="24" min="7" max="7"/>
+    <col width="10" customWidth="1" style="24" min="8" max="8"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="60" t="inlineStr">
+    <row r="1" ht="20" customHeight="1" s="24">
+      <c r="A1" s="23" t="inlineStr">
         <is>
           <t>Spiria 밸런스 운영 가이드</t>
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" s="61" t="inlineStr">
+    <row r="2" ht="18" customHeight="1" s="24">
+      <c r="A2" s="14" t="inlineStr">
         <is>
           <t>분류</t>
         </is>
       </c>
-      <c r="B2" s="61" t="inlineStr">
+      <c r="B2" s="14" t="inlineStr">
         <is>
           <t>탭</t>
         </is>
       </c>
-      <c r="C2" s="61" t="inlineStr">
+      <c r="C2" s="14" t="inlineStr">
         <is>
           <t>여기서 조절하는 것</t>
         </is>
       </c>
-      <c r="D2" s="61" t="inlineStr">
+      <c r="D2" s="14" t="inlineStr">
         <is>
           <t>대표 키</t>
         </is>
       </c>
-      <c r="E2" s="61" t="inlineStr">
+      <c r="E2" s="14" t="inlineStr">
         <is>
           <t>연동 파일</t>
         </is>
       </c>
-      <c r="F2" s="61" t="inlineStr">
+      <c r="F2" s="14" t="inlineStr">
         <is>
           <t>설명</t>
         </is>
       </c>
-      <c r="G2" s="61" t="inlineStr">
+      <c r="G2" s="14" t="inlineStr">
         <is>
           <t>비고</t>
         </is>
       </c>
-      <c r="H2" s="61" t="inlineStr"/>
-    </row>
-    <row r="3">
-      <c r="A3" s="20" t="inlineStr">
+      <c r="H2" s="14" t="n"/>
+    </row>
+    <row r="3" ht="36" customHeight="1" s="24">
+      <c r="A3" s="1" t="inlineStr">
         <is>
           <t>운영</t>
         </is>
       </c>
-      <c r="B3" s="20" t="inlineStr">
+      <c r="B3" s="1" t="inlineStr">
         <is>
           <t>01_Player</t>
         </is>
       </c>
-      <c r="C3" s="20" t="inlineStr">
+      <c r="C3" s="1" t="inlineStr">
         <is>
           <t>플레이어 기본값/마력</t>
         </is>
       </c>
-      <c r="D3" s="20" t="inlineStr">
+      <c r="D3" s="1" t="inlineStr">
         <is>
           <t>max_level, initial_mana, max_mana</t>
         </is>
       </c>
-      <c r="E3" s="20" t="inlineStr">
+      <c r="E3" s="1" t="inlineStr">
         <is>
           <t>src/data/constants.ts</t>
         </is>
       </c>
-      <c r="F3" s="20" t="inlineStr">
+      <c r="F3" s="1" t="inlineStr">
         <is>
           <t>플레이어 성장과 마나 회복의 기준값</t>
         </is>
       </c>
-      <c r="G3" s="20" t="inlineStr">
+      <c r="G3" s="1" t="inlineStr">
         <is>
           <t>현재 값은 예시 기준</t>
         </is>
       </c>
-      <c r="H3" s="20" t="inlineStr"/>
-    </row>
-    <row r="4">
-      <c r="A4" s="20" t="inlineStr">
+      <c r="H3" s="1" t="n"/>
+    </row>
+    <row r="4" ht="36" customHeight="1" s="24">
+      <c r="A4" s="1" t="inlineStr">
         <is>
           <t>운영</t>
         </is>
       </c>
-      <c r="B4" s="20" t="inlineStr">
+      <c r="B4" s="1" t="inlineStr">
         <is>
           <t>02_Level</t>
         </is>
       </c>
-      <c r="C4" s="20" t="inlineStr">
+      <c r="C4" s="1" t="inlineStr">
         <is>
           <t>레벨 EXP/컬러</t>
         </is>
       </c>
-      <c r="D4" s="20" t="inlineStr">
+      <c r="D4" s="1" t="inlineStr">
         <is>
           <t>exp_to_next, LEVEL_COLORS</t>
         </is>
       </c>
-      <c r="E4" s="20" t="inlineStr">
+      <c r="E4" s="1" t="inlineStr">
         <is>
           <t>src/data/levels.ts</t>
         </is>
       </c>
-      <c r="F4" s="20" t="inlineStr">
+      <c r="F4" s="1" t="inlineStr">
         <is>
           <t>레벨업 속도와 레벨 색상</t>
         </is>
       </c>
-      <c r="G4" s="20" t="inlineStr">
+      <c r="G4" s="1" t="inlineStr">
         <is>
           <t>전 구간 조절 가능</t>
         </is>
       </c>
-      <c r="H4" s="20" t="inlineStr"/>
-    </row>
-    <row r="5">
-      <c r="A5" s="20" t="inlineStr">
+      <c r="H4" s="1" t="n"/>
+    </row>
+    <row r="5" ht="54" customHeight="1" s="24">
+      <c r="A5" s="1" t="inlineStr">
         <is>
           <t>운영</t>
         </is>
       </c>
-      <c r="B5" s="20" t="inlineStr">
+      <c r="B5" s="1" t="inlineStr">
         <is>
           <t>03_Exploration</t>
         </is>
       </c>
-      <c r="C5" s="20" t="inlineStr">
+      <c r="C5" s="1" t="inlineStr">
         <is>
           <t>탐사 지역 비용/보상</t>
         </is>
       </c>
-      <c r="D5" s="20" t="inlineStr">
+      <c r="D5" s="1" t="inlineStr">
         <is>
           <t>mana_cost, exploreSteps, reward draft</t>
         </is>
       </c>
-      <c r="E5" s="20" t="inlineStr">
+      <c r="E5" s="1" t="inlineStr">
         <is>
           <t>src/data/regions.ts, src/data/drops.ts</t>
         </is>
       </c>
-      <c r="F5" s="20" t="inlineStr">
+      <c r="F5" s="1" t="inlineStr">
         <is>
           <t>탐사 1회 진행 구조와 보상</t>
         </is>
       </c>
-      <c r="G5" s="20" t="inlineStr">
+      <c r="G5" s="1" t="inlineStr">
         <is>
           <t>Map1 우선 적용</t>
         </is>
       </c>
-      <c r="H5" s="20" t="inlineStr"/>
-    </row>
-    <row r="6">
-      <c r="A6" s="20" t="inlineStr">
+      <c r="H5" s="1" t="n"/>
+    </row>
+    <row r="6" ht="36" customHeight="1" s="24">
+      <c r="A6" s="1" t="inlineStr">
         <is>
           <t>운영</t>
         </is>
       </c>
-      <c r="B6" s="20" t="inlineStr">
+      <c r="B6" s="1" t="inlineStr">
         <is>
           <t>04_Quest</t>
         </is>
       </c>
-      <c r="C6" s="20" t="inlineStr">
+      <c r="C6" s="1" t="inlineStr">
         <is>
           <t>의뢰 보상/생성</t>
         </is>
       </c>
-      <c r="D6" s="20" t="inlineStr">
+      <c r="D6" s="1" t="inlineStr">
         <is>
           <t>QUEST_REWARDS, QUEST_TIER_WEIGHTS</t>
         </is>
       </c>
-      <c r="E6" s="20" t="inlineStr">
+      <c r="E6" s="1" t="inlineStr">
         <is>
           <t>src/data/quests.ts</t>
         </is>
       </c>
-      <c r="F6" s="20" t="inlineStr">
+      <c r="F6" s="1" t="inlineStr">
         <is>
           <t>의뢰 등급별 보상과 생성비율</t>
         </is>
       </c>
-      <c r="G6" s="20" t="inlineStr">
+      <c r="G6" s="1" t="inlineStr">
         <is>
           <t>거절 패널티 포함</t>
         </is>
       </c>
-      <c r="H6" s="20" t="inlineStr"/>
-    </row>
-    <row r="7">
-      <c r="A7" s="20" t="inlineStr">
+      <c r="H6" s="1" t="n"/>
+    </row>
+    <row r="7" ht="36" customHeight="1" s="24">
+      <c r="A7" s="1" t="inlineStr">
         <is>
           <t>운영</t>
         </is>
       </c>
-      <c r="B7" s="20" t="inlineStr">
+      <c r="B7" s="1" t="inlineStr">
         <is>
           <t>05_Item</t>
         </is>
       </c>
-      <c r="C7" s="20" t="inlineStr">
+      <c r="C7" s="1" t="inlineStr">
         <is>
           <t>재료 기본 정보</t>
         </is>
       </c>
-      <c r="D7" s="20" t="inlineStr">
+      <c r="D7" s="1" t="inlineStr">
         <is>
           <t>id, name, category</t>
         </is>
       </c>
-      <c r="E7" s="20" t="inlineStr">
+      <c r="E7" s="1" t="inlineStr">
         <is>
           <t>src/data/items.ts</t>
         </is>
       </c>
-      <c r="F7" s="20" t="inlineStr">
+      <c r="F7" s="1" t="inlineStr">
         <is>
           <t>재료/기타 아이템 목록</t>
         </is>
       </c>
-      <c r="G7" s="20" t="inlineStr">
+      <c r="G7" s="1" t="inlineStr">
         <is>
           <t>가치값은 추후 추가 가능</t>
         </is>
       </c>
-      <c r="H7" s="20" t="inlineStr"/>
-    </row>
-    <row r="8">
-      <c r="A8" s="20" t="inlineStr">
+      <c r="H7" s="1" t="n"/>
+    </row>
+    <row r="8" ht="18" customHeight="1" s="24">
+      <c r="A8" s="1" t="inlineStr">
         <is>
           <t>운영</t>
         </is>
       </c>
-      <c r="B8" s="20" t="inlineStr">
+      <c r="B8" s="1" t="inlineStr">
         <is>
           <t>06_Drop</t>
         </is>
       </c>
-      <c r="C8" s="20" t="inlineStr">
+      <c r="C8" s="1" t="inlineStr">
         <is>
           <t>지역별 드랍 확률</t>
         </is>
       </c>
-      <c r="D8" s="20" t="inlineStr">
+      <c r="D8" s="1" t="inlineStr">
         <is>
           <t>dropTable weight, count</t>
         </is>
       </c>
-      <c r="E8" s="20" t="inlineStr">
-        <is>
-          <t>src/data/regions.ts</t>
-        </is>
-      </c>
-      <c r="F8" s="20" t="inlineStr">
+      <c r="E8" s="1" t="inlineStr">
+        <is>
+          <t>src/data/regions.ts</t>
+        </is>
+      </c>
+      <c r="F8" s="1" t="inlineStr">
         <is>
           <t>Map별 드랍 비율</t>
         </is>
       </c>
-      <c r="G8" s="20" t="inlineStr">
+      <c r="G8" s="1" t="inlineStr">
         <is>
           <t>Map2~5는 예시 탭만</t>
         </is>
       </c>
-      <c r="H8" s="20" t="inlineStr"/>
-    </row>
-    <row r="9">
-      <c r="A9" s="20" t="inlineStr">
+      <c r="H8" s="1" t="n"/>
+    </row>
+    <row r="9" ht="18" customHeight="1" s="24">
+      <c r="A9" s="1" t="inlineStr">
         <is>
           <t>운영</t>
         </is>
       </c>
-      <c r="B9" s="20" t="inlineStr">
+      <c r="B9" s="1" t="inlineStr">
         <is>
           <t>07_Spirit</t>
         </is>
       </c>
-      <c r="C9" s="20" t="inlineStr">
+      <c r="C9" s="1" t="inlineStr">
         <is>
           <t>정령 정보(미정)</t>
         </is>
       </c>
-      <c r="D9" s="20" t="inlineStr">
+      <c r="D9" s="1" t="inlineStr">
         <is>
           <t>희귀도, 해금 조건, 조각</t>
         </is>
       </c>
-      <c r="E9" s="20" t="inlineStr">
+      <c r="E9" s="1" t="inlineStr">
         <is>
           <t>src/data/spirits.ts</t>
         </is>
       </c>
-      <c r="F9" s="20" t="inlineStr">
+      <c r="F9" s="1" t="inlineStr">
         <is>
           <t>정령 확장용 템플릿</t>
         </is>
       </c>
-      <c r="G9" s="20" t="inlineStr">
+      <c r="G9" s="1" t="inlineStr">
         <is>
           <t>미정은 TBD로 표기</t>
         </is>
       </c>
-      <c r="H9" s="20" t="inlineStr"/>
-    </row>
-    <row r="10">
-      <c r="A10" s="20" t="inlineStr">
+      <c r="H9" s="1" t="n"/>
+    </row>
+    <row r="10" ht="18" customHeight="1" s="24">
+      <c r="A10" s="1" t="inlineStr">
         <is>
           <t>운영</t>
         </is>
       </c>
-      <c r="B10" s="20" t="inlineStr">
+      <c r="B10" s="1" t="inlineStr">
         <is>
           <t>08_Recipe</t>
         </is>
       </c>
-      <c r="C10" s="20" t="inlineStr">
+      <c r="C10" s="1" t="inlineStr">
         <is>
           <t>레시피(미정)</t>
         </is>
       </c>
-      <c r="D10" s="20" t="inlineStr">
+      <c r="D10" s="1" t="inlineStr">
         <is>
           <t>재료 조합, 결과 정령</t>
         </is>
       </c>
-      <c r="E10" s="20" t="inlineStr">
+      <c r="E10" s="1" t="inlineStr">
         <is>
           <t>src/data/recipes.ts</t>
         </is>
       </c>
-      <c r="F10" s="20" t="inlineStr">
+      <c r="F10" s="1" t="inlineStr">
         <is>
           <t>정령 제작 룰 확장용 템플릿</t>
         </is>
       </c>
-      <c r="G10" s="20" t="inlineStr">
+      <c r="G10" s="1" t="inlineStr">
         <is>
           <t>미정은 TBD로 표기</t>
         </is>
       </c>
-      <c r="H10" s="20" t="inlineStr"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="20" t="inlineStr">
+      <c r="H10" s="1" t="n"/>
+    </row>
+    <row r="11" ht="36" customHeight="1" s="24">
+      <c r="A11" s="1" t="inlineStr">
         <is>
           <t>운영</t>
         </is>
       </c>
-      <c r="B11" s="20" t="inlineStr">
+      <c r="B11" s="1" t="inlineStr">
         <is>
           <t>09_Economy</t>
         </is>
       </c>
-      <c r="C11" s="20" t="inlineStr">
+      <c r="C11" s="1" t="inlineStr">
         <is>
           <t>전체 경제/제작비</t>
         </is>
       </c>
-      <c r="D11" s="20" t="inlineStr">
+      <c r="D11" s="1" t="inlineStr">
         <is>
           <t>CRAFTING_COST_TIERS, TOTAL_EXP_TO_MAX</t>
         </is>
       </c>
-      <c r="E11" s="20" t="inlineStr">
+      <c r="E11" s="1" t="inlineStr">
         <is>
           <t>src/data/economy.ts</t>
         </is>
       </c>
-      <c r="F11" s="20" t="inlineStr">
+      <c r="F11" s="1" t="inlineStr">
         <is>
           <t>제작비/총 성장량</t>
         </is>
       </c>
-      <c r="G11" s="20" t="inlineStr">
+      <c r="G11" s="1" t="inlineStr">
         <is>
           <t>게임 전체 균형 축</t>
         </is>
       </c>
-      <c r="H11" s="20" t="inlineStr"/>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:H1"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:H10"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="32" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="10" customWidth="1" min="4" max="4"/>
-    <col width="24" customWidth="1" min="5" max="5"/>
-    <col width="16" customWidth="1" min="6" max="6"/>
-    <col width="16" customWidth="1" min="7" max="7"/>
-    <col width="28" customWidth="1" min="8" max="8"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="58" t="inlineStr">
-        <is>
-          <t>09_Economy - 전체 경제/제작 밸런스</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="71" t="inlineStr">
-        <is>
-          <t>카테고리</t>
-        </is>
-      </c>
-      <c r="B2" s="71" t="inlineStr">
-        <is>
-          <t>키</t>
-        </is>
-      </c>
-      <c r="C2" s="71" t="inlineStr">
-        <is>
-          <t>value</t>
-        </is>
-      </c>
-      <c r="D2" s="71" t="inlineStr">
-        <is>
-          <t>단위</t>
-        </is>
-      </c>
-      <c r="E2" s="71" t="inlineStr">
-        <is>
-          <t>설명</t>
-        </is>
-      </c>
-      <c r="F2" s="71" t="inlineStr">
-        <is>
-          <t>올리면</t>
-        </is>
-      </c>
-      <c r="G2" s="71" t="inlineStr">
-        <is>
-          <t>내리면</t>
-        </is>
-      </c>
-      <c r="H2" s="71" t="inlineStr">
-        <is>
-          <t>코드소스</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="20" t="inlineStr">
-        <is>
-          <t>경제</t>
-        </is>
-      </c>
-      <c r="B3" s="20" t="inlineStr">
-        <is>
-          <t>total_exp_required</t>
-        </is>
-      </c>
-      <c r="C3" s="63" t="n">
-        <v>43450</v>
-      </c>
-      <c r="D3" s="20" t="inlineStr">
-        <is>
-          <t>exp</t>
-        </is>
-      </c>
-      <c r="E3" s="20" t="inlineStr">
-        <is>
-          <t>만렙까지 총 EXP</t>
-        </is>
-      </c>
-      <c r="F3" s="20" t="inlineStr">
-        <is>
-          <t>성장기간 증가</t>
-        </is>
-      </c>
-      <c r="G3" s="20" t="inlineStr">
-        <is>
-          <t>성장기간 감소</t>
-        </is>
-      </c>
-      <c r="H3" s="20" t="inlineStr">
-        <is>
-          <t>src/data/economy.ts</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="20" t="inlineStr">
-        <is>
-          <t>경제</t>
-        </is>
-      </c>
-      <c r="B4" s="20" t="inlineStr">
-        <is>
-          <t>main_color</t>
-        </is>
-      </c>
-      <c r="C4" s="63" t="inlineStr">
-        <is>
-          <t>#A894FF</t>
-        </is>
-      </c>
-      <c r="D4" s="20" t="inlineStr">
-        <is>
-          <t>hex</t>
-        </is>
-      </c>
-      <c r="E4" s="20" t="inlineStr">
-        <is>
-          <t>경제 메인 컬러</t>
-        </is>
-      </c>
-      <c r="F4" s="20" t="inlineStr">
-        <is>
-          <t>UI 강조 변경</t>
-        </is>
-      </c>
-      <c r="G4" s="20" t="inlineStr">
-        <is>
-          <t>UI 강조 완화</t>
-        </is>
-      </c>
-      <c r="H4" s="20" t="inlineStr">
-        <is>
-          <t>src/data/economy.ts</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="20" t="inlineStr">
-        <is>
-          <t>제작티어</t>
-        </is>
-      </c>
-      <c r="B5" s="20" t="inlineStr">
-        <is>
-          <t>tier1_required_per_material</t>
-        </is>
-      </c>
-      <c r="C5" s="63" t="n">
-        <v>2</v>
-      </c>
-      <c r="D5" s="20" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="E5" s="20" t="inlineStr">
-        <is>
-          <t>Lv1~19 재료당 요구량</t>
-        </is>
-      </c>
-      <c r="F5" s="20" t="inlineStr">
-        <is>
-          <t>초반 난이도↑</t>
-        </is>
-      </c>
-      <c r="G5" s="20" t="inlineStr">
-        <is>
-          <t>초반 난이도↓</t>
-        </is>
-      </c>
-      <c r="H5" s="20" t="inlineStr">
-        <is>
-          <t>src/data/economy.ts</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="20" t="inlineStr">
-        <is>
-          <t>제작티어</t>
-        </is>
-      </c>
-      <c r="B6" s="20" t="inlineStr">
-        <is>
-          <t>tier2_required_per_material</t>
-        </is>
-      </c>
-      <c r="C6" s="63" t="n">
-        <v>3</v>
-      </c>
-      <c r="D6" s="20" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="E6" s="20" t="inlineStr">
-        <is>
-          <t>Lv20~49 재료당 요구량</t>
-        </is>
-      </c>
-      <c r="F6" s="20" t="inlineStr">
-        <is>
-          <t>중반 난이도↑</t>
-        </is>
-      </c>
-      <c r="G6" s="20" t="inlineStr">
-        <is>
-          <t>중반 난이도↓</t>
-        </is>
-      </c>
-      <c r="H6" s="20" t="inlineStr">
-        <is>
-          <t>src/data/economy.ts</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="20" t="inlineStr">
-        <is>
-          <t>제작티어</t>
-        </is>
-      </c>
-      <c r="B7" s="20" t="inlineStr">
-        <is>
-          <t>tier3_required_per_material</t>
-        </is>
-      </c>
-      <c r="C7" s="63" t="n">
-        <v>4</v>
-      </c>
-      <c r="D7" s="20" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="E7" s="20" t="inlineStr">
-        <is>
-          <t>Lv50~79 재료당 요구량</t>
-        </is>
-      </c>
-      <c r="F7" s="20" t="inlineStr">
-        <is>
-          <t>후반 난이도↑</t>
-        </is>
-      </c>
-      <c r="G7" s="20" t="inlineStr">
-        <is>
-          <t>후반 난이도↓</t>
-        </is>
-      </c>
-      <c r="H7" s="20" t="inlineStr">
-        <is>
-          <t>src/data/economy.ts</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="20" t="inlineStr">
-        <is>
-          <t>제작티어</t>
-        </is>
-      </c>
-      <c r="B8" s="20" t="inlineStr">
-        <is>
-          <t>tier4_required_per_material</t>
-        </is>
-      </c>
-      <c r="C8" s="63" t="n">
-        <v>5</v>
-      </c>
-      <c r="D8" s="20" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="E8" s="20" t="inlineStr">
-        <is>
-          <t>Lv80~99 재료당 요구량</t>
-        </is>
-      </c>
-      <c r="F8" s="20" t="inlineStr">
-        <is>
-          <t>후반 난이도↑</t>
-        </is>
-      </c>
-      <c r="G8" s="20" t="inlineStr">
-        <is>
-          <t>후반 난이도↓</t>
-        </is>
-      </c>
-      <c r="H8" s="20" t="inlineStr">
-        <is>
-          <t>src/data/economy.ts</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="20" t="inlineStr">
-        <is>
-          <t>제작공통</t>
-        </is>
-      </c>
-      <c r="B9" s="20" t="inlineStr">
-        <is>
-          <t>selected_material_kinds</t>
-        </is>
-      </c>
-      <c r="C9" s="63" t="n">
-        <v>3</v>
-      </c>
-      <c r="D9" s="20" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="E9" s="20" t="inlineStr">
-        <is>
-          <t>제작에 필요한 재료 종류 수</t>
-        </is>
-      </c>
-      <c r="F9" s="20" t="inlineStr">
-        <is>
-          <t>난이도↑</t>
-        </is>
-      </c>
-      <c r="G9" s="20" t="inlineStr">
-        <is>
-          <t>난이도↓</t>
-        </is>
-      </c>
-      <c r="H9" s="20" t="inlineStr">
-        <is>
-          <t>src/data/economy.ts</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="20" t="inlineStr">
-        <is>
-          <t>패널티</t>
-        </is>
-      </c>
-      <c r="B10" s="20" t="inlineStr">
-        <is>
-          <t>quest_reject_penalty_gold</t>
-        </is>
-      </c>
-      <c r="C10" s="63" t="n">
-        <v>200</v>
-      </c>
-      <c r="D10" s="20" t="inlineStr">
-        <is>
-          <t>gold</t>
-        </is>
-      </c>
-      <c r="E10" s="20" t="inlineStr">
-        <is>
-          <t>의뢰 거절 패널티</t>
-        </is>
-      </c>
-      <c r="F10" s="20" t="inlineStr">
-        <is>
-          <t>거절 부담↑</t>
-        </is>
-      </c>
-      <c r="G10" s="20" t="inlineStr">
-        <is>
-          <t>거절 부담↓</t>
-        </is>
-      </c>
-      <c r="H10" s="20" t="inlineStr">
-        <is>
-          <t>src/components/CraftScreen.tsx</t>
-        </is>
-      </c>
+      <c r="H11" s="1" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -1698,302 +1109,301 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:H8"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="17"/>
   <cols>
-    <col width="16" customWidth="1" min="1" max="1"/>
-    <col width="28" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="10" customWidth="1" min="4" max="4"/>
-    <col width="24" customWidth="1" min="5" max="5"/>
-    <col width="18" customWidth="1" min="6" max="6"/>
-    <col width="18" customWidth="1" min="7" max="7"/>
-    <col width="28" customWidth="1" min="8" max="8"/>
+    <col width="16" customWidth="1" style="24" min="1" max="1"/>
+    <col width="28" customWidth="1" style="24" min="2" max="2"/>
+    <col width="12" customWidth="1" style="24" min="3" max="3"/>
+    <col width="10" customWidth="1" style="24" min="4" max="4"/>
+    <col width="24" customWidth="1" style="24" min="5" max="5"/>
+    <col width="18" customWidth="1" style="24" min="6" max="7"/>
+    <col width="28" customWidth="1" style="24" min="8" max="8"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="29" t="inlineStr">
+    <row r="1" ht="20" customHeight="1" s="24">
+      <c r="A1" s="25" t="inlineStr">
         <is>
           <t>01_Player - 플레이어 레벨·마력 기본값</t>
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" s="62" t="inlineStr">
+    <row r="2" ht="18" customHeight="1" s="24">
+      <c r="A2" s="15" t="inlineStr">
         <is>
           <t>카테고리</t>
         </is>
       </c>
-      <c r="B2" s="62" t="inlineStr">
+      <c r="B2" s="15" t="inlineStr">
         <is>
           <t>키</t>
         </is>
       </c>
-      <c r="C2" s="62" t="inlineStr">
+      <c r="C2" s="15" t="inlineStr">
         <is>
           <t>value</t>
         </is>
       </c>
-      <c r="D2" s="62" t="inlineStr">
+      <c r="D2" s="15" t="inlineStr">
         <is>
           <t>단위</t>
         </is>
       </c>
-      <c r="E2" s="62" t="inlineStr">
+      <c r="E2" s="15" t="inlineStr">
         <is>
           <t>어디에 쓰나</t>
         </is>
       </c>
-      <c r="F2" s="62" t="inlineStr">
+      <c r="F2" s="15" t="inlineStr">
         <is>
           <t>값↑</t>
         </is>
       </c>
-      <c r="G2" s="62" t="inlineStr">
+      <c r="G2" s="15" t="inlineStr">
         <is>
           <t>값↓</t>
         </is>
       </c>
-      <c r="H2" s="62" t="inlineStr">
+      <c r="H2" s="15" t="inlineStr">
         <is>
           <t>코드소스</t>
         </is>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" s="20" t="inlineStr">
+    <row r="3" ht="18" customHeight="1" s="24">
+      <c r="A3" s="1" t="inlineStr">
         <is>
           <t>플레이어</t>
         </is>
       </c>
-      <c r="B3" s="20" t="inlineStr">
+      <c r="B3" s="1" t="inlineStr">
         <is>
           <t>max_level</t>
         </is>
       </c>
-      <c r="C3" s="63" t="n">
+      <c r="C3" s="16" t="n">
         <v>99</v>
       </c>
-      <c r="D3" s="20" t="inlineStr">
+      <c r="D3" s="1" t="inlineStr">
         <is>
           <t>level</t>
         </is>
       </c>
-      <c r="E3" s="20" t="inlineStr">
+      <c r="E3" s="1" t="inlineStr">
         <is>
           <t>플레이어 최대 레벨</t>
         </is>
       </c>
-      <c r="F3" s="20" t="inlineStr">
+      <c r="F3" s="1" t="inlineStr">
         <is>
           <t>성장 길어짐</t>
         </is>
       </c>
-      <c r="G3" s="20" t="inlineStr">
+      <c r="G3" s="1" t="inlineStr">
         <is>
           <t>성장 짧아짐</t>
         </is>
       </c>
-      <c r="H3" s="20" t="inlineStr">
+      <c r="H3" s="1" t="inlineStr">
         <is>
           <t>src/data/constants.ts</t>
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" s="20" t="inlineStr">
+    <row r="4" ht="18" customHeight="1" s="24">
+      <c r="A4" s="1" t="inlineStr">
         <is>
           <t>플레이어</t>
         </is>
       </c>
-      <c r="B4" s="20" t="inlineStr">
+      <c r="B4" s="1" t="inlineStr">
         <is>
           <t>total_exp_to_max</t>
         </is>
       </c>
-      <c r="C4" s="63" t="n">
+      <c r="C4" s="16" t="n">
         <v>43450</v>
       </c>
-      <c r="D4" s="20" t="inlineStr">
+      <c r="D4" s="1" t="inlineStr">
         <is>
           <t>exp</t>
         </is>
       </c>
-      <c r="E4" s="20" t="inlineStr">
+      <c r="E4" s="1" t="inlineStr">
         <is>
           <t>만렙까지 총 EXP</t>
         </is>
       </c>
-      <c r="F4" s="20" t="inlineStr">
+      <c r="F4" s="1" t="inlineStr">
         <is>
           <t>최종 성장 증가</t>
         </is>
       </c>
-      <c r="G4" s="20" t="inlineStr">
+      <c r="G4" s="1" t="inlineStr">
         <is>
           <t>최종 성장 감소</t>
         </is>
       </c>
-      <c r="H4" s="20" t="inlineStr">
+      <c r="H4" s="1" t="inlineStr">
         <is>
           <t>src/data/constants.ts</t>
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" s="20" t="inlineStr">
+    <row r="5" ht="18" customHeight="1" s="24">
+      <c r="A5" s="1" t="inlineStr">
         <is>
           <t>마력</t>
         </is>
       </c>
-      <c r="B5" s="20" t="inlineStr">
+      <c r="B5" s="1" t="inlineStr">
         <is>
           <t>initial_mana</t>
         </is>
       </c>
-      <c r="C5" s="63" t="n">
+      <c r="C5" s="16" t="n">
         <v>5</v>
       </c>
-      <c r="D5" s="20" t="inlineStr">
+      <c r="D5" s="1" t="inlineStr">
         <is>
           <t>point</t>
         </is>
       </c>
-      <c r="E5" s="20" t="inlineStr">
+      <c r="E5" s="1" t="inlineStr">
         <is>
           <t>초기 마나</t>
         </is>
       </c>
-      <c r="F5" s="20" t="inlineStr">
+      <c r="F5" s="1" t="inlineStr">
         <is>
           <t>초반 연속 탐험 증가</t>
         </is>
       </c>
-      <c r="G5" s="20" t="inlineStr">
+      <c r="G5" s="1" t="inlineStr">
         <is>
           <t>초반 연속 탐험 감소</t>
         </is>
       </c>
-      <c r="H5" s="20" t="inlineStr">
+      <c r="H5" s="1" t="inlineStr">
         <is>
           <t>src/data/constants.ts</t>
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" s="20" t="inlineStr">
+    <row r="6" ht="18" customHeight="1" s="24">
+      <c r="A6" s="1" t="inlineStr">
         <is>
           <t>마력</t>
         </is>
       </c>
-      <c r="B6" s="20" t="inlineStr">
+      <c r="B6" s="1" t="inlineStr">
         <is>
           <t>max_mana</t>
         </is>
       </c>
-      <c r="C6" s="63" t="n">
+      <c r="C6" s="16" t="n">
         <v>5</v>
       </c>
-      <c r="D6" s="20" t="inlineStr">
+      <c r="D6" s="1" t="inlineStr">
         <is>
           <t>point</t>
         </is>
       </c>
-      <c r="E6" s="20" t="inlineStr">
+      <c r="E6" s="1" t="inlineStr">
         <is>
           <t>최대 마나</t>
         </is>
       </c>
-      <c r="F6" s="20" t="inlineStr">
+      <c r="F6" s="1" t="inlineStr">
         <is>
           <t>연속 탐험 수 증가</t>
         </is>
       </c>
-      <c r="G6" s="20" t="inlineStr">
+      <c r="G6" s="1" t="inlineStr">
         <is>
           <t>연속 탐험 수 감소</t>
         </is>
       </c>
-      <c r="H6" s="20" t="inlineStr">
+      <c r="H6" s="1" t="inlineStr">
         <is>
           <t>src/data/constants.ts</t>
         </is>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" s="20" t="inlineStr">
+    <row r="7" ht="18" customHeight="1" s="24">
+      <c r="A7" s="1" t="inlineStr">
         <is>
           <t>마력</t>
         </is>
       </c>
-      <c r="B7" s="20" t="inlineStr">
+      <c r="B7" s="1" t="inlineStr">
         <is>
           <t>mana_per_explore</t>
         </is>
       </c>
-      <c r="C7" s="63" t="n">
-        <v>1</v>
-      </c>
-      <c r="D7" s="20" t="inlineStr">
+      <c r="C7" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="D7" s="1" t="inlineStr">
         <is>
           <t>point</t>
         </is>
       </c>
-      <c r="E7" s="20" t="inlineStr">
+      <c r="E7" s="1" t="inlineStr">
         <is>
           <t>탐험 1회 소모 마나</t>
         </is>
       </c>
-      <c r="F7" s="20" t="inlineStr">
+      <c r="F7" s="1" t="inlineStr">
         <is>
           <t>탐험 비용 증가</t>
         </is>
       </c>
-      <c r="G7" s="20" t="inlineStr">
+      <c r="G7" s="1" t="inlineStr">
         <is>
           <t>탐험 비용 감소</t>
         </is>
       </c>
-      <c r="H7" s="20" t="inlineStr">
+      <c r="H7" s="1" t="inlineStr">
         <is>
           <t>src/data/constants.ts</t>
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" s="20" t="inlineStr">
+    <row r="8" ht="18" customHeight="1" s="24">
+      <c r="A8" s="1" t="inlineStr">
         <is>
           <t>마력</t>
         </is>
       </c>
-      <c r="B8" s="20" t="inlineStr">
+      <c r="B8" s="1" t="inlineStr">
         <is>
           <t>mana_regen_minutes</t>
         </is>
       </c>
-      <c r="C8" s="63" t="n">
+      <c r="C8" s="16" t="n">
         <v>20</v>
       </c>
-      <c r="D8" s="20" t="inlineStr">
+      <c r="D8" s="1" t="inlineStr">
         <is>
           <t>minute</t>
         </is>
       </c>
-      <c r="E8" s="20" t="inlineStr">
+      <c r="E8" s="1" t="inlineStr">
         <is>
           <t>마나 회복 간격</t>
         </is>
       </c>
-      <c r="F8" s="20" t="inlineStr">
+      <c r="F8" s="1" t="inlineStr">
         <is>
           <t>회복 느려짐</t>
         </is>
       </c>
-      <c r="G8" s="20" t="inlineStr">
+      <c r="G8" s="1" t="inlineStr">
         <is>
           <t>회복 빨라짐</t>
         </is>
       </c>
-      <c r="H8" s="20" t="inlineStr">
+      <c r="H8" s="1" t="inlineStr">
         <is>
           <t>src/data/constants.ts</t>
         </is>
@@ -2014,513 +1424,511 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:I14"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="17"/>
   <cols>
-    <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="8" customWidth="1" min="2" max="2"/>
-    <col width="8" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
-    <col width="12" customWidth="1" min="6" max="6"/>
-    <col width="22" customWidth="1" min="7" max="7"/>
-    <col width="22" customWidth="1" min="8" max="8"/>
-    <col width="24" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" style="24" min="1" max="1"/>
+    <col width="8" customWidth="1" style="24" min="2" max="3"/>
+    <col width="18" customWidth="1" style="24" min="4" max="4"/>
+    <col width="14" customWidth="1" style="24" min="5" max="5"/>
+    <col width="12" customWidth="1" style="24" min="6" max="6"/>
+    <col width="22" customWidth="1" style="24" min="7" max="8"/>
+    <col width="24" customWidth="1" style="24" min="9" max="9"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="31" t="inlineStr">
+    <row r="1" ht="20" customHeight="1" s="24">
+      <c r="A1" s="26" t="inlineStr">
         <is>
           <t>02_Level - 레벨별 필요/누적 경험치와 컬러</t>
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" s="64" t="inlineStr">
+    <row r="2" ht="18" customHeight="1" s="24">
+      <c r="A2" s="17" t="inlineStr">
         <is>
           <t>구간</t>
         </is>
       </c>
-      <c r="B2" s="64" t="inlineStr">
+      <c r="B2" s="17" t="inlineStr">
         <is>
           <t>from</t>
         </is>
       </c>
-      <c r="C2" s="64" t="inlineStr">
+      <c r="C2" s="17" t="inlineStr">
         <is>
           <t>to</t>
         </is>
       </c>
-      <c r="D2" s="64" t="inlineStr">
+      <c r="D2" s="17" t="inlineStr">
         <is>
           <t>exp_to_next(value)</t>
         </is>
       </c>
-      <c r="E2" s="64" t="inlineStr">
+      <c r="E2" s="17" t="inlineStr">
         <is>
           <t>누적EXP 시작</t>
         </is>
       </c>
-      <c r="F2" s="64" t="inlineStr">
+      <c r="F2" s="17" t="inlineStr">
         <is>
           <t>색상</t>
         </is>
       </c>
-      <c r="G2" s="64" t="inlineStr">
+      <c r="G2" s="17" t="inlineStr">
         <is>
           <t>어디에 쓰나</t>
         </is>
       </c>
-      <c r="H2" s="64" t="inlineStr">
+      <c r="H2" s="17" t="inlineStr">
         <is>
           <t>값↑/값↓</t>
         </is>
       </c>
-      <c r="I2" s="64" t="inlineStr">
+      <c r="I2" s="17" t="inlineStr">
         <is>
           <t>코드소스</t>
         </is>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" s="20" t="inlineStr">
+    <row r="3" ht="36" customHeight="1" s="24">
+      <c r="A3" s="1" t="inlineStr">
         <is>
           <t>Lv1-9</t>
         </is>
       </c>
-      <c r="B3" s="63" t="n">
-        <v>1</v>
-      </c>
-      <c r="C3" s="63" t="n">
+      <c r="B3" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="C3" s="16" t="n">
         <v>9</v>
       </c>
-      <c r="D3" s="63" t="n">
+      <c r="D3" s="16" t="n">
         <v>50</v>
       </c>
-      <c r="E3" s="63" t="n">
+      <c r="E3" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="F3" s="33" t="inlineStr">
+      <c r="F3" s="2" t="inlineStr">
         <is>
           <t>#B8BEC9</t>
         </is>
       </c>
-      <c r="G3" s="20" t="inlineStr">
+      <c r="G3" s="1" t="inlineStr">
         <is>
           <t>레벨업 속도/색상</t>
         </is>
       </c>
-      <c r="H3" s="20" t="inlineStr">
+      <c r="H3" s="1" t="inlineStr">
         <is>
           <t>EXP↑ 난이도↑ / EXP↓ 난이도↓</t>
         </is>
       </c>
-      <c r="I3" s="20" t="inlineStr">
+      <c r="I3" s="1" t="inlineStr">
         <is>
           <t>src/data/levels.ts</t>
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" s="20" t="inlineStr">
+    <row r="4" ht="36" customHeight="1" s="24">
+      <c r="A4" s="1" t="inlineStr">
         <is>
           <t>Lv10-19</t>
         </is>
       </c>
-      <c r="B4" s="63" t="n">
+      <c r="B4" s="16" t="n">
         <v>10</v>
       </c>
-      <c r="C4" s="63" t="n">
+      <c r="C4" s="16" t="n">
         <v>19</v>
       </c>
-      <c r="D4" s="63" t="n">
+      <c r="D4" s="16" t="n">
         <v>80</v>
       </c>
-      <c r="E4" s="63" t="n">
+      <c r="E4" s="16" t="n">
         <v>450</v>
       </c>
-      <c r="F4" s="34" t="inlineStr">
+      <c r="F4" s="3" t="inlineStr">
         <is>
           <t>#79D8C6</t>
         </is>
       </c>
-      <c r="G4" s="20" t="inlineStr">
+      <c r="G4" s="1" t="inlineStr">
         <is>
           <t>레벨업 속도/색상</t>
         </is>
       </c>
-      <c r="H4" s="20" t="inlineStr">
+      <c r="H4" s="1" t="inlineStr">
         <is>
           <t>EXP↑ 난이도↑ / EXP↓ 난이도↓</t>
         </is>
       </c>
-      <c r="I4" s="20" t="inlineStr">
+      <c r="I4" s="1" t="inlineStr">
         <is>
           <t>src/data/levels.ts</t>
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" s="20" t="inlineStr">
+    <row r="5" ht="36" customHeight="1" s="24">
+      <c r="A5" s="1" t="inlineStr">
         <is>
           <t>Lv20-29</t>
         </is>
       </c>
-      <c r="B5" s="63" t="n">
+      <c r="B5" s="16" t="n">
         <v>20</v>
       </c>
-      <c r="C5" s="63" t="n">
+      <c r="C5" s="16" t="n">
         <v>29</v>
       </c>
-      <c r="D5" s="63" t="n">
+      <c r="D5" s="16" t="n">
         <v>120</v>
       </c>
-      <c r="E5" s="63" t="n">
+      <c r="E5" s="16" t="n">
         <v>1250</v>
       </c>
-      <c r="F5" s="35" t="inlineStr">
+      <c r="F5" s="4" t="inlineStr">
         <is>
           <t>#6EBEFF</t>
         </is>
       </c>
-      <c r="G5" s="20" t="inlineStr">
+      <c r="G5" s="1" t="inlineStr">
         <is>
           <t>레벨업 속도/색상</t>
         </is>
       </c>
-      <c r="H5" s="20" t="inlineStr">
+      <c r="H5" s="1" t="inlineStr">
         <is>
           <t>EXP↑ 난이도↑ / EXP↓ 난이도↓</t>
         </is>
       </c>
-      <c r="I5" s="20" t="inlineStr">
+      <c r="I5" s="1" t="inlineStr">
         <is>
           <t>src/data/levels.ts</t>
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" s="20" t="inlineStr">
+    <row r="6" ht="36" customHeight="1" s="24">
+      <c r="A6" s="1" t="inlineStr">
         <is>
           <t>Lv30-39</t>
         </is>
       </c>
-      <c r="B6" s="63" t="n">
+      <c r="B6" s="16" t="n">
         <v>30</v>
       </c>
-      <c r="C6" s="63" t="n">
+      <c r="C6" s="16" t="n">
         <v>39</v>
       </c>
-      <c r="D6" s="63" t="n">
+      <c r="D6" s="16" t="n">
         <v>180</v>
       </c>
-      <c r="E6" s="63" t="n">
+      <c r="E6" s="16" t="n">
         <v>2450</v>
       </c>
-      <c r="F6" s="36" t="inlineStr">
+      <c r="F6" s="5" t="inlineStr">
         <is>
           <t>#8ED46B</t>
         </is>
       </c>
-      <c r="G6" s="20" t="inlineStr">
+      <c r="G6" s="1" t="inlineStr">
         <is>
           <t>레벨업 속도/색상</t>
         </is>
       </c>
-      <c r="H6" s="20" t="inlineStr">
+      <c r="H6" s="1" t="inlineStr">
         <is>
           <t>EXP↑ 난이도↑ / EXP↓ 난이도↓</t>
         </is>
       </c>
-      <c r="I6" s="20" t="inlineStr">
+      <c r="I6" s="1" t="inlineStr">
         <is>
           <t>src/data/levels.ts</t>
         </is>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" s="20" t="inlineStr">
+    <row r="7" ht="36" customHeight="1" s="24">
+      <c r="A7" s="1" t="inlineStr">
         <is>
           <t>Lv40-49</t>
         </is>
       </c>
-      <c r="B7" s="63" t="n">
+      <c r="B7" s="16" t="n">
         <v>40</v>
       </c>
-      <c r="C7" s="63" t="n">
+      <c r="C7" s="16" t="n">
         <v>49</v>
       </c>
-      <c r="D7" s="63" t="n">
+      <c r="D7" s="16" t="n">
         <v>250</v>
       </c>
-      <c r="E7" s="63" t="n">
+      <c r="E7" s="16" t="n">
         <v>4250</v>
       </c>
-      <c r="F7" s="37" t="inlineStr">
+      <c r="F7" s="6" t="inlineStr">
         <is>
           <t>#E5C46B</t>
         </is>
       </c>
-      <c r="G7" s="20" t="inlineStr">
+      <c r="G7" s="1" t="inlineStr">
         <is>
           <t>레벨업 속도/색상</t>
         </is>
       </c>
-      <c r="H7" s="20" t="inlineStr">
+      <c r="H7" s="1" t="inlineStr">
         <is>
           <t>EXP↑ 난이도↑ / EXP↓ 난이도↓</t>
         </is>
       </c>
-      <c r="I7" s="20" t="inlineStr">
+      <c r="I7" s="1" t="inlineStr">
         <is>
           <t>src/data/levels.ts</t>
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" s="20" t="inlineStr">
+    <row r="8" ht="36" customHeight="1" s="24">
+      <c r="A8" s="1" t="inlineStr">
         <is>
           <t>Lv50-59</t>
         </is>
       </c>
-      <c r="B8" s="63" t="n">
+      <c r="B8" s="16" t="n">
         <v>50</v>
       </c>
-      <c r="C8" s="63" t="n">
+      <c r="C8" s="16" t="n">
         <v>59</v>
       </c>
-      <c r="D8" s="63" t="n">
+      <c r="D8" s="16" t="n">
         <v>350</v>
       </c>
-      <c r="E8" s="63" t="n">
+      <c r="E8" s="16" t="n">
         <v>6750</v>
       </c>
-      <c r="F8" s="38" t="inlineStr">
+      <c r="F8" s="7" t="inlineStr">
         <is>
           <t>#A894FF</t>
         </is>
       </c>
-      <c r="G8" s="20" t="inlineStr">
+      <c r="G8" s="1" t="inlineStr">
         <is>
           <t>레벨업 속도/색상</t>
         </is>
       </c>
-      <c r="H8" s="20" t="inlineStr">
+      <c r="H8" s="1" t="inlineStr">
         <is>
           <t>EXP↑ 난이도↑ / EXP↓ 난이도↓</t>
         </is>
       </c>
-      <c r="I8" s="20" t="inlineStr">
+      <c r="I8" s="1" t="inlineStr">
         <is>
           <t>src/data/levels.ts</t>
         </is>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" s="20" t="inlineStr">
+    <row r="9" ht="36" customHeight="1" s="24">
+      <c r="A9" s="1" t="inlineStr">
         <is>
           <t>Lv60-69</t>
         </is>
       </c>
-      <c r="B9" s="63" t="n">
+      <c r="B9" s="16" t="n">
         <v>60</v>
       </c>
-      <c r="C9" s="63" t="n">
+      <c r="C9" s="16" t="n">
         <v>69</v>
       </c>
-      <c r="D9" s="63" t="n">
+      <c r="D9" s="16" t="n">
         <v>500</v>
       </c>
-      <c r="E9" s="63" t="n">
+      <c r="E9" s="16" t="n">
         <v>10250</v>
       </c>
-      <c r="F9" s="39" t="inlineStr">
+      <c r="F9" s="8" t="inlineStr">
         <is>
           <t>#866BFF</t>
         </is>
       </c>
-      <c r="G9" s="20" t="inlineStr">
+      <c r="G9" s="1" t="inlineStr">
         <is>
           <t>레벨업 속도/색상</t>
         </is>
       </c>
-      <c r="H9" s="20" t="inlineStr">
+      <c r="H9" s="1" t="inlineStr">
         <is>
           <t>EXP↑ 난이도↑ / EXP↓ 난이도↓</t>
         </is>
       </c>
-      <c r="I9" s="20" t="inlineStr">
+      <c r="I9" s="1" t="inlineStr">
         <is>
           <t>src/data/levels.ts</t>
         </is>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" s="20" t="inlineStr">
+    <row r="10" ht="36" customHeight="1" s="24">
+      <c r="A10" s="1" t="inlineStr">
         <is>
           <t>Lv70-79</t>
         </is>
       </c>
-      <c r="B10" s="63" t="n">
+      <c r="B10" s="16" t="n">
         <v>70</v>
       </c>
-      <c r="C10" s="63" t="n">
+      <c r="C10" s="16" t="n">
         <v>79</v>
       </c>
-      <c r="D10" s="63" t="n">
+      <c r="D10" s="16" t="n">
         <v>700</v>
       </c>
-      <c r="E10" s="63" t="n">
+      <c r="E10" s="16" t="n">
         <v>15250</v>
       </c>
-      <c r="F10" s="40" t="inlineStr">
+      <c r="F10" s="9" t="inlineStr">
         <is>
           <t>#6A46E8</t>
         </is>
       </c>
-      <c r="G10" s="20" t="inlineStr">
+      <c r="G10" s="1" t="inlineStr">
         <is>
           <t>레벨업 속도/색상</t>
         </is>
       </c>
-      <c r="H10" s="20" t="inlineStr">
+      <c r="H10" s="1" t="inlineStr">
         <is>
           <t>EXP↑ 난이도↑ / EXP↓ 난이도↓</t>
         </is>
       </c>
-      <c r="I10" s="20" t="inlineStr">
+      <c r="I10" s="1" t="inlineStr">
         <is>
           <t>src/data/levels.ts</t>
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" s="20" t="inlineStr">
+    <row r="11" ht="36" customHeight="1" s="24">
+      <c r="A11" s="1" t="inlineStr">
         <is>
           <t>Lv80-89</t>
         </is>
       </c>
-      <c r="B11" s="63" t="n">
+      <c r="B11" s="16" t="n">
         <v>80</v>
       </c>
-      <c r="C11" s="63" t="n">
+      <c r="C11" s="16" t="n">
         <v>89</v>
       </c>
-      <c r="D11" s="63" t="n">
+      <c r="D11" s="16" t="n">
         <v>950</v>
       </c>
-      <c r="E11" s="63" t="n">
+      <c r="E11" s="16" t="n">
         <v>22250</v>
       </c>
-      <c r="F11" s="41" t="inlineStr">
+      <c r="F11" s="10" t="inlineStr">
         <is>
           <t>#4E5EEA</t>
         </is>
       </c>
-      <c r="G11" s="20" t="inlineStr">
+      <c r="G11" s="1" t="inlineStr">
         <is>
           <t>레벨업 속도/색상</t>
         </is>
       </c>
-      <c r="H11" s="20" t="inlineStr">
+      <c r="H11" s="1" t="inlineStr">
         <is>
           <t>EXP↑ 난이도↑ / EXP↓ 난이도↓</t>
         </is>
       </c>
-      <c r="I11" s="20" t="inlineStr">
+      <c r="I11" s="1" t="inlineStr">
         <is>
           <t>src/data/levels.ts</t>
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" s="20" t="inlineStr">
+    <row r="12" ht="36" customHeight="1" s="24">
+      <c r="A12" s="1" t="inlineStr">
         <is>
           <t>Lv90-98</t>
         </is>
       </c>
-      <c r="B12" s="63" t="n">
+      <c r="B12" s="16" t="n">
         <v>90</v>
       </c>
-      <c r="C12" s="63" t="n">
+      <c r="C12" s="16" t="n">
         <v>98</v>
       </c>
-      <c r="D12" s="63" t="n">
+      <c r="D12" s="16" t="n">
         <v>1300</v>
       </c>
-      <c r="E12" s="63" t="n">
+      <c r="E12" s="16" t="n">
         <v>31750</v>
       </c>
-      <c r="F12" s="42" t="inlineStr">
+      <c r="F12" s="11" t="inlineStr">
         <is>
           <t>#F6E7A8</t>
         </is>
       </c>
-      <c r="G12" s="20" t="inlineStr">
+      <c r="G12" s="1" t="inlineStr">
         <is>
           <t>레벨업 속도/색상</t>
         </is>
       </c>
-      <c r="H12" s="20" t="inlineStr">
+      <c r="H12" s="1" t="inlineStr">
         <is>
           <t>EXP↑ 난이도↑ / EXP↓ 난이도↓</t>
         </is>
       </c>
-      <c r="I12" s="20" t="inlineStr">
+      <c r="I12" s="1" t="inlineStr">
         <is>
           <t>src/data/levels.ts</t>
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="20" t="inlineStr">
+    <row r="13" ht="36" customHeight="1" s="24">
+      <c r="A13" s="1" t="inlineStr">
         <is>
           <t>Lv99-99</t>
         </is>
       </c>
-      <c r="B13" s="63" t="n">
+      <c r="B13" s="16" t="n">
         <v>99</v>
       </c>
-      <c r="C13" s="63" t="n">
+      <c r="C13" s="16" t="n">
         <v>99</v>
       </c>
-      <c r="D13" s="63" t="n">
+      <c r="D13" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="E13" s="63" t="n">
+      <c r="E13" s="16" t="n">
         <v>43450</v>
       </c>
-      <c r="F13" s="42" t="inlineStr">
+      <c r="F13" s="11" t="inlineStr">
         <is>
           <t>#F6E7A8</t>
         </is>
       </c>
-      <c r="G13" s="20" t="inlineStr">
+      <c r="G13" s="1" t="inlineStr">
         <is>
           <t>레벨업 속도/색상</t>
         </is>
       </c>
-      <c r="H13" s="20" t="inlineStr">
+      <c r="H13" s="1" t="inlineStr">
         <is>
           <t>EXP↑ 난이도↑ / EXP↓ 난이도↓</t>
         </is>
       </c>
-      <c r="I13" s="20" t="inlineStr">
+      <c r="I13" s="1" t="inlineStr">
         <is>
           <t>src/data/levels.ts</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="43" t="inlineStr">
+      <c r="A14" s="12" t="inlineStr">
         <is>
           <t>check_total_exp</t>
         </is>
       </c>
-      <c r="B14" s="43">
+      <c r="B14" s="12">
         <f>SUMPRODUCT((C3:C12-B3:B12+1),D3:D12)</f>
         <v/>
       </c>
-      <c r="C14" s="44" t="inlineStr">
+      <c r="C14" s="13" t="inlineStr">
         <is>
           <t>기준 43450</t>
         </is>
@@ -2541,462 +1949,461 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:H101"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="17"/>
   <cols>
-    <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="28" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="10" customWidth="1" min="4" max="4"/>
-    <col width="24" customWidth="1" min="5" max="5"/>
-    <col width="16" customWidth="1" min="6" max="6"/>
-    <col width="16" customWidth="1" min="7" max="7"/>
-    <col width="26" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" style="24" min="1" max="1"/>
+    <col width="28" customWidth="1" style="24" min="2" max="2"/>
+    <col width="12" customWidth="1" style="24" min="3" max="3"/>
+    <col width="10" customWidth="1" style="24" min="4" max="4"/>
+    <col width="24" customWidth="1" style="24" min="5" max="5"/>
+    <col width="16" customWidth="1" style="24" min="6" max="7"/>
+    <col width="26" customWidth="1" style="24" min="8" max="8"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="45" t="inlineStr">
+    <row r="1" ht="20" customHeight="1" s="24">
+      <c r="A1" s="27" t="inlineStr">
         <is>
           <t>03_Exploration - 탐사 지역별 비용·보상</t>
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" s="65" t="inlineStr">
+    <row r="2" ht="18" customHeight="1" s="24">
+      <c r="A2" s="18" t="inlineStr">
         <is>
           <t>카테고리</t>
         </is>
       </c>
-      <c r="B2" s="65" t="inlineStr">
+      <c r="B2" s="18" t="inlineStr">
         <is>
           <t>키</t>
         </is>
       </c>
-      <c r="C2" s="65" t="inlineStr">
+      <c r="C2" s="18" t="inlineStr">
         <is>
           <t>value</t>
         </is>
       </c>
-      <c r="D2" s="65" t="inlineStr">
+      <c r="D2" s="18" t="inlineStr">
         <is>
           <t>단위</t>
         </is>
       </c>
-      <c r="E2" s="65" t="inlineStr">
+      <c r="E2" s="18" t="inlineStr">
         <is>
           <t>어디에 쓰나</t>
         </is>
       </c>
-      <c r="F2" s="65" t="inlineStr">
+      <c r="F2" s="18" t="inlineStr">
         <is>
           <t>값↑</t>
         </is>
       </c>
-      <c r="G2" s="65" t="inlineStr">
+      <c r="G2" s="18" t="inlineStr">
         <is>
           <t>값↓</t>
         </is>
       </c>
-      <c r="H2" s="65" t="inlineStr">
+      <c r="H2" s="18" t="inlineStr">
         <is>
           <t>코드소스</t>
         </is>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" s="20" t="inlineStr">
+    <row r="3" ht="18" customHeight="1" s="24">
+      <c r="A3" s="1" t="inlineStr">
         <is>
           <t>공통</t>
         </is>
       </c>
-      <c r="B3" s="20" t="inlineStr">
+      <c r="B3" s="1" t="inlineStr">
         <is>
           <t>explore_steps</t>
         </is>
       </c>
-      <c r="C3" s="63" t="n">
+      <c r="C3" s="16" t="n">
         <v>10</v>
       </c>
-      <c r="D3" s="20" t="inlineStr">
+      <c r="D3" s="1" t="inlineStr">
         <is>
           <t>count</t>
         </is>
       </c>
-      <c r="E3" s="20" t="inlineStr">
+      <c r="E3" s="1" t="inlineStr">
         <is>
           <t>탐사 1회 행동 횟수</t>
         </is>
       </c>
-      <c r="F3" s="20" t="inlineStr">
+      <c r="F3" s="1" t="inlineStr">
         <is>
           <t>한 판 길어짐</t>
         </is>
       </c>
-      <c r="G3" s="20" t="inlineStr">
+      <c r="G3" s="1" t="inlineStr">
         <is>
           <t>한 판 짧아짐</t>
         </is>
       </c>
-      <c r="H3" s="20" t="inlineStr">
-        <is>
-          <t>src/data/regions.ts</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="20" t="inlineStr">
+      <c r="H3" s="1" t="inlineStr">
+        <is>
+          <t>src/data/regions.ts</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="18" customHeight="1" s="24">
+      <c r="A4" s="1" t="inlineStr">
         <is>
           <t>공통</t>
         </is>
       </c>
-      <c r="B4" s="20" t="inlineStr">
+      <c r="B4" s="1" t="inlineStr">
         <is>
           <t>result_reveal_delay_ms</t>
         </is>
       </c>
-      <c r="C4" s="63" t="n">
+      <c r="C4" s="16" t="n">
         <v>700</v>
       </c>
-      <c r="D4" s="20" t="inlineStr">
+      <c r="D4" s="1" t="inlineStr">
         <is>
           <t>ms</t>
         </is>
       </c>
-      <c r="E4" s="20" t="inlineStr">
+      <c r="E4" s="1" t="inlineStr">
         <is>
           <t>결과창 노출 지연</t>
         </is>
       </c>
-      <c r="F4" s="20" t="inlineStr">
+      <c r="F4" s="1" t="inlineStr">
         <is>
           <t>느려짐</t>
         </is>
       </c>
-      <c r="G4" s="20" t="inlineStr">
+      <c r="G4" s="1" t="inlineStr">
         <is>
           <t>빨라짐</t>
         </is>
       </c>
-      <c r="H4" s="20" t="inlineStr">
+      <c r="H4" s="1" t="inlineStr">
         <is>
           <t>src/data/drops.ts</t>
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" s="20" t="inlineStr">
+    <row r="5" ht="18" customHeight="1" s="24">
+      <c r="A5" s="1" t="inlineStr">
         <is>
           <t>공통</t>
         </is>
       </c>
-      <c r="B5" s="20" t="inlineStr">
+      <c r="B5" s="1" t="inlineStr">
         <is>
           <t>mana_cost</t>
         </is>
       </c>
-      <c r="C5" s="63" t="n">
-        <v>1</v>
-      </c>
-      <c r="D5" s="20" t="inlineStr">
+      <c r="C5" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="D5" s="1" t="inlineStr">
         <is>
           <t>mana</t>
         </is>
       </c>
-      <c r="E5" s="20" t="inlineStr">
+      <c r="E5" s="1" t="inlineStr">
         <is>
           <t>탐사 1회 입장 소모 마나</t>
         </is>
       </c>
-      <c r="F5" s="20" t="inlineStr">
+      <c r="F5" s="1" t="inlineStr">
         <is>
           <t>비용 증가</t>
         </is>
       </c>
-      <c r="G5" s="20" t="inlineStr">
+      <c r="G5" s="1" t="inlineStr">
         <is>
           <t>비용 감소</t>
         </is>
       </c>
-      <c r="H5" s="20" t="inlineStr">
-        <is>
-          <t>src/data/regions.ts</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="20" t="inlineStr">
+      <c r="H5" s="1" t="inlineStr">
+        <is>
+          <t>src/data/regions.ts</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="18" customHeight="1" s="24">
+      <c r="A6" s="1" t="inlineStr">
         <is>
           <t>공통</t>
         </is>
       </c>
-      <c r="B6" s="20" t="inlineStr">
+      <c r="B6" s="1" t="inlineStr">
         <is>
           <t>hidden_stage_required_amount</t>
         </is>
       </c>
-      <c r="C6" s="63" t="n">
+      <c r="C6" s="16" t="n">
         <v>20</v>
       </c>
-      <c r="D6" s="20" t="inlineStr">
+      <c r="D6" s="1" t="inlineStr">
         <is>
           <t>count</t>
         </is>
       </c>
-      <c r="E6" s="20" t="inlineStr">
+      <c r="E6" s="1" t="inlineStr">
         <is>
           <t>히든 스테이지 입장 흔적 수</t>
         </is>
       </c>
-      <c r="F6" s="20" t="inlineStr">
+      <c r="F6" s="1" t="inlineStr">
         <is>
           <t>진입 어렵게</t>
         </is>
       </c>
-      <c r="G6" s="20" t="inlineStr">
+      <c r="G6" s="1" t="inlineStr">
         <is>
           <t>진입 쉽게</t>
         </is>
       </c>
-      <c r="H6" s="20" t="inlineStr">
-        <is>
-          <t>src/data/regions.ts</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="20" t="inlineStr">
+      <c r="H6" s="1" t="inlineStr">
+        <is>
+          <t>src/data/regions.ts</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="18" customHeight="1" s="24">
+      <c r="A7" s="1" t="inlineStr">
         <is>
           <t>공통</t>
         </is>
       </c>
-      <c r="B7" s="20" t="inlineStr">
+      <c r="B7" s="1" t="inlineStr">
         <is>
           <t>event_material</t>
         </is>
       </c>
-      <c r="C7" s="63" t="n">
+      <c r="C7" s="16" t="n">
         <v>0.48</v>
       </c>
-      <c r="D7" s="20" t="inlineStr">
+      <c r="D7" s="1" t="inlineStr">
         <is>
           <t>ratio</t>
         </is>
       </c>
-      <c r="E7" s="20" t="inlineStr">
+      <c r="E7" s="1" t="inlineStr">
         <is>
           <t>재료 이벤트 확률</t>
         </is>
       </c>
-      <c r="F7" s="20" t="inlineStr">
+      <c r="F7" s="1" t="inlineStr">
         <is>
           <t>재료 많아짐</t>
         </is>
       </c>
-      <c r="G7" s="20" t="inlineStr">
+      <c r="G7" s="1" t="inlineStr">
         <is>
           <t>재료 적어짐</t>
         </is>
       </c>
-      <c r="H7" s="20" t="inlineStr">
+      <c r="H7" s="1" t="inlineStr">
         <is>
           <t>src/data/drops.ts</t>
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" s="20" t="inlineStr">
+    <row r="8" ht="18" customHeight="1" s="24">
+      <c r="A8" s="1" t="inlineStr">
         <is>
           <t>공통</t>
         </is>
       </c>
-      <c r="B8" s="20" t="inlineStr">
+      <c r="B8" s="1" t="inlineStr">
         <is>
           <t>event_spirit</t>
         </is>
       </c>
-      <c r="C8" s="63" t="n">
+      <c r="C8" s="16" t="n">
         <v>0.18</v>
       </c>
-      <c r="D8" s="20" t="inlineStr">
+      <c r="D8" s="1" t="inlineStr">
         <is>
           <t>ratio</t>
         </is>
       </c>
-      <c r="E8" s="20" t="inlineStr">
+      <c r="E8" s="1" t="inlineStr">
         <is>
           <t>정령 이벤트 확률</t>
         </is>
       </c>
-      <c r="F8" s="20" t="inlineStr">
+      <c r="F8" s="1" t="inlineStr">
         <is>
           <t>정령 많아짐</t>
         </is>
       </c>
-      <c r="G8" s="20" t="inlineStr">
+      <c r="G8" s="1" t="inlineStr">
         <is>
           <t>정령 적어짐</t>
         </is>
       </c>
-      <c r="H8" s="20" t="inlineStr">
+      <c r="H8" s="1" t="inlineStr">
         <is>
           <t>src/data/drops.ts</t>
         </is>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" s="20" t="inlineStr">
+    <row r="9" ht="36" customHeight="1" s="24">
+      <c r="A9" s="1" t="inlineStr">
         <is>
           <t>공통</t>
         </is>
       </c>
-      <c r="B9" s="20" t="inlineStr">
+      <c r="B9" s="1" t="inlineStr">
         <is>
           <t>event_regional</t>
         </is>
       </c>
-      <c r="C9" s="63" t="n">
+      <c r="C9" s="16" t="n">
         <v>0.14</v>
       </c>
-      <c r="D9" s="20" t="inlineStr">
+      <c r="D9" s="1" t="inlineStr">
         <is>
           <t>ratio</t>
         </is>
       </c>
-      <c r="E9" s="20" t="inlineStr">
+      <c r="E9" s="1" t="inlineStr">
         <is>
           <t>지역 이벤트 확률</t>
         </is>
       </c>
-      <c r="F9" s="20" t="inlineStr">
+      <c r="F9" s="1" t="inlineStr">
         <is>
           <t>지역 이벤트 많아짐</t>
         </is>
       </c>
-      <c r="G9" s="20" t="inlineStr">
+      <c r="G9" s="1" t="inlineStr">
         <is>
           <t>지역 이벤트 적어짐</t>
         </is>
       </c>
-      <c r="H9" s="20" t="inlineStr">
+      <c r="H9" s="1" t="inlineStr">
         <is>
           <t>src/data/drops.ts</t>
         </is>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" s="20" t="inlineStr">
+    <row r="10" ht="18" customHeight="1" s="24">
+      <c r="A10" s="1" t="inlineStr">
         <is>
           <t>공통</t>
         </is>
       </c>
-      <c r="B10" s="20" t="inlineStr">
+      <c r="B10" s="1" t="inlineStr">
         <is>
           <t>event_treasure</t>
         </is>
       </c>
-      <c r="C10" s="63" t="n">
+      <c r="C10" s="16" t="n">
         <v>0.1</v>
       </c>
-      <c r="D10" s="20" t="inlineStr">
+      <c r="D10" s="1" t="inlineStr">
         <is>
           <t>ratio</t>
         </is>
       </c>
-      <c r="E10" s="20" t="inlineStr">
+      <c r="E10" s="1" t="inlineStr">
         <is>
           <t>보물 이벤트 확률</t>
         </is>
       </c>
-      <c r="F10" s="20" t="inlineStr">
+      <c r="F10" s="1" t="inlineStr">
         <is>
           <t>보물 많아짐</t>
         </is>
       </c>
-      <c r="G10" s="20" t="inlineStr">
+      <c r="G10" s="1" t="inlineStr">
         <is>
           <t>보물 적어짐</t>
         </is>
       </c>
-      <c r="H10" s="20" t="inlineStr">
+      <c r="H10" s="1" t="inlineStr">
         <is>
           <t>src/data/drops.ts</t>
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" s="20" t="inlineStr">
+    <row r="11" ht="18" customHeight="1" s="24">
+      <c r="A11" s="1" t="inlineStr">
         <is>
           <t>공통</t>
         </is>
       </c>
-      <c r="B11" s="20" t="inlineStr">
+      <c r="B11" s="1" t="inlineStr">
         <is>
           <t>event_trace</t>
         </is>
       </c>
-      <c r="C11" s="63" t="n">
+      <c r="C11" s="16" t="n">
         <v>0.04</v>
       </c>
-      <c r="D11" s="20" t="inlineStr">
+      <c r="D11" s="1" t="inlineStr">
         <is>
           <t>ratio</t>
         </is>
       </c>
-      <c r="E11" s="20" t="inlineStr">
+      <c r="E11" s="1" t="inlineStr">
         <is>
           <t>흔적 이벤트 확률</t>
         </is>
       </c>
-      <c r="F11" s="20" t="inlineStr">
+      <c r="F11" s="1" t="inlineStr">
         <is>
           <t>흔적 많아짐</t>
         </is>
       </c>
-      <c r="G11" s="20" t="inlineStr">
+      <c r="G11" s="1" t="inlineStr">
         <is>
           <t>흔적 적어짐</t>
         </is>
       </c>
-      <c r="H11" s="20" t="inlineStr">
+      <c r="H11" s="1" t="inlineStr">
         <is>
           <t>src/data/drops.ts</t>
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" s="20" t="inlineStr">
+    <row r="12" ht="18" customHeight="1" s="24">
+      <c r="A12" s="1" t="inlineStr">
         <is>
           <t>공통</t>
         </is>
       </c>
-      <c r="B12" s="20" t="inlineStr">
+      <c r="B12" s="1" t="inlineStr">
         <is>
           <t>event_none</t>
         </is>
       </c>
-      <c r="C12" s="63" t="n">
+      <c r="C12" s="16" t="n">
         <v>0.08</v>
       </c>
-      <c r="D12" s="20" t="inlineStr">
+      <c r="D12" s="1" t="inlineStr">
         <is>
           <t>ratio</t>
         </is>
       </c>
-      <c r="E12" s="20" t="inlineStr">
+      <c r="E12" s="1" t="inlineStr">
         <is>
           <t>아무것도 없음 확률</t>
         </is>
       </c>
-      <c r="F12" s="20" t="inlineStr">
+      <c r="F12" s="1" t="inlineStr">
         <is>
           <t>빈 이벤트 많아짐</t>
         </is>
       </c>
-      <c r="G12" s="20" t="inlineStr">
+      <c r="G12" s="1" t="inlineStr">
         <is>
           <t>빈 이벤트 적어짐</t>
         </is>
       </c>
-      <c r="H12" s="20" t="inlineStr">
+      <c r="H12" s="1" t="inlineStr">
         <is>
           <t>src/data/drops.ts</t>
         </is>
@@ -3042,485 +2449,485 @@
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="20" t="inlineStr">
+    <row r="14" ht="36" customHeight="1" s="24">
+      <c r="A14" s="1" t="inlineStr">
         <is>
           <t>Map1</t>
         </is>
       </c>
-      <c r="B14" s="20" t="inlineStr">
+      <c r="B14" s="1" t="inlineStr">
         <is>
           <t>region_id</t>
         </is>
       </c>
-      <c r="C14" s="63" t="inlineStr">
+      <c r="C14" s="16" t="inlineStr">
         <is>
           <t>starlight_forest</t>
         </is>
       </c>
-      <c r="D14" s="20" t="inlineStr">
+      <c r="D14" s="1" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="E14" s="20" t="inlineStr">
+      <c r="E14" s="1" t="inlineStr">
         <is>
           <t>현재 적용 지역 ID</t>
         </is>
       </c>
-      <c r="F14" s="20" t="inlineStr">
+      <c r="F14" s="1" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="G14" s="20" t="inlineStr">
+      <c r="G14" s="1" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="H14" s="20" t="inlineStr">
-        <is>
-          <t>src/data/regions.ts</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="20" t="inlineStr">
+      <c r="H14" s="1" t="inlineStr">
+        <is>
+          <t>src/data/regions.ts</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="18" customHeight="1" s="24">
+      <c r="A15" s="1" t="inlineStr">
         <is>
           <t>Map1</t>
         </is>
       </c>
-      <c r="B15" s="20" t="inlineStr">
+      <c r="B15" s="1" t="inlineStr">
         <is>
           <t>region_name</t>
         </is>
       </c>
-      <c r="C15" s="63" t="inlineStr">
+      <c r="C15" s="16" t="inlineStr">
         <is>
           <t>별빛 숲속</t>
         </is>
       </c>
-      <c r="D15" s="20" t="inlineStr">
+      <c r="D15" s="1" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="E15" s="20" t="inlineStr">
+      <c r="E15" s="1" t="inlineStr">
         <is>
           <t>현재 적용 지역명</t>
         </is>
       </c>
-      <c r="F15" s="20" t="inlineStr">
+      <c r="F15" s="1" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="G15" s="20" t="inlineStr">
+      <c r="G15" s="1" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="H15" s="20" t="inlineStr">
-        <is>
-          <t>src/data/regions.ts</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="20" t="inlineStr">
+      <c r="H15" s="1" t="inlineStr">
+        <is>
+          <t>src/data/regions.ts</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="18" customHeight="1" s="24">
+      <c r="A16" s="1" t="inlineStr">
         <is>
           <t>Map1</t>
         </is>
       </c>
-      <c r="B16" s="20" t="inlineStr">
+      <c r="B16" s="1" t="inlineStr">
         <is>
           <t>unlock_level</t>
         </is>
       </c>
-      <c r="C16" s="63" t="n">
-        <v>1</v>
-      </c>
-      <c r="D16" s="20" t="inlineStr">
+      <c r="C16" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="D16" s="1" t="inlineStr">
         <is>
           <t>level</t>
         </is>
       </c>
-      <c r="E16" s="20" t="inlineStr">
+      <c r="E16" s="1" t="inlineStr">
         <is>
           <t>입장 레벨</t>
         </is>
       </c>
-      <c r="F16" s="20" t="inlineStr">
+      <c r="F16" s="1" t="inlineStr">
         <is>
           <t>해금 지연</t>
         </is>
       </c>
-      <c r="G16" s="20" t="inlineStr">
+      <c r="G16" s="1" t="inlineStr">
         <is>
           <t>해금 빨라짐</t>
         </is>
       </c>
-      <c r="H16" s="20" t="inlineStr">
-        <is>
-          <t>src/data/regions.ts</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="20" t="inlineStr">
+      <c r="H16" s="1" t="inlineStr">
+        <is>
+          <t>src/data/regions.ts</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="18" customHeight="1" s="24">
+      <c r="A17" s="1" t="inlineStr">
         <is>
           <t>Map1</t>
         </is>
       </c>
-      <c r="B17" s="20" t="inlineStr">
+      <c r="B17" s="1" t="inlineStr">
         <is>
           <t>recommended_level</t>
         </is>
       </c>
-      <c r="C17" s="63" t="n">
-        <v>1</v>
-      </c>
-      <c r="D17" s="20" t="inlineStr">
+      <c r="C17" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="D17" s="1" t="inlineStr">
         <is>
           <t>level</t>
         </is>
       </c>
-      <c r="E17" s="20" t="inlineStr">
+      <c r="E17" s="1" t="inlineStr">
         <is>
           <t>권장 레벨</t>
         </is>
       </c>
-      <c r="F17" s="20" t="inlineStr">
+      <c r="F17" s="1" t="inlineStr">
         <is>
           <t>권장치 상승</t>
         </is>
       </c>
-      <c r="G17" s="20" t="inlineStr">
+      <c r="G17" s="1" t="inlineStr">
         <is>
           <t>권장치 하락</t>
         </is>
       </c>
-      <c r="H17" s="20" t="inlineStr">
-        <is>
-          <t>src/data/regions.ts</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="20" t="inlineStr">
+      <c r="H17" s="1" t="inlineStr">
+        <is>
+          <t>src/data/regions.ts</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="36" customHeight="1" s="24">
+      <c r="A18" s="1" t="inlineStr">
         <is>
           <t>Map1</t>
         </is>
       </c>
-      <c r="B18" s="20" t="inlineStr">
+      <c r="B18" s="1" t="inlineStr">
         <is>
           <t>weight_material</t>
         </is>
       </c>
-      <c r="C18" s="63" t="n">
+      <c r="C18" s="16" t="n">
         <v>30</v>
       </c>
-      <c r="D18" s="20" t="inlineStr">
+      <c r="D18" s="1" t="inlineStr">
         <is>
           <t>weight</t>
         </is>
       </c>
-      <c r="E18" s="20" t="inlineStr">
+      <c r="E18" s="1" t="inlineStr">
         <is>
           <t>탐색률 재료 기여</t>
         </is>
       </c>
-      <c r="F18" s="20" t="inlineStr">
+      <c r="F18" s="1" t="inlineStr">
         <is>
           <t>탐색률 해당 항목 비중↑</t>
         </is>
       </c>
-      <c r="G18" s="20" t="inlineStr">
+      <c r="G18" s="1" t="inlineStr">
         <is>
           <t>비중↓</t>
         </is>
       </c>
-      <c r="H18" s="20" t="inlineStr">
-        <is>
-          <t>src/data/regions.ts</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="20" t="inlineStr">
+      <c r="H18" s="1" t="inlineStr">
+        <is>
+          <t>src/data/regions.ts</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="36" customHeight="1" s="24">
+      <c r="A19" s="1" t="inlineStr">
         <is>
           <t>Map1</t>
         </is>
       </c>
-      <c r="B19" s="20" t="inlineStr">
+      <c r="B19" s="1" t="inlineStr">
         <is>
           <t>weight_spirit</t>
         </is>
       </c>
-      <c r="C19" s="63" t="n">
+      <c r="C19" s="16" t="n">
         <v>30</v>
       </c>
-      <c r="D19" s="20" t="inlineStr">
+      <c r="D19" s="1" t="inlineStr">
         <is>
           <t>weight</t>
         </is>
       </c>
-      <c r="E19" s="20" t="inlineStr">
+      <c r="E19" s="1" t="inlineStr">
         <is>
           <t>탐색률 정령 기여</t>
         </is>
       </c>
-      <c r="F19" s="20" t="inlineStr">
+      <c r="F19" s="1" t="inlineStr">
         <is>
           <t>탐색률 해당 항목 비중↑</t>
         </is>
       </c>
-      <c r="G19" s="20" t="inlineStr">
+      <c r="G19" s="1" t="inlineStr">
         <is>
           <t>비중↓</t>
         </is>
       </c>
-      <c r="H19" s="20" t="inlineStr">
-        <is>
-          <t>src/data/regions.ts</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="20" t="inlineStr">
+      <c r="H19" s="1" t="inlineStr">
+        <is>
+          <t>src/data/regions.ts</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="36" customHeight="1" s="24">
+      <c r="A20" s="1" t="inlineStr">
         <is>
           <t>Map1</t>
         </is>
       </c>
-      <c r="B20" s="20" t="inlineStr">
+      <c r="B20" s="1" t="inlineStr">
         <is>
           <t>weight_regional</t>
         </is>
       </c>
-      <c r="C20" s="63" t="n">
+      <c r="C20" s="16" t="n">
         <v>30</v>
       </c>
-      <c r="D20" s="20" t="inlineStr">
+      <c r="D20" s="1" t="inlineStr">
         <is>
           <t>weight</t>
         </is>
       </c>
-      <c r="E20" s="20" t="inlineStr">
+      <c r="E20" s="1" t="inlineStr">
         <is>
           <t>탐색률 지역 기여</t>
         </is>
       </c>
-      <c r="F20" s="20" t="inlineStr">
+      <c r="F20" s="1" t="inlineStr">
         <is>
           <t>탐색률 해당 항목 비중↑</t>
         </is>
       </c>
-      <c r="G20" s="20" t="inlineStr">
+      <c r="G20" s="1" t="inlineStr">
         <is>
           <t>비중↓</t>
         </is>
       </c>
-      <c r="H20" s="20" t="inlineStr">
-        <is>
-          <t>src/data/regions.ts</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="20" t="inlineStr">
+      <c r="H20" s="1" t="inlineStr">
+        <is>
+          <t>src/data/regions.ts</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="36" customHeight="1" s="24">
+      <c r="A21" s="1" t="inlineStr">
         <is>
           <t>Map1</t>
         </is>
       </c>
-      <c r="B21" s="20" t="inlineStr">
+      <c r="B21" s="1" t="inlineStr">
         <is>
           <t>weight_treasure</t>
         </is>
       </c>
-      <c r="C21" s="63" t="n">
+      <c r="C21" s="16" t="n">
         <v>10</v>
       </c>
-      <c r="D21" s="20" t="inlineStr">
+      <c r="D21" s="1" t="inlineStr">
         <is>
           <t>weight</t>
         </is>
       </c>
-      <c r="E21" s="20" t="inlineStr">
+      <c r="E21" s="1" t="inlineStr">
         <is>
           <t>탐색률 보물 기여</t>
         </is>
       </c>
-      <c r="F21" s="20" t="inlineStr">
+      <c r="F21" s="1" t="inlineStr">
         <is>
           <t>탐색률 해당 항목 비중↑</t>
         </is>
       </c>
-      <c r="G21" s="20" t="inlineStr">
+      <c r="G21" s="1" t="inlineStr">
         <is>
           <t>비중↓</t>
         </is>
       </c>
-      <c r="H21" s="20" t="inlineStr">
-        <is>
-          <t>src/data/regions.ts</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="20" t="inlineStr">
+      <c r="H21" s="1" t="inlineStr">
+        <is>
+          <t>src/data/regions.ts</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="18" customHeight="1" s="24">
+      <c r="A22" s="1" t="inlineStr">
         <is>
           <t>Map1</t>
         </is>
       </c>
-      <c r="B22" s="20" t="inlineStr">
+      <c r="B22" s="1" t="inlineStr">
         <is>
           <t>total_material_discovery</t>
         </is>
       </c>
-      <c r="C22" s="63" t="n">
+      <c r="C22" s="16" t="n">
         <v>7</v>
       </c>
-      <c r="D22" s="20" t="inlineStr">
+      <c r="D22" s="1" t="inlineStr">
         <is>
           <t>count</t>
         </is>
       </c>
-      <c r="E22" s="20" t="inlineStr">
+      <c r="E22" s="1" t="inlineStr">
         <is>
           <t>재료 발견 총량</t>
         </is>
       </c>
-      <c r="F22" s="20" t="inlineStr">
+      <c r="F22" s="1" t="inlineStr">
         <is>
           <t>완료 난이도↑</t>
         </is>
       </c>
-      <c r="G22" s="20" t="inlineStr">
+      <c r="G22" s="1" t="inlineStr">
         <is>
           <t>완료 난이도↓</t>
         </is>
       </c>
-      <c r="H22" s="20" t="inlineStr">
-        <is>
-          <t>src/data/regions.ts</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="20" t="inlineStr">
+      <c r="H22" s="1" t="inlineStr">
+        <is>
+          <t>src/data/regions.ts</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="18" customHeight="1" s="24">
+      <c r="A23" s="1" t="inlineStr">
         <is>
           <t>Map1</t>
         </is>
       </c>
-      <c r="B23" s="20" t="inlineStr">
+      <c r="B23" s="1" t="inlineStr">
         <is>
           <t>total_spirit_discovery</t>
         </is>
       </c>
-      <c r="C23" s="63" t="n">
+      <c r="C23" s="16" t="n">
         <v>3</v>
       </c>
-      <c r="D23" s="20" t="inlineStr">
+      <c r="D23" s="1" t="inlineStr">
         <is>
           <t>count</t>
         </is>
       </c>
-      <c r="E23" s="20" t="inlineStr">
+      <c r="E23" s="1" t="inlineStr">
         <is>
           <t>정령 발견 총량</t>
         </is>
       </c>
-      <c r="F23" s="20" t="inlineStr">
+      <c r="F23" s="1" t="inlineStr">
         <is>
           <t>완료 난이도↑</t>
         </is>
       </c>
-      <c r="G23" s="20" t="inlineStr">
+      <c r="G23" s="1" t="inlineStr">
         <is>
           <t>완료 난이도↓</t>
         </is>
       </c>
-      <c r="H23" s="20" t="inlineStr">
-        <is>
-          <t>src/data/regions.ts</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="20" t="inlineStr">
+      <c r="H23" s="1" t="inlineStr">
+        <is>
+          <t>src/data/regions.ts</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="18" customHeight="1" s="24">
+      <c r="A24" s="1" t="inlineStr">
         <is>
           <t>Map1</t>
         </is>
       </c>
-      <c r="B24" s="20" t="inlineStr">
+      <c r="B24" s="1" t="inlineStr">
         <is>
           <t>total_regional_discovery</t>
         </is>
       </c>
-      <c r="C24" s="63" t="n">
+      <c r="C24" s="16" t="n">
         <v>4</v>
       </c>
-      <c r="D24" s="20" t="inlineStr">
+      <c r="D24" s="1" t="inlineStr">
         <is>
           <t>count</t>
         </is>
       </c>
-      <c r="E24" s="20" t="inlineStr">
+      <c r="E24" s="1" t="inlineStr">
         <is>
           <t>지역 발견 총량</t>
         </is>
       </c>
-      <c r="F24" s="20" t="inlineStr">
+      <c r="F24" s="1" t="inlineStr">
         <is>
           <t>완료 난이도↑</t>
         </is>
       </c>
-      <c r="G24" s="20" t="inlineStr">
+      <c r="G24" s="1" t="inlineStr">
         <is>
           <t>완료 난이도↓</t>
         </is>
       </c>
-      <c r="H24" s="20" t="inlineStr">
-        <is>
-          <t>src/data/regions.ts</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="20" t="inlineStr">
+      <c r="H24" s="1" t="inlineStr">
+        <is>
+          <t>src/data/regions.ts</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="18" customHeight="1" s="24">
+      <c r="A25" s="1" t="inlineStr">
         <is>
           <t>Map1</t>
         </is>
       </c>
-      <c r="B25" s="20" t="inlineStr">
+      <c r="B25" s="1" t="inlineStr">
         <is>
           <t>total_treasure_discovery</t>
         </is>
       </c>
-      <c r="C25" s="63" t="n">
-        <v>1</v>
-      </c>
-      <c r="D25" s="20" t="inlineStr">
+      <c r="C25" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="D25" s="1" t="inlineStr">
         <is>
           <t>count</t>
         </is>
       </c>
-      <c r="E25" s="20" t="inlineStr">
+      <c r="E25" s="1" t="inlineStr">
         <is>
           <t>보물 발견 총량</t>
         </is>
       </c>
-      <c r="F25" s="20" t="inlineStr">
+      <c r="F25" s="1" t="inlineStr">
         <is>
           <t>완료 난이도↑</t>
         </is>
       </c>
-      <c r="G25" s="20" t="inlineStr">
+      <c r="G25" s="1" t="inlineStr">
         <is>
           <t>완료 난이도↓</t>
         </is>
       </c>
-      <c r="H25" s="20" t="inlineStr">
+      <c r="H25" s="1" t="inlineStr">
         <is>
           <t>src/data/regions.ts</t>
         </is>
@@ -6616,678 +6023,677 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:H18"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="17"/>
   <cols>
-    <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="28" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="10" customWidth="1" min="4" max="4"/>
-    <col width="24" customWidth="1" min="5" max="5"/>
-    <col width="16" customWidth="1" min="6" max="6"/>
-    <col width="16" customWidth="1" min="7" max="7"/>
-    <col width="28" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" style="24" min="1" max="1"/>
+    <col width="28" customWidth="1" style="24" min="2" max="2"/>
+    <col width="12" customWidth="1" style="24" min="3" max="3"/>
+    <col width="10" customWidth="1" style="24" min="4" max="4"/>
+    <col width="24" customWidth="1" style="24" min="5" max="5"/>
+    <col width="16" customWidth="1" style="24" min="6" max="7"/>
+    <col width="28" customWidth="1" style="24" min="8" max="8"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="48" t="inlineStr">
+    <row r="1" ht="20" customHeight="1" s="24">
+      <c r="A1" s="28" t="inlineStr">
         <is>
           <t>04_Quest - 의뢰 등급별 보상과 생성 규칙</t>
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" s="66" t="inlineStr">
+    <row r="2" ht="18" customHeight="1" s="24">
+      <c r="A2" s="19" t="inlineStr">
         <is>
           <t>카테고리</t>
         </is>
       </c>
-      <c r="B2" s="66" t="inlineStr">
+      <c r="B2" s="19" t="inlineStr">
         <is>
           <t>키</t>
         </is>
       </c>
-      <c r="C2" s="66" t="inlineStr">
+      <c r="C2" s="19" t="inlineStr">
         <is>
           <t>value</t>
         </is>
       </c>
-      <c r="D2" s="66" t="inlineStr">
+      <c r="D2" s="19" t="inlineStr">
         <is>
           <t>단위</t>
         </is>
       </c>
-      <c r="E2" s="66" t="inlineStr">
+      <c r="E2" s="19" t="inlineStr">
         <is>
           <t>어디에 쓰나</t>
         </is>
       </c>
-      <c r="F2" s="66" t="inlineStr">
+      <c r="F2" s="19" t="inlineStr">
         <is>
           <t>값↑</t>
         </is>
       </c>
-      <c r="G2" s="66" t="inlineStr">
+      <c r="G2" s="19" t="inlineStr">
         <is>
           <t>값↓</t>
         </is>
       </c>
-      <c r="H2" s="66" t="inlineStr">
+      <c r="H2" s="19" t="inlineStr">
         <is>
           <t>코드소스</t>
         </is>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" s="20" t="inlineStr">
+    <row r="3" ht="18" customHeight="1" s="24">
+      <c r="A3" s="1" t="inlineStr">
         <is>
           <t>보상</t>
         </is>
       </c>
-      <c r="B3" s="20" t="inlineStr">
+      <c r="B3" s="1" t="inlineStr">
         <is>
           <t>Easy_exp</t>
         </is>
       </c>
-      <c r="C3" s="63" t="n">
+      <c r="C3" s="16" t="n">
         <v>30</v>
       </c>
-      <c r="D3" s="20" t="inlineStr">
+      <c r="D3" s="1" t="inlineStr">
         <is>
           <t>exp</t>
         </is>
       </c>
-      <c r="E3" s="20" t="inlineStr">
+      <c r="E3" s="1" t="inlineStr">
         <is>
           <t>Easy 의뢰 EXP</t>
         </is>
       </c>
-      <c r="F3" s="20" t="inlineStr">
+      <c r="F3" s="1" t="inlineStr">
         <is>
           <t>보상 증가</t>
         </is>
       </c>
-      <c r="G3" s="20" t="inlineStr">
+      <c r="G3" s="1" t="inlineStr">
         <is>
           <t>보상 감소</t>
         </is>
       </c>
-      <c r="H3" s="20" t="inlineStr">
+      <c r="H3" s="1" t="inlineStr">
         <is>
           <t>src/data/quests.ts</t>
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" s="20" t="inlineStr">
+    <row r="4" ht="18" customHeight="1" s="24">
+      <c r="A4" s="1" t="inlineStr">
         <is>
           <t>보상</t>
         </is>
       </c>
-      <c r="B4" s="20" t="inlineStr">
+      <c r="B4" s="1" t="inlineStr">
         <is>
           <t>Easy_gold</t>
         </is>
       </c>
-      <c r="C4" s="63" t="n">
+      <c r="C4" s="16" t="n">
         <v>40</v>
       </c>
-      <c r="D4" s="20" t="inlineStr">
+      <c r="D4" s="1" t="inlineStr">
         <is>
           <t>gold</t>
         </is>
       </c>
-      <c r="E4" s="20" t="inlineStr">
+      <c r="E4" s="1" t="inlineStr">
         <is>
           <t>Easy 의뢰 Gold</t>
         </is>
       </c>
-      <c r="F4" s="20" t="inlineStr">
+      <c r="F4" s="1" t="inlineStr">
         <is>
           <t>보상 증가</t>
         </is>
       </c>
-      <c r="G4" s="20" t="inlineStr">
+      <c r="G4" s="1" t="inlineStr">
         <is>
           <t>보상 감소</t>
         </is>
       </c>
-      <c r="H4" s="20" t="inlineStr">
+      <c r="H4" s="1" t="inlineStr">
         <is>
           <t>src/data/quests.ts</t>
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" s="20" t="inlineStr">
+    <row r="5" ht="18" customHeight="1" s="24">
+      <c r="A5" s="1" t="inlineStr">
         <is>
           <t>보상</t>
         </is>
       </c>
-      <c r="B5" s="20" t="inlineStr">
+      <c r="B5" s="1" t="inlineStr">
         <is>
           <t>Normal_exp</t>
         </is>
       </c>
-      <c r="C5" s="63" t="n">
+      <c r="C5" s="16" t="n">
         <v>50</v>
       </c>
-      <c r="D5" s="20" t="inlineStr">
+      <c r="D5" s="1" t="inlineStr">
         <is>
           <t>exp</t>
         </is>
       </c>
-      <c r="E5" s="20" t="inlineStr">
+      <c r="E5" s="1" t="inlineStr">
         <is>
           <t>Normal 의뢰 EXP</t>
         </is>
       </c>
-      <c r="F5" s="20" t="inlineStr">
+      <c r="F5" s="1" t="inlineStr">
         <is>
           <t>보상 증가</t>
         </is>
       </c>
-      <c r="G5" s="20" t="inlineStr">
+      <c r="G5" s="1" t="inlineStr">
         <is>
           <t>보상 감소</t>
         </is>
       </c>
-      <c r="H5" s="20" t="inlineStr">
+      <c r="H5" s="1" t="inlineStr">
         <is>
           <t>src/data/quests.ts</t>
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" s="20" t="inlineStr">
+    <row r="6" ht="18" customHeight="1" s="24">
+      <c r="A6" s="1" t="inlineStr">
         <is>
           <t>보상</t>
         </is>
       </c>
-      <c r="B6" s="20" t="inlineStr">
+      <c r="B6" s="1" t="inlineStr">
         <is>
           <t>Normal_gold</t>
         </is>
       </c>
-      <c r="C6" s="63" t="n">
+      <c r="C6" s="16" t="n">
         <v>70</v>
       </c>
-      <c r="D6" s="20" t="inlineStr">
+      <c r="D6" s="1" t="inlineStr">
         <is>
           <t>gold</t>
         </is>
       </c>
-      <c r="E6" s="20" t="inlineStr">
+      <c r="E6" s="1" t="inlineStr">
         <is>
           <t>Normal 의뢰 Gold</t>
         </is>
       </c>
-      <c r="F6" s="20" t="inlineStr">
+      <c r="F6" s="1" t="inlineStr">
         <is>
           <t>보상 증가</t>
         </is>
       </c>
-      <c r="G6" s="20" t="inlineStr">
+      <c r="G6" s="1" t="inlineStr">
         <is>
           <t>보상 감소</t>
         </is>
       </c>
-      <c r="H6" s="20" t="inlineStr">
+      <c r="H6" s="1" t="inlineStr">
         <is>
           <t>src/data/quests.ts</t>
         </is>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" s="20" t="inlineStr">
+    <row r="7" ht="18" customHeight="1" s="24">
+      <c r="A7" s="1" t="inlineStr">
         <is>
           <t>보상</t>
         </is>
       </c>
-      <c r="B7" s="20" t="inlineStr">
+      <c r="B7" s="1" t="inlineStr">
         <is>
           <t>Hard_exp</t>
         </is>
       </c>
-      <c r="C7" s="63" t="n">
+      <c r="C7" s="16" t="n">
         <v>80</v>
       </c>
-      <c r="D7" s="20" t="inlineStr">
+      <c r="D7" s="1" t="inlineStr">
         <is>
           <t>exp</t>
         </is>
       </c>
-      <c r="E7" s="20" t="inlineStr">
+      <c r="E7" s="1" t="inlineStr">
         <is>
           <t>Hard 의뢰 EXP</t>
         </is>
       </c>
-      <c r="F7" s="20" t="inlineStr">
+      <c r="F7" s="1" t="inlineStr">
         <is>
           <t>보상 증가</t>
         </is>
       </c>
-      <c r="G7" s="20" t="inlineStr">
+      <c r="G7" s="1" t="inlineStr">
         <is>
           <t>보상 감소</t>
         </is>
       </c>
-      <c r="H7" s="20" t="inlineStr">
+      <c r="H7" s="1" t="inlineStr">
         <is>
           <t>src/data/quests.ts</t>
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" s="20" t="inlineStr">
+    <row r="8" ht="18" customHeight="1" s="24">
+      <c r="A8" s="1" t="inlineStr">
         <is>
           <t>보상</t>
         </is>
       </c>
-      <c r="B8" s="20" t="inlineStr">
+      <c r="B8" s="1" t="inlineStr">
         <is>
           <t>Hard_gold</t>
         </is>
       </c>
-      <c r="C8" s="63" t="n">
+      <c r="C8" s="16" t="n">
         <v>120</v>
       </c>
-      <c r="D8" s="20" t="inlineStr">
+      <c r="D8" s="1" t="inlineStr">
         <is>
           <t>gold</t>
         </is>
       </c>
-      <c r="E8" s="20" t="inlineStr">
+      <c r="E8" s="1" t="inlineStr">
         <is>
           <t>Hard 의뢰 Gold</t>
         </is>
       </c>
-      <c r="F8" s="20" t="inlineStr">
+      <c r="F8" s="1" t="inlineStr">
         <is>
           <t>보상 증가</t>
         </is>
       </c>
-      <c r="G8" s="20" t="inlineStr">
+      <c r="G8" s="1" t="inlineStr">
         <is>
           <t>보상 감소</t>
         </is>
       </c>
-      <c r="H8" s="20" t="inlineStr">
+      <c r="H8" s="1" t="inlineStr">
         <is>
           <t>src/data/quests.ts</t>
         </is>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" s="20" t="inlineStr">
+    <row r="9" ht="18" customHeight="1" s="24">
+      <c r="A9" s="1" t="inlineStr">
         <is>
           <t>보상</t>
         </is>
       </c>
-      <c r="B9" s="20" t="inlineStr">
+      <c r="B9" s="1" t="inlineStr">
         <is>
           <t>Special_exp</t>
         </is>
       </c>
-      <c r="C9" s="63" t="n">
+      <c r="C9" s="16" t="n">
         <v>120</v>
       </c>
-      <c r="D9" s="20" t="inlineStr">
+      <c r="D9" s="1" t="inlineStr">
         <is>
           <t>exp</t>
         </is>
       </c>
-      <c r="E9" s="20" t="inlineStr">
+      <c r="E9" s="1" t="inlineStr">
         <is>
           <t>Special 의뢰 EXP</t>
         </is>
       </c>
-      <c r="F9" s="20" t="inlineStr">
+      <c r="F9" s="1" t="inlineStr">
         <is>
           <t>보상 증가</t>
         </is>
       </c>
-      <c r="G9" s="20" t="inlineStr">
+      <c r="G9" s="1" t="inlineStr">
         <is>
           <t>보상 감소</t>
         </is>
       </c>
-      <c r="H9" s="20" t="inlineStr">
+      <c r="H9" s="1" t="inlineStr">
         <is>
           <t>src/data/quests.ts</t>
         </is>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" s="20" t="inlineStr">
+    <row r="10" ht="18" customHeight="1" s="24">
+      <c r="A10" s="1" t="inlineStr">
         <is>
           <t>보상</t>
         </is>
       </c>
-      <c r="B10" s="20" t="inlineStr">
+      <c r="B10" s="1" t="inlineStr">
         <is>
           <t>Special_gold</t>
         </is>
       </c>
-      <c r="C10" s="63" t="n">
+      <c r="C10" s="16" t="n">
         <v>200</v>
       </c>
-      <c r="D10" s="20" t="inlineStr">
+      <c r="D10" s="1" t="inlineStr">
         <is>
           <t>gold</t>
         </is>
       </c>
-      <c r="E10" s="20" t="inlineStr">
+      <c r="E10" s="1" t="inlineStr">
         <is>
           <t>Special 의뢰 Gold</t>
         </is>
       </c>
-      <c r="F10" s="20" t="inlineStr">
+      <c r="F10" s="1" t="inlineStr">
         <is>
           <t>보상 증가</t>
         </is>
       </c>
-      <c r="G10" s="20" t="inlineStr">
+      <c r="G10" s="1" t="inlineStr">
         <is>
           <t>보상 감소</t>
         </is>
       </c>
-      <c r="H10" s="20" t="inlineStr">
+      <c r="H10" s="1" t="inlineStr">
         <is>
           <t>src/data/quests.ts</t>
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" s="20" t="inlineStr">
+    <row r="11" ht="18" customHeight="1" s="24">
+      <c r="A11" s="1" t="inlineStr">
         <is>
           <t>생성</t>
         </is>
       </c>
-      <c r="B11" s="20" t="inlineStr">
+      <c r="B11" s="1" t="inlineStr">
         <is>
           <t>weight_Easy</t>
         </is>
       </c>
-      <c r="C11" s="63" t="n">
+      <c r="C11" s="16" t="n">
         <v>45</v>
       </c>
-      <c r="D11" s="20" t="inlineStr">
+      <c r="D11" s="1" t="inlineStr">
         <is>
           <t>weight</t>
         </is>
       </c>
-      <c r="E11" s="20" t="inlineStr">
+      <c r="E11" s="1" t="inlineStr">
         <is>
           <t>Easy 생성 비중</t>
         </is>
       </c>
-      <c r="F11" s="20" t="inlineStr">
+      <c r="F11" s="1" t="inlineStr">
         <is>
           <t>빈도 증가</t>
         </is>
       </c>
-      <c r="G11" s="20" t="inlineStr">
+      <c r="G11" s="1" t="inlineStr">
         <is>
           <t>빈도 감소</t>
         </is>
       </c>
-      <c r="H11" s="20" t="inlineStr">
+      <c r="H11" s="1" t="inlineStr">
         <is>
           <t>src/data/quests.ts</t>
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" s="20" t="inlineStr">
+    <row r="12" ht="18" customHeight="1" s="24">
+      <c r="A12" s="1" t="inlineStr">
         <is>
           <t>생성</t>
         </is>
       </c>
-      <c r="B12" s="20" t="inlineStr">
+      <c r="B12" s="1" t="inlineStr">
         <is>
           <t>weight_Normal</t>
         </is>
       </c>
-      <c r="C12" s="63" t="n">
+      <c r="C12" s="16" t="n">
         <v>35</v>
       </c>
-      <c r="D12" s="20" t="inlineStr">
+      <c r="D12" s="1" t="inlineStr">
         <is>
           <t>weight</t>
         </is>
       </c>
-      <c r="E12" s="20" t="inlineStr">
+      <c r="E12" s="1" t="inlineStr">
         <is>
           <t>Normal 생성 비중</t>
         </is>
       </c>
-      <c r="F12" s="20" t="inlineStr">
+      <c r="F12" s="1" t="inlineStr">
         <is>
           <t>빈도 증가</t>
         </is>
       </c>
-      <c r="G12" s="20" t="inlineStr">
+      <c r="G12" s="1" t="inlineStr">
         <is>
           <t>빈도 감소</t>
         </is>
       </c>
-      <c r="H12" s="20" t="inlineStr">
+      <c r="H12" s="1" t="inlineStr">
         <is>
           <t>src/data/quests.ts</t>
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="20" t="inlineStr">
+    <row r="13" ht="18" customHeight="1" s="24">
+      <c r="A13" s="1" t="inlineStr">
         <is>
           <t>생성</t>
         </is>
       </c>
-      <c r="B13" s="20" t="inlineStr">
+      <c r="B13" s="1" t="inlineStr">
         <is>
           <t>weight_Hard</t>
         </is>
       </c>
-      <c r="C13" s="63" t="n">
+      <c r="C13" s="16" t="n">
         <v>15</v>
       </c>
-      <c r="D13" s="20" t="inlineStr">
+      <c r="D13" s="1" t="inlineStr">
         <is>
           <t>weight</t>
         </is>
       </c>
-      <c r="E13" s="20" t="inlineStr">
+      <c r="E13" s="1" t="inlineStr">
         <is>
           <t>Hard 생성 비중</t>
         </is>
       </c>
-      <c r="F13" s="20" t="inlineStr">
+      <c r="F13" s="1" t="inlineStr">
         <is>
           <t>빈도 증가</t>
         </is>
       </c>
-      <c r="G13" s="20" t="inlineStr">
+      <c r="G13" s="1" t="inlineStr">
         <is>
           <t>빈도 감소</t>
         </is>
       </c>
-      <c r="H13" s="20" t="inlineStr">
+      <c r="H13" s="1" t="inlineStr">
         <is>
           <t>src/data/quests.ts</t>
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="20" t="inlineStr">
+    <row r="14" ht="18" customHeight="1" s="24">
+      <c r="A14" s="1" t="inlineStr">
         <is>
           <t>생성</t>
         </is>
       </c>
-      <c r="B14" s="20" t="inlineStr">
+      <c r="B14" s="1" t="inlineStr">
         <is>
           <t>weight_Special</t>
         </is>
       </c>
-      <c r="C14" s="63" t="n">
+      <c r="C14" s="16" t="n">
         <v>5</v>
       </c>
-      <c r="D14" s="20" t="inlineStr">
+      <c r="D14" s="1" t="inlineStr">
         <is>
           <t>weight</t>
         </is>
       </c>
-      <c r="E14" s="20" t="inlineStr">
+      <c r="E14" s="1" t="inlineStr">
         <is>
           <t>Special 생성 비중</t>
         </is>
       </c>
-      <c r="F14" s="20" t="inlineStr">
+      <c r="F14" s="1" t="inlineStr">
         <is>
           <t>빈도 증가</t>
         </is>
       </c>
-      <c r="G14" s="20" t="inlineStr">
+      <c r="G14" s="1" t="inlineStr">
         <is>
           <t>빈도 감소</t>
         </is>
       </c>
-      <c r="H14" s="20" t="inlineStr">
+      <c r="H14" s="1" t="inlineStr">
         <is>
           <t>src/data/quests.ts</t>
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" s="20" t="inlineStr">
+    <row r="15" ht="18" customHeight="1" s="24">
+      <c r="A15" s="1" t="inlineStr">
         <is>
           <t>보드</t>
         </is>
       </c>
-      <c r="B15" s="20" t="inlineStr">
+      <c r="B15" s="1" t="inlineStr">
         <is>
           <t>max_slots</t>
         </is>
       </c>
-      <c r="C15" s="63" t="n">
+      <c r="C15" s="16" t="n">
         <v>6</v>
       </c>
-      <c r="D15" s="20" t="inlineStr">
+      <c r="D15" s="1" t="inlineStr">
         <is>
           <t>slot</t>
         </is>
       </c>
-      <c r="E15" s="20" t="inlineStr">
+      <c r="E15" s="1" t="inlineStr">
         <is>
           <t>동시 의뢰 슬롯 수</t>
         </is>
       </c>
-      <c r="F15" s="20" t="inlineStr">
+      <c r="F15" s="1" t="inlineStr">
         <is>
           <t>동시 진행 증가</t>
         </is>
       </c>
-      <c r="G15" s="20" t="inlineStr">
+      <c r="G15" s="1" t="inlineStr">
         <is>
           <t>동시 진행 감소</t>
         </is>
       </c>
-      <c r="H15" s="20" t="inlineStr">
+      <c r="H15" s="1" t="inlineStr">
         <is>
           <t>src/data/constants.ts</t>
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" s="20" t="inlineStr">
+    <row r="16" ht="18" customHeight="1" s="24">
+      <c r="A16" s="1" t="inlineStr">
         <is>
           <t>보드</t>
         </is>
       </c>
-      <c r="B16" s="20" t="inlineStr">
+      <c r="B16" s="1" t="inlineStr">
         <is>
           <t>respawn_minutes</t>
         </is>
       </c>
-      <c r="C16" s="63" t="n">
+      <c r="C16" s="16" t="n">
         <v>20</v>
       </c>
-      <c r="D16" s="20" t="inlineStr">
+      <c r="D16" s="1" t="inlineStr">
         <is>
           <t>minute</t>
         </is>
       </c>
-      <c r="E16" s="20" t="inlineStr">
+      <c r="E16" s="1" t="inlineStr">
         <is>
           <t>의뢰 재생성 주기</t>
         </is>
       </c>
-      <c r="F16" s="20" t="inlineStr">
+      <c r="F16" s="1" t="inlineStr">
         <is>
           <t>재생성 느림</t>
         </is>
       </c>
-      <c r="G16" s="20" t="inlineStr">
+      <c r="G16" s="1" t="inlineStr">
         <is>
           <t>재생성 빠름</t>
         </is>
       </c>
-      <c r="H16" s="20" t="inlineStr">
+      <c r="H16" s="1" t="inlineStr">
         <is>
           <t>src/data/constants.ts</t>
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" s="20" t="inlineStr">
+    <row r="17" ht="18" customHeight="1" s="24">
+      <c r="A17" s="1" t="inlineStr">
         <is>
           <t>패널티</t>
         </is>
       </c>
-      <c r="B17" s="20" t="inlineStr">
+      <c r="B17" s="1" t="inlineStr">
         <is>
           <t>reject_penalty_gold</t>
         </is>
       </c>
-      <c r="C17" s="63" t="n">
+      <c r="C17" s="16" t="n">
         <v>200</v>
       </c>
-      <c r="D17" s="20" t="inlineStr">
+      <c r="D17" s="1" t="inlineStr">
         <is>
           <t>gold</t>
         </is>
       </c>
-      <c r="E17" s="20" t="inlineStr">
+      <c r="E17" s="1" t="inlineStr">
         <is>
           <t>의뢰 거절 패널티</t>
         </is>
       </c>
-      <c r="F17" s="20" t="inlineStr">
+      <c r="F17" s="1" t="inlineStr">
         <is>
           <t>거절 부담 증가</t>
         </is>
       </c>
-      <c r="G17" s="20" t="inlineStr">
+      <c r="G17" s="1" t="inlineStr">
         <is>
           <t>거절 부담 감소</t>
         </is>
       </c>
-      <c r="H17" s="20" t="inlineStr">
+      <c r="H17" s="1" t="inlineStr">
         <is>
           <t>src/components/CraftScreen.tsx</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="43" t="inlineStr">
+      <c r="A18" s="12" t="inlineStr">
         <is>
           <t>check_weight_sum</t>
         </is>
       </c>
-      <c r="B18" s="43">
+      <c r="B18" s="12">
         <f>SUM(C11:C14)</f>
         <v/>
       </c>
-      <c r="C18" s="44" t="inlineStr">
+      <c r="C18" s="13" t="inlineStr">
         <is>
           <t>100 권장</t>
         </is>
@@ -7308,42 +6714,42 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:I25"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="17"/>
   <cols>
-    <col width="16" customWidth="1" min="1" max="1"/>
-    <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="10" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
-    <col width="16" customWidth="1" min="6" max="6"/>
-    <col width="20" customWidth="1" min="7" max="7"/>
-    <col width="24" customWidth="1" min="8" max="8"/>
+    <col width="16" customWidth="1" style="24" min="1" max="1"/>
+    <col width="12" customWidth="1" style="24" min="2" max="2"/>
+    <col width="10" customWidth="1" style="24" min="3" max="3"/>
+    <col width="12" customWidth="1" style="24" min="4" max="4"/>
+    <col width="14" customWidth="1" style="24" min="5" max="5"/>
+    <col width="16" customWidth="1" style="24" min="6" max="6"/>
+    <col width="20" customWidth="1" style="24" min="7" max="7"/>
+    <col width="24" customWidth="1" style="24" min="8" max="8"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="50" t="inlineStr">
+    <row r="1" ht="20" customHeight="1" s="24">
+      <c r="A1" s="29" t="inlineStr">
         <is>
           <t>05_Item - 재료/기타 아이템 기본 정보와 희귀도</t>
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" s="67" t="inlineStr">
+    <row r="2" ht="18" customHeight="1" s="24">
+      <c r="A2" s="20" t="inlineStr">
         <is>
           <t>item_id</t>
         </is>
       </c>
-      <c r="B2" s="67" t="inlineStr">
+      <c r="B2" s="20" t="inlineStr">
         <is>
           <t>이름</t>
         </is>
       </c>
-      <c r="C2" s="67" t="inlineStr">
+      <c r="C2" s="20" t="inlineStr">
         <is>
           <t>카테고리</t>
         </is>
       </c>
-      <c r="D2" s="67" t="inlineStr">
+      <c r="D2" s="20" t="inlineStr">
         <is>
           <t>재료분류</t>
         </is>
@@ -7353,44 +6759,44 @@
           <t>희귀도(value)</t>
         </is>
       </c>
-      <c r="F2" s="67" t="inlineStr">
+      <c r="F2" s="20" t="inlineStr">
         <is>
           <t>기본가치(value)</t>
         </is>
       </c>
-      <c r="G2" s="67" t="inlineStr">
+      <c r="G2" s="20" t="inlineStr">
         <is>
           <t>조절 기준</t>
         </is>
       </c>
-      <c r="H2" s="67" t="inlineStr">
+      <c r="H2" s="20" t="inlineStr">
         <is>
           <t>메모</t>
         </is>
       </c>
-      <c r="I2" s="67" t="inlineStr">
+      <c r="I2" s="20" t="inlineStr">
         <is>
           <t>코드소스</t>
         </is>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" s="20" t="inlineStr">
+    <row r="3" ht="36" customHeight="1" s="24">
+      <c r="A3" s="1" t="inlineStr">
         <is>
           <t>flower</t>
         </is>
       </c>
-      <c r="B3" s="20" t="inlineStr">
+      <c r="B3" s="1" t="inlineStr">
         <is>
           <t>꽃</t>
         </is>
       </c>
-      <c r="C3" s="20" t="inlineStr">
+      <c r="C3" s="1" t="inlineStr">
         <is>
           <t>재료</t>
         </is>
       </c>
-      <c r="D3" s="20" t="inlineStr">
+      <c r="D3" s="1" t="inlineStr">
         <is>
           <t>nature</t>
         </is>
@@ -7400,40 +6806,40 @@
           <t>common</t>
         </is>
       </c>
-      <c r="F3" s="63" t="inlineStr"/>
-      <c r="G3" s="20" t="inlineStr">
+      <c r="F3" s="16" t="n"/>
+      <c r="G3" s="1" t="inlineStr">
         <is>
           <t>Map1 드랍</t>
         </is>
       </c>
-      <c r="H3" s="20" t="inlineStr">
+      <c r="H3" s="1" t="inlineStr">
         <is>
           <t>기본 재료</t>
         </is>
       </c>
-      <c r="I3" s="20" t="inlineStr">
+      <c r="I3" s="1" t="inlineStr">
         <is>
           <t>src/data/items.ts</t>
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" s="20" t="inlineStr">
+    <row r="4" ht="36" customHeight="1" s="24">
+      <c r="A4" s="1" t="inlineStr">
         <is>
           <t>leaf</t>
         </is>
       </c>
-      <c r="B4" s="20" t="inlineStr">
+      <c r="B4" s="1" t="inlineStr">
         <is>
           <t>잎</t>
         </is>
       </c>
-      <c r="C4" s="20" t="inlineStr">
+      <c r="C4" s="1" t="inlineStr">
         <is>
           <t>재료</t>
         </is>
       </c>
-      <c r="D4" s="20" t="inlineStr">
+      <c r="D4" s="1" t="inlineStr">
         <is>
           <t>nature</t>
         </is>
@@ -7443,40 +6849,40 @@
           <t>common</t>
         </is>
       </c>
-      <c r="F4" s="63" t="inlineStr"/>
-      <c r="G4" s="20" t="inlineStr">
+      <c r="F4" s="16" t="n"/>
+      <c r="G4" s="1" t="inlineStr">
         <is>
           <t>Map1 드랍</t>
         </is>
       </c>
-      <c r="H4" s="20" t="inlineStr">
+      <c r="H4" s="1" t="inlineStr">
         <is>
           <t>기본 재료</t>
         </is>
       </c>
-      <c r="I4" s="20" t="inlineStr">
+      <c r="I4" s="1" t="inlineStr">
         <is>
           <t>src/data/items.ts</t>
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" s="20" t="inlineStr">
+    <row r="5" ht="36" customHeight="1" s="24">
+      <c r="A5" s="1" t="inlineStr">
         <is>
           <t>soil</t>
         </is>
       </c>
-      <c r="B5" s="20" t="inlineStr">
+      <c r="B5" s="1" t="inlineStr">
         <is>
           <t>흙</t>
         </is>
       </c>
-      <c r="C5" s="20" t="inlineStr">
+      <c r="C5" s="1" t="inlineStr">
         <is>
           <t>재료</t>
         </is>
       </c>
-      <c r="D5" s="20" t="inlineStr">
+      <c r="D5" s="1" t="inlineStr">
         <is>
           <t>nature</t>
         </is>
@@ -7486,40 +6892,40 @@
           <t>common</t>
         </is>
       </c>
-      <c r="F5" s="63" t="inlineStr"/>
-      <c r="G5" s="20" t="inlineStr">
+      <c r="F5" s="16" t="n"/>
+      <c r="G5" s="1" t="inlineStr">
         <is>
           <t>Map1 드랍</t>
         </is>
       </c>
-      <c r="H5" s="20" t="inlineStr">
+      <c r="H5" s="1" t="inlineStr">
         <is>
           <t>기본 재료</t>
         </is>
       </c>
-      <c r="I5" s="20" t="inlineStr">
+      <c r="I5" s="1" t="inlineStr">
         <is>
           <t>src/data/items.ts</t>
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" s="20" t="inlineStr">
+    <row r="6" ht="36" customHeight="1" s="24">
+      <c r="A6" s="1" t="inlineStr">
         <is>
           <t>water</t>
         </is>
       </c>
-      <c r="B6" s="20" t="inlineStr">
+      <c r="B6" s="1" t="inlineStr">
         <is>
           <t>물</t>
         </is>
       </c>
-      <c r="C6" s="20" t="inlineStr">
+      <c r="C6" s="1" t="inlineStr">
         <is>
           <t>재료</t>
         </is>
       </c>
-      <c r="D6" s="20" t="inlineStr">
+      <c r="D6" s="1" t="inlineStr">
         <is>
           <t>element</t>
         </is>
@@ -7529,40 +6935,40 @@
           <t>common</t>
         </is>
       </c>
-      <c r="F6" s="63" t="inlineStr"/>
-      <c r="G6" s="20" t="inlineStr">
+      <c r="F6" s="16" t="n"/>
+      <c r="G6" s="1" t="inlineStr">
         <is>
           <t>Map1 드랍</t>
         </is>
       </c>
-      <c r="H6" s="20" t="inlineStr">
+      <c r="H6" s="1" t="inlineStr">
         <is>
           <t>기본 재료</t>
         </is>
       </c>
-      <c r="I6" s="20" t="inlineStr">
+      <c r="I6" s="1" t="inlineStr">
         <is>
           <t>src/data/items.ts</t>
         </is>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" s="20" t="inlineStr">
+    <row r="7" ht="36" customHeight="1" s="24">
+      <c r="A7" s="1" t="inlineStr">
         <is>
           <t>fire</t>
         </is>
       </c>
-      <c r="B7" s="20" t="inlineStr">
+      <c r="B7" s="1" t="inlineStr">
         <is>
           <t>불</t>
         </is>
       </c>
-      <c r="C7" s="20" t="inlineStr">
+      <c r="C7" s="1" t="inlineStr">
         <is>
           <t>재료</t>
         </is>
       </c>
-      <c r="D7" s="20" t="inlineStr">
+      <c r="D7" s="1" t="inlineStr">
         <is>
           <t>element</t>
         </is>
@@ -7572,40 +6978,40 @@
           <t>common</t>
         </is>
       </c>
-      <c r="F7" s="63" t="inlineStr"/>
-      <c r="G7" s="20" t="inlineStr">
+      <c r="F7" s="16" t="n"/>
+      <c r="G7" s="1" t="inlineStr">
         <is>
           <t>미사용 예시</t>
         </is>
       </c>
-      <c r="H7" s="20" t="inlineStr">
+      <c r="H7" s="1" t="inlineStr">
         <is>
           <t>추후 지역용</t>
         </is>
       </c>
-      <c r="I7" s="20" t="inlineStr">
+      <c r="I7" s="1" t="inlineStr">
         <is>
           <t>src/data/items.ts</t>
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" s="20" t="inlineStr">
+    <row r="8" ht="36" customHeight="1" s="24">
+      <c r="A8" s="1" t="inlineStr">
         <is>
           <t>wind</t>
         </is>
       </c>
-      <c r="B8" s="20" t="inlineStr">
+      <c r="B8" s="1" t="inlineStr">
         <is>
           <t>바람</t>
         </is>
       </c>
-      <c r="C8" s="20" t="inlineStr">
+      <c r="C8" s="1" t="inlineStr">
         <is>
           <t>재료</t>
         </is>
       </c>
-      <c r="D8" s="20" t="inlineStr">
+      <c r="D8" s="1" t="inlineStr">
         <is>
           <t>element</t>
         </is>
@@ -7615,40 +7021,40 @@
           <t>common</t>
         </is>
       </c>
-      <c r="F8" s="63" t="inlineStr"/>
-      <c r="G8" s="20" t="inlineStr">
+      <c r="F8" s="16" t="n"/>
+      <c r="G8" s="1" t="inlineStr">
         <is>
           <t>미사용 예시</t>
         </is>
       </c>
-      <c r="H8" s="20" t="inlineStr">
+      <c r="H8" s="1" t="inlineStr">
         <is>
           <t>추후 지역용</t>
         </is>
       </c>
-      <c r="I8" s="20" t="inlineStr">
+      <c r="I8" s="1" t="inlineStr">
         <is>
           <t>src/data/items.ts</t>
         </is>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" s="20" t="inlineStr">
+    <row r="9" ht="36" customHeight="1" s="24">
+      <c r="A9" s="1" t="inlineStr">
         <is>
           <t>star</t>
         </is>
       </c>
-      <c r="B9" s="20" t="inlineStr">
+      <c r="B9" s="1" t="inlineStr">
         <is>
           <t>별</t>
         </is>
       </c>
-      <c r="C9" s="20" t="inlineStr">
+      <c r="C9" s="1" t="inlineStr">
         <is>
           <t>재료</t>
         </is>
       </c>
-      <c r="D9" s="20" t="inlineStr">
+      <c r="D9" s="1" t="inlineStr">
         <is>
           <t>sky</t>
         </is>
@@ -7658,40 +7064,40 @@
           <t>common</t>
         </is>
       </c>
-      <c r="F9" s="63" t="inlineStr"/>
-      <c r="G9" s="20" t="inlineStr">
+      <c r="F9" s="16" t="n"/>
+      <c r="G9" s="1" t="inlineStr">
         <is>
           <t>Map1 드랍</t>
         </is>
       </c>
-      <c r="H9" s="20" t="inlineStr">
+      <c r="H9" s="1" t="inlineStr">
         <is>
           <t>기본 재료</t>
         </is>
       </c>
-      <c r="I9" s="20" t="inlineStr">
+      <c r="I9" s="1" t="inlineStr">
         <is>
           <t>src/data/items.ts</t>
         </is>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" s="20" t="inlineStr">
+    <row r="10" ht="36" customHeight="1" s="24">
+      <c r="A10" s="1" t="inlineStr">
         <is>
           <t>moon</t>
         </is>
       </c>
-      <c r="B10" s="20" t="inlineStr">
+      <c r="B10" s="1" t="inlineStr">
         <is>
           <t>달</t>
         </is>
       </c>
-      <c r="C10" s="20" t="inlineStr">
+      <c r="C10" s="1" t="inlineStr">
         <is>
           <t>재료</t>
         </is>
       </c>
-      <c r="D10" s="20" t="inlineStr">
+      <c r="D10" s="1" t="inlineStr">
         <is>
           <t>sky</t>
         </is>
@@ -7701,40 +7107,40 @@
           <t>common</t>
         </is>
       </c>
-      <c r="F10" s="63" t="inlineStr"/>
-      <c r="G10" s="20" t="inlineStr">
+      <c r="F10" s="16" t="n"/>
+      <c r="G10" s="1" t="inlineStr">
         <is>
           <t>미사용 예시</t>
         </is>
       </c>
-      <c r="H10" s="20" t="inlineStr">
+      <c r="H10" s="1" t="inlineStr">
         <is>
           <t>추후 지역용</t>
         </is>
       </c>
-      <c r="I10" s="20" t="inlineStr">
+      <c r="I10" s="1" t="inlineStr">
         <is>
           <t>src/data/items.ts</t>
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" s="20" t="inlineStr">
+    <row r="11" ht="36" customHeight="1" s="24">
+      <c r="A11" s="1" t="inlineStr">
         <is>
           <t>light</t>
         </is>
       </c>
-      <c r="B11" s="20" t="inlineStr">
+      <c r="B11" s="1" t="inlineStr">
         <is>
           <t>태양</t>
         </is>
       </c>
-      <c r="C11" s="20" t="inlineStr">
+      <c r="C11" s="1" t="inlineStr">
         <is>
           <t>재료</t>
         </is>
       </c>
-      <c r="D11" s="20" t="inlineStr">
+      <c r="D11" s="1" t="inlineStr">
         <is>
           <t>sky</t>
         </is>
@@ -7744,40 +7150,40 @@
           <t>common</t>
         </is>
       </c>
-      <c r="F11" s="63" t="inlineStr"/>
-      <c r="G11" s="20" t="inlineStr">
+      <c r="F11" s="16" t="n"/>
+      <c r="G11" s="1" t="inlineStr">
         <is>
           <t>미사용 예시</t>
         </is>
       </c>
-      <c r="H11" s="20" t="inlineStr">
+      <c r="H11" s="1" t="inlineStr">
         <is>
           <t>추후 지역용</t>
         </is>
       </c>
-      <c r="I11" s="20" t="inlineStr">
+      <c r="I11" s="1" t="inlineStr">
         <is>
           <t>src/data/items.ts</t>
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" s="20" t="inlineStr">
+    <row r="12" ht="36" customHeight="1" s="24">
+      <c r="A12" s="1" t="inlineStr">
         <is>
           <t>magic</t>
         </is>
       </c>
-      <c r="B12" s="20" t="inlineStr">
+      <c r="B12" s="1" t="inlineStr">
         <is>
           <t>마법</t>
         </is>
       </c>
-      <c r="C12" s="20" t="inlineStr">
+      <c r="C12" s="1" t="inlineStr">
         <is>
           <t>재료</t>
         </is>
       </c>
-      <c r="D12" s="20" t="inlineStr">
+      <c r="D12" s="1" t="inlineStr">
         <is>
           <t>mystic</t>
         </is>
@@ -7787,40 +7193,40 @@
           <t>common</t>
         </is>
       </c>
-      <c r="F12" s="63" t="inlineStr"/>
-      <c r="G12" s="20" t="inlineStr">
+      <c r="F12" s="16" t="n"/>
+      <c r="G12" s="1" t="inlineStr">
         <is>
           <t>Map1 드랍</t>
         </is>
       </c>
-      <c r="H12" s="20" t="inlineStr">
+      <c r="H12" s="1" t="inlineStr">
         <is>
           <t>기본 재료</t>
         </is>
       </c>
-      <c r="I12" s="20" t="inlineStr">
+      <c r="I12" s="1" t="inlineStr">
         <is>
           <t>src/data/items.ts</t>
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="20" t="inlineStr">
+    <row r="13" ht="36" customHeight="1" s="24">
+      <c r="A13" s="1" t="inlineStr">
         <is>
           <t>ether</t>
         </is>
       </c>
-      <c r="B13" s="20" t="inlineStr">
+      <c r="B13" s="1" t="inlineStr">
         <is>
           <t>에테르</t>
         </is>
       </c>
-      <c r="C13" s="20" t="inlineStr">
+      <c r="C13" s="1" t="inlineStr">
         <is>
           <t>재료</t>
         </is>
       </c>
-      <c r="D13" s="20" t="inlineStr">
+      <c r="D13" s="1" t="inlineStr">
         <is>
           <t>mystic</t>
         </is>
@@ -7830,40 +7236,40 @@
           <t>common</t>
         </is>
       </c>
-      <c r="F13" s="63" t="inlineStr"/>
-      <c r="G13" s="20" t="inlineStr">
+      <c r="F13" s="16" t="n"/>
+      <c r="G13" s="1" t="inlineStr">
         <is>
           <t>미사용 예시</t>
         </is>
       </c>
-      <c r="H13" s="20" t="inlineStr">
+      <c r="H13" s="1" t="inlineStr">
         <is>
           <t>추후 지역용</t>
         </is>
       </c>
-      <c r="I13" s="20" t="inlineStr">
+      <c r="I13" s="1" t="inlineStr">
         <is>
           <t>src/data/items.ts</t>
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="20" t="inlineStr">
+    <row r="14" ht="36" customHeight="1" s="24">
+      <c r="A14" s="1" t="inlineStr">
         <is>
           <t>gem</t>
         </is>
       </c>
-      <c r="B14" s="20" t="inlineStr">
+      <c r="B14" s="1" t="inlineStr">
         <is>
           <t>보석</t>
         </is>
       </c>
-      <c r="C14" s="20" t="inlineStr">
+      <c r="C14" s="1" t="inlineStr">
         <is>
           <t>재료</t>
         </is>
       </c>
-      <c r="D14" s="20" t="inlineStr">
+      <c r="D14" s="1" t="inlineStr">
         <is>
           <t>mystic</t>
         </is>
@@ -7873,18 +7279,18 @@
           <t>common</t>
         </is>
       </c>
-      <c r="F14" s="63" t="inlineStr"/>
-      <c r="G14" s="20" t="inlineStr">
+      <c r="F14" s="16" t="n"/>
+      <c r="G14" s="1" t="inlineStr">
         <is>
           <t>Map1 드랍</t>
         </is>
       </c>
-      <c r="H14" s="20" t="inlineStr">
+      <c r="H14" s="1" t="inlineStr">
         <is>
           <t>기본 재료</t>
         </is>
       </c>
-      <c r="I14" s="20" t="inlineStr">
+      <c r="I14" s="1" t="inlineStr">
         <is>
           <t>src/data/items.ts</t>
         </is>
@@ -8367,314 +7773,311 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:H62"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="17"/>
   <cols>
-    <col width="18" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
-    <col width="20" customWidth="1" min="6" max="6"/>
-    <col width="16" customWidth="1" min="7" max="7"/>
-    <col width="24" customWidth="1" min="8" max="8"/>
+    <col width="18" customWidth="1" style="24" min="1" max="1"/>
+    <col width="14" customWidth="1" style="24" min="2" max="5"/>
+    <col width="20" customWidth="1" style="24" min="6" max="6"/>
+    <col width="16" customWidth="1" style="24" min="7" max="7"/>
+    <col width="24" customWidth="1" style="24" min="8" max="8"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="52" t="inlineStr">
+    <row r="1" ht="20" customHeight="1" s="24">
+      <c r="A1" s="30" t="inlineStr">
         <is>
           <t>06_Drop - 지역별 재료 드랍 확률</t>
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" s="68" t="inlineStr">
+    <row r="2" ht="36" customHeight="1" s="24">
+      <c r="A2" s="21" t="inlineStr">
         <is>
           <t>region</t>
         </is>
       </c>
-      <c r="B2" s="68" t="inlineStr">
+      <c r="B2" s="21" t="inlineStr">
         <is>
           <t>item_id</t>
         </is>
       </c>
-      <c r="C2" s="68" t="inlineStr">
+      <c r="C2" s="21" t="inlineStr">
         <is>
           <t>weight(value)</t>
         </is>
       </c>
-      <c r="D2" s="68" t="inlineStr">
+      <c r="D2" s="21" t="inlineStr">
         <is>
           <t>min_count(value)</t>
         </is>
       </c>
-      <c r="E2" s="68" t="inlineStr">
+      <c r="E2" s="21" t="inlineStr">
         <is>
           <t>max_count(value)</t>
         </is>
       </c>
-      <c r="F2" s="68" t="inlineStr">
+      <c r="F2" s="21" t="inlineStr">
         <is>
           <t>설명</t>
         </is>
       </c>
-      <c r="G2" s="68" t="inlineStr">
+      <c r="G2" s="21" t="inlineStr">
         <is>
           <t>조절 포인트</t>
         </is>
       </c>
-      <c r="H2" s="68" t="inlineStr">
+      <c r="H2" s="21" t="inlineStr">
         <is>
           <t>코드소스</t>
         </is>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" s="20" t="inlineStr">
+    <row r="3" ht="18" customHeight="1" s="24">
+      <c r="A3" s="1" t="inlineStr">
         <is>
           <t>starlight_forest</t>
         </is>
       </c>
-      <c r="B3" s="20" t="inlineStr">
+      <c r="B3" s="1" t="inlineStr">
         <is>
           <t>flower</t>
         </is>
       </c>
-      <c r="C3" s="63" t="n">
+      <c r="C3" s="16" t="n">
         <v>30</v>
       </c>
-      <c r="D3" s="63" t="n">
-        <v>1</v>
-      </c>
-      <c r="E3" s="63" t="n">
+      <c r="D3" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="E3" s="16" t="n">
         <v>3</v>
       </c>
-      <c r="F3" s="20" t="inlineStr">
+      <c r="F3" s="1" t="inlineStr">
         <is>
           <t>꽃 드랍 가중치</t>
         </is>
       </c>
-      <c r="G3" s="20" t="inlineStr">
+      <c r="G3" s="1" t="inlineStr">
         <is>
           <t>weight / count</t>
         </is>
       </c>
-      <c r="H3" s="20" t="inlineStr">
-        <is>
-          <t>src/data/regions.ts</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="20" t="inlineStr">
+      <c r="H3" s="1" t="inlineStr">
+        <is>
+          <t>src/data/regions.ts</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="18" customHeight="1" s="24">
+      <c r="A4" s="1" t="inlineStr">
         <is>
           <t>starlight_forest</t>
         </is>
       </c>
-      <c r="B4" s="20" t="inlineStr">
+      <c r="B4" s="1" t="inlineStr">
         <is>
           <t>leaf</t>
         </is>
       </c>
-      <c r="C4" s="63" t="n">
+      <c r="C4" s="16" t="n">
         <v>27</v>
       </c>
-      <c r="D4" s="63" t="n">
-        <v>1</v>
-      </c>
-      <c r="E4" s="63" t="n">
+      <c r="D4" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="E4" s="16" t="n">
         <v>3</v>
       </c>
-      <c r="F4" s="20" t="inlineStr">
+      <c r="F4" s="1" t="inlineStr">
         <is>
           <t>잎 드랍 가중치</t>
         </is>
       </c>
-      <c r="G4" s="20" t="inlineStr">
+      <c r="G4" s="1" t="inlineStr">
         <is>
           <t>weight / count</t>
         </is>
       </c>
-      <c r="H4" s="20" t="inlineStr">
-        <is>
-          <t>src/data/regions.ts</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="20" t="inlineStr">
+      <c r="H4" s="1" t="inlineStr">
+        <is>
+          <t>src/data/regions.ts</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="18" customHeight="1" s="24">
+      <c r="A5" s="1" t="inlineStr">
         <is>
           <t>starlight_forest</t>
         </is>
       </c>
-      <c r="B5" s="20" t="inlineStr">
+      <c r="B5" s="1" t="inlineStr">
         <is>
           <t>soil</t>
         </is>
       </c>
-      <c r="C5" s="63" t="n">
+      <c r="C5" s="16" t="n">
         <v>18</v>
       </c>
-      <c r="D5" s="63" t="n">
-        <v>1</v>
-      </c>
-      <c r="E5" s="63" t="n">
+      <c r="D5" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="E5" s="16" t="n">
         <v>2</v>
       </c>
-      <c r="F5" s="20" t="inlineStr">
+      <c r="F5" s="1" t="inlineStr">
         <is>
           <t>흙 드랍 가중치</t>
         </is>
       </c>
-      <c r="G5" s="20" t="inlineStr">
+      <c r="G5" s="1" t="inlineStr">
         <is>
           <t>weight / count</t>
         </is>
       </c>
-      <c r="H5" s="20" t="inlineStr">
-        <is>
-          <t>src/data/regions.ts</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="20" t="inlineStr">
+      <c r="H5" s="1" t="inlineStr">
+        <is>
+          <t>src/data/regions.ts</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="18" customHeight="1" s="24">
+      <c r="A6" s="1" t="inlineStr">
         <is>
           <t>starlight_forest</t>
         </is>
       </c>
-      <c r="B6" s="20" t="inlineStr">
+      <c r="B6" s="1" t="inlineStr">
         <is>
           <t>water</t>
         </is>
       </c>
-      <c r="C6" s="63" t="n">
+      <c r="C6" s="16" t="n">
         <v>10</v>
       </c>
-      <c r="D6" s="63" t="n">
-        <v>1</v>
-      </c>
-      <c r="E6" s="63" t="n">
+      <c r="D6" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="E6" s="16" t="n">
         <v>2</v>
       </c>
-      <c r="F6" s="20" t="inlineStr">
+      <c r="F6" s="1" t="inlineStr">
         <is>
           <t>물 드랍 가중치</t>
         </is>
       </c>
-      <c r="G6" s="20" t="inlineStr">
+      <c r="G6" s="1" t="inlineStr">
         <is>
           <t>weight / count</t>
         </is>
       </c>
-      <c r="H6" s="20" t="inlineStr">
-        <is>
-          <t>src/data/regions.ts</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="20" t="inlineStr">
+      <c r="H6" s="1" t="inlineStr">
+        <is>
+          <t>src/data/regions.ts</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="18" customHeight="1" s="24">
+      <c r="A7" s="1" t="inlineStr">
         <is>
           <t>starlight_forest</t>
         </is>
       </c>
-      <c r="B7" s="20" t="inlineStr">
+      <c r="B7" s="1" t="inlineStr">
         <is>
           <t>star</t>
         </is>
       </c>
-      <c r="C7" s="63" t="n">
+      <c r="C7" s="16" t="n">
         <v>8</v>
       </c>
-      <c r="D7" s="63" t="n">
-        <v>1</v>
-      </c>
-      <c r="E7" s="63" t="n">
-        <v>1</v>
-      </c>
-      <c r="F7" s="20" t="inlineStr">
+      <c r="D7" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="E7" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="F7" s="1" t="inlineStr">
         <is>
           <t>별 드랍 가중치</t>
         </is>
       </c>
-      <c r="G7" s="20" t="inlineStr">
+      <c r="G7" s="1" t="inlineStr">
         <is>
           <t>weight / count</t>
         </is>
       </c>
-      <c r="H7" s="20" t="inlineStr">
-        <is>
-          <t>src/data/regions.ts</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="20" t="inlineStr">
+      <c r="H7" s="1" t="inlineStr">
+        <is>
+          <t>src/data/regions.ts</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="18" customHeight="1" s="24">
+      <c r="A8" s="1" t="inlineStr">
         <is>
           <t>starlight_forest</t>
         </is>
       </c>
-      <c r="B8" s="20" t="inlineStr">
+      <c r="B8" s="1" t="inlineStr">
         <is>
           <t>magic</t>
         </is>
       </c>
-      <c r="C8" s="63" t="n">
+      <c r="C8" s="16" t="n">
         <v>4</v>
       </c>
-      <c r="D8" s="63" t="n">
-        <v>1</v>
-      </c>
-      <c r="E8" s="63" t="n">
-        <v>1</v>
-      </c>
-      <c r="F8" s="20" t="inlineStr">
+      <c r="D8" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="E8" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="F8" s="1" t="inlineStr">
         <is>
           <t>마법 드랍 가중치</t>
         </is>
       </c>
-      <c r="G8" s="20" t="inlineStr">
+      <c r="G8" s="1" t="inlineStr">
         <is>
           <t>weight / count</t>
         </is>
       </c>
-      <c r="H8" s="20" t="inlineStr">
-        <is>
-          <t>src/data/regions.ts</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="20" t="inlineStr">
+      <c r="H8" s="1" t="inlineStr">
+        <is>
+          <t>src/data/regions.ts</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="18" customHeight="1" s="24">
+      <c r="A9" s="1" t="inlineStr">
         <is>
           <t>starlight_forest</t>
         </is>
       </c>
-      <c r="B9" s="20" t="inlineStr">
+      <c r="B9" s="1" t="inlineStr">
         <is>
           <t>gem</t>
         </is>
       </c>
-      <c r="C9" s="63" t="n">
+      <c r="C9" s="16" t="n">
         <v>3</v>
       </c>
-      <c r="D9" s="63" t="n">
-        <v>1</v>
-      </c>
-      <c r="E9" s="63" t="n">
-        <v>1</v>
-      </c>
-      <c r="F9" s="20" t="inlineStr">
+      <c r="D9" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="E9" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="F9" s="1" t="inlineStr">
         <is>
           <t>보석 드랍 가중치</t>
         </is>
       </c>
-      <c r="G9" s="20" t="inlineStr">
+      <c r="G9" s="1" t="inlineStr">
         <is>
           <t>weight / count</t>
         </is>
       </c>
-      <c r="H9" s="20" t="inlineStr">
+      <c r="H9" s="1" t="inlineStr">
         <is>
           <t>src/data/regions.ts</t>
         </is>
@@ -8860,145 +8263,145 @@
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" s="20" t="inlineStr">
+    <row r="15" ht="18" customHeight="1" s="24">
+      <c r="A15" s="1" t="inlineStr">
         <is>
           <t>wind_canyon</t>
         </is>
       </c>
-      <c r="B15" s="20" t="inlineStr">
+      <c r="B15" s="1" t="inlineStr">
         <is>
           <t>wind</t>
         </is>
       </c>
-      <c r="C15" s="63" t="n">
+      <c r="C15" s="16" t="n">
         <v>30</v>
       </c>
-      <c r="D15" s="63" t="n">
-        <v>1</v>
-      </c>
-      <c r="E15" s="63" t="n">
+      <c r="D15" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="E15" s="16" t="n">
         <v>3</v>
       </c>
-      <c r="F15" s="20" t="inlineStr">
+      <c r="F15" s="1" t="inlineStr">
         <is>
           <t>바람 드랍 가중치</t>
         </is>
       </c>
-      <c r="G15" s="20" t="inlineStr">
+      <c r="G15" s="1" t="inlineStr">
         <is>
           <t>weight / count</t>
         </is>
       </c>
-      <c r="H15" s="20" t="inlineStr">
-        <is>
-          <t>src/data/regions.ts</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="20" t="inlineStr">
+      <c r="H15" s="1" t="inlineStr">
+        <is>
+          <t>src/data/regions.ts</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="18" customHeight="1" s="24">
+      <c r="A16" s="1" t="inlineStr">
         <is>
           <t>wind_canyon</t>
         </is>
       </c>
-      <c r="B16" s="20" t="inlineStr">
+      <c r="B16" s="1" t="inlineStr">
         <is>
           <t>water</t>
         </is>
       </c>
-      <c r="C16" s="63" t="n">
+      <c r="C16" s="16" t="n">
         <v>25</v>
       </c>
-      <c r="D16" s="63" t="n">
-        <v>1</v>
-      </c>
-      <c r="E16" s="63" t="n">
+      <c r="D16" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="E16" s="16" t="n">
         <v>3</v>
       </c>
-      <c r="F16" s="20" t="inlineStr">
+      <c r="F16" s="1" t="inlineStr">
         <is>
           <t>물 드랍 가중치</t>
         </is>
       </c>
-      <c r="G16" s="20" t="inlineStr">
+      <c r="G16" s="1" t="inlineStr">
         <is>
           <t>weight / count</t>
         </is>
       </c>
-      <c r="H16" s="20" t="inlineStr">
-        <is>
-          <t>src/data/regions.ts</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="20" t="inlineStr">
+      <c r="H16" s="1" t="inlineStr">
+        <is>
+          <t>src/data/regions.ts</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="18" customHeight="1" s="24">
+      <c r="A17" s="1" t="inlineStr">
         <is>
           <t>wind_canyon</t>
         </is>
       </c>
-      <c r="B17" s="20" t="inlineStr">
+      <c r="B17" s="1" t="inlineStr">
         <is>
           <t>leaf</t>
         </is>
       </c>
-      <c r="C17" s="63" t="n">
+      <c r="C17" s="16" t="n">
         <v>18</v>
       </c>
-      <c r="D17" s="63" t="n">
-        <v>1</v>
-      </c>
-      <c r="E17" s="63" t="n">
+      <c r="D17" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="E17" s="16" t="n">
         <v>2</v>
       </c>
-      <c r="F17" s="20" t="inlineStr">
+      <c r="F17" s="1" t="inlineStr">
         <is>
           <t>잎 드랍 가중치</t>
         </is>
       </c>
-      <c r="G17" s="20" t="inlineStr">
+      <c r="G17" s="1" t="inlineStr">
         <is>
           <t>weight / count</t>
         </is>
       </c>
-      <c r="H17" s="20" t="inlineStr">
-        <is>
-          <t>src/data/regions.ts</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="20" t="inlineStr">
+      <c r="H17" s="1" t="inlineStr">
+        <is>
+          <t>src/data/regions.ts</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="18" customHeight="1" s="24">
+      <c r="A18" s="1" t="inlineStr">
         <is>
           <t>wind_canyon</t>
         </is>
       </c>
-      <c r="B18" s="20" t="inlineStr">
+      <c r="B18" s="1" t="inlineStr">
         <is>
           <t>star</t>
         </is>
       </c>
-      <c r="C18" s="63" t="n">
+      <c r="C18" s="16" t="n">
         <v>10</v>
       </c>
-      <c r="D18" s="63" t="n">
-        <v>1</v>
-      </c>
-      <c r="E18" s="63" t="n">
+      <c r="D18" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="E18" s="16" t="n">
         <v>2</v>
       </c>
-      <c r="F18" s="20" t="inlineStr">
+      <c r="F18" s="1" t="inlineStr">
         <is>
           <t>별 드랍 가중치</t>
         </is>
       </c>
-      <c r="G18" s="20" t="inlineStr">
+      <c r="G18" s="1" t="inlineStr">
         <is>
           <t>weight / count</t>
         </is>
       </c>
-      <c r="H18" s="20" t="inlineStr">
+      <c r="H18" s="1" t="inlineStr">
         <is>
           <t>src/data/regions.ts</t>
         </is>
@@ -10602,519 +10005,1186 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H8"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <dimension ref="A1:H30"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="17"/>
   <cols>
-    <col width="16" customWidth="1" min="1" max="1"/>
-    <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="16" customWidth="1" min="4" max="4"/>
-    <col width="16" customWidth="1" min="5" max="5"/>
-    <col width="16" customWidth="1" min="6" max="6"/>
-    <col width="20" customWidth="1" min="7" max="7"/>
-    <col width="24" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" style="24" min="1" max="1"/>
+    <col width="32" customWidth="1" style="24" min="2" max="2"/>
+    <col width="12" customWidth="1" style="24" min="3" max="3"/>
+    <col width="10" customWidth="1" style="24" min="4" max="4"/>
+    <col width="24" customWidth="1" style="24" min="5" max="5"/>
+    <col width="16" customWidth="1" style="24" min="6" max="7"/>
+    <col width="28" customWidth="1" style="24" min="8" max="8"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="54" t="inlineStr">
-        <is>
-          <t>07_Spirit - 정령 정보 (미확정 템플릿)</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="69" t="inlineStr">
-        <is>
-          <t>spirit_id</t>
-        </is>
-      </c>
-      <c r="B2" s="69" t="inlineStr">
-        <is>
-          <t>이름</t>
-        </is>
-      </c>
-      <c r="C2" s="69" t="inlineStr">
-        <is>
-          <t>희귀도(value)</t>
-        </is>
-      </c>
-      <c r="D2" s="69" t="inlineStr">
-        <is>
-          <t>해금조건(value)</t>
-        </is>
-      </c>
-      <c r="E2" s="69" t="inlineStr">
-        <is>
-          <t>조각필요량(value)</t>
-        </is>
-      </c>
-      <c r="F2" s="69" t="inlineStr">
-        <is>
-          <t>효과(value)</t>
-        </is>
-      </c>
-      <c r="G2" s="69" t="inlineStr">
-        <is>
-          <t>메모</t>
-        </is>
-      </c>
-      <c r="H2" s="69" t="inlineStr">
+    <row r="1" ht="20" customHeight="1" s="24">
+      <c r="A1" s="31" t="inlineStr">
+        <is>
+          <t>09_Economy - 전체 경제/제작 밸런스</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="18" customHeight="1" s="24">
+      <c r="A2" s="22" t="inlineStr">
+        <is>
+          <t>카테고리</t>
+        </is>
+      </c>
+      <c r="B2" s="22" t="inlineStr">
+        <is>
+          <t>키</t>
+        </is>
+      </c>
+      <c r="C2" s="22" t="inlineStr">
+        <is>
+          <t>value</t>
+        </is>
+      </c>
+      <c r="D2" s="22" t="inlineStr">
+        <is>
+          <t>단위</t>
+        </is>
+      </c>
+      <c r="E2" s="22" t="inlineStr">
+        <is>
+          <t>설명</t>
+        </is>
+      </c>
+      <c r="F2" s="22" t="inlineStr">
+        <is>
+          <t>올리면</t>
+        </is>
+      </c>
+      <c r="G2" s="22" t="inlineStr">
+        <is>
+          <t>내리면</t>
+        </is>
+      </c>
+      <c r="H2" s="22" t="inlineStr">
         <is>
           <t>코드소스</t>
         </is>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" s="20" t="inlineStr">
-        <is>
-          <t>spirit_soyo</t>
-        </is>
-      </c>
-      <c r="B3" s="20" t="inlineStr">
-        <is>
-          <t>소요</t>
-        </is>
-      </c>
-      <c r="C3" s="20" t="inlineStr">
-        <is>
-          <t>common</t>
-        </is>
-      </c>
-      <c r="D3" s="20" t="inlineStr">
-        <is>
-          <t>조각</t>
-        </is>
-      </c>
-      <c r="E3" s="63" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="F3" s="20" t="inlineStr">
-        <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="G3" s="20" t="inlineStr">
-        <is>
-          <t>현재 조각 시스템 예시</t>
-        </is>
-      </c>
-      <c r="H3" s="20" t="inlineStr">
-        <is>
-          <t>src/data/spirits.ts</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="20" t="inlineStr">
-        <is>
-          <t>spirit_rua</t>
-        </is>
-      </c>
-      <c r="B4" s="20" t="inlineStr">
-        <is>
-          <t>루아</t>
-        </is>
-      </c>
-      <c r="C4" s="20" t="inlineStr">
-        <is>
-          <t>rare</t>
-        </is>
-      </c>
-      <c r="D4" s="20" t="inlineStr">
-        <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="E4" s="63" t="inlineStr">
-        <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="F4" s="20" t="inlineStr">
-        <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="G4" s="20" t="inlineStr">
-        <is>
-          <t>미정</t>
-        </is>
-      </c>
-      <c r="H4" s="20" t="inlineStr">
-        <is>
-          <t>src/data/spirits.ts</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="20" t="inlineStr">
-        <is>
-          <t>spirit_pleo</t>
-        </is>
-      </c>
-      <c r="B5" s="20" t="inlineStr">
-        <is>
-          <t>플레오</t>
-        </is>
-      </c>
-      <c r="C5" s="20" t="inlineStr">
-        <is>
-          <t>rare</t>
-        </is>
-      </c>
-      <c r="D5" s="20" t="inlineStr">
-        <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="E5" s="63" t="inlineStr">
-        <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="F5" s="20" t="inlineStr">
-        <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="G5" s="20" t="inlineStr">
-        <is>
-          <t>미정</t>
-        </is>
-      </c>
-      <c r="H5" s="20" t="inlineStr">
-        <is>
-          <t>src/data/spirits.ts</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="20" t="inlineStr">
-        <is>
-          <t>spirit_stellio</t>
-        </is>
-      </c>
-      <c r="B6" s="20" t="inlineStr">
-        <is>
-          <t>스텔리오</t>
-        </is>
-      </c>
-      <c r="C6" s="20" t="inlineStr">
-        <is>
-          <t>epic</t>
-        </is>
-      </c>
-      <c r="D6" s="20" t="inlineStr">
-        <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="E6" s="63" t="inlineStr">
-        <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="F6" s="20" t="inlineStr">
-        <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="G6" s="20" t="inlineStr">
-        <is>
-          <t>미정</t>
-        </is>
-      </c>
-      <c r="H6" s="20" t="inlineStr">
-        <is>
-          <t>src/data/spirits.ts</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="20" t="inlineStr">
-        <is>
-          <t>spirit_porina</t>
-        </is>
-      </c>
-      <c r="B7" s="20" t="inlineStr">
-        <is>
-          <t>포리나</t>
-        </is>
-      </c>
-      <c r="C7" s="20" t="inlineStr">
-        <is>
-          <t>epic</t>
-        </is>
-      </c>
-      <c r="D7" s="20" t="inlineStr">
-        <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="E7" s="63" t="inlineStr">
-        <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="F7" s="20" t="inlineStr">
-        <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="G7" s="20" t="inlineStr">
-        <is>
-          <t>미정</t>
-        </is>
-      </c>
-      <c r="H7" s="20" t="inlineStr">
-        <is>
-          <t>src/data/spirits.ts</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="20" t="inlineStr">
-        <is>
-          <t>spirit_nubi</t>
-        </is>
-      </c>
-      <c r="B8" s="20" t="inlineStr">
-        <is>
-          <t>누비</t>
-        </is>
-      </c>
-      <c r="C8" s="20" t="inlineStr">
-        <is>
-          <t>legendary</t>
-        </is>
-      </c>
-      <c r="D8" s="20" t="inlineStr">
-        <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="E8" s="63" t="inlineStr">
-        <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="F8" s="20" t="inlineStr">
-        <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="G8" s="20" t="inlineStr">
-        <is>
-          <t>미정</t>
-        </is>
-      </c>
-      <c r="H8" s="20" t="inlineStr">
-        <is>
-          <t>src/data/spirits.ts</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:H1"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:H5"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="18" customWidth="1" min="1" max="1"/>
-    <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
-    <col width="14" customWidth="1" min="6" max="6"/>
-    <col width="14" customWidth="1" min="7" max="7"/>
-    <col width="24" customWidth="1" min="8" max="8"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="56" t="inlineStr">
-        <is>
-          <t>08_Recipe - 재료 조합별 정령 (미확정 템플릿)</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="70" t="inlineStr">
-        <is>
-          <t>recipe_id</t>
-        </is>
-      </c>
-      <c r="B2" s="70" t="inlineStr">
-        <is>
-          <t>재료1</t>
-        </is>
-      </c>
-      <c r="C2" s="70" t="inlineStr">
-        <is>
-          <t>재료2</t>
-        </is>
-      </c>
-      <c r="D2" s="70" t="inlineStr">
-        <is>
-          <t>재료3</t>
-        </is>
-      </c>
-      <c r="E2" s="70" t="inlineStr">
-        <is>
-          <t>결과정령(value)</t>
-        </is>
-      </c>
-      <c r="F2" s="70" t="inlineStr">
-        <is>
-          <t>성공률(value)</t>
-        </is>
-      </c>
-      <c r="G2" s="70" t="inlineStr">
-        <is>
-          <t>실패결과(value)</t>
-        </is>
-      </c>
-      <c r="H2" s="70" t="inlineStr">
-        <is>
-          <t>코드소스</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="20" t="inlineStr">
-        <is>
-          <t>recipe_tbd_001</t>
-        </is>
-      </c>
-      <c r="B3" s="20" t="inlineStr">
-        <is>
-          <t>flower</t>
-        </is>
-      </c>
-      <c r="C3" s="20" t="inlineStr">
-        <is>
-          <t>leaf</t>
-        </is>
-      </c>
-      <c r="D3" s="20" t="inlineStr">
-        <is>
-          <t>water</t>
-        </is>
-      </c>
-      <c r="E3" s="20" t="inlineStr">
-        <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="F3" s="63" t="inlineStr">
-        <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="G3" s="20" t="inlineStr">
-        <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="H3" s="20" t="inlineStr">
-        <is>
-          <t>src/data/recipes.ts</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="20" t="inlineStr">
-        <is>
-          <t>recipe_tbd_002</t>
-        </is>
-      </c>
-      <c r="B4" s="20" t="inlineStr">
-        <is>
-          <t>soil</t>
-        </is>
-      </c>
-      <c r="C4" s="20" t="inlineStr">
-        <is>
-          <t>fire</t>
-        </is>
-      </c>
-      <c r="D4" s="20" t="inlineStr">
-        <is>
-          <t>wind</t>
-        </is>
-      </c>
-      <c r="E4" s="20" t="inlineStr">
-        <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="F4" s="63" t="inlineStr">
-        <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="G4" s="20" t="inlineStr">
-        <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="H4" s="20" t="inlineStr">
-        <is>
-          <t>src/data/recipes.ts</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="20" t="inlineStr">
-        <is>
-          <t>recipe_tbd_003</t>
-        </is>
-      </c>
-      <c r="B5" s="20" t="inlineStr">
-        <is>
-          <t>star</t>
-        </is>
-      </c>
-      <c r="C5" s="20" t="inlineStr">
-        <is>
-          <t>magic</t>
-        </is>
-      </c>
-      <c r="D5" s="20" t="inlineStr">
-        <is>
-          <t>gem</t>
-        </is>
-      </c>
-      <c r="E5" s="20" t="inlineStr">
-        <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="F5" s="63" t="inlineStr">
-        <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="G5" s="20" t="inlineStr">
-        <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="H5" s="20" t="inlineStr">
-        <is>
-          <t>src/data/recipes.ts</t>
+    <row r="3" ht="18" customHeight="1" s="24">
+      <c r="A3" s="1" t="inlineStr">
+        <is>
+          <t>경제</t>
+        </is>
+      </c>
+      <c r="B3" s="1" t="inlineStr">
+        <is>
+          <t>total_exp_required</t>
+        </is>
+      </c>
+      <c r="C3" s="16" t="n">
+        <v>43450</v>
+      </c>
+      <c r="D3" s="1" t="inlineStr">
+        <is>
+          <t>exp</t>
+        </is>
+      </c>
+      <c r="E3" s="1" t="inlineStr">
+        <is>
+          <t>만렙까지 총 EXP</t>
+        </is>
+      </c>
+      <c r="F3" s="1" t="inlineStr">
+        <is>
+          <t>성장기간 증가</t>
+        </is>
+      </c>
+      <c r="G3" s="1" t="inlineStr">
+        <is>
+          <t>성장기간 감소</t>
+        </is>
+      </c>
+      <c r="H3" s="1" t="inlineStr">
+        <is>
+          <t>src/data/economy.ts</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="18" customHeight="1" s="24">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>경제</t>
+        </is>
+      </c>
+      <c r="B4" s="1" t="inlineStr">
+        <is>
+          <t>main_color</t>
+        </is>
+      </c>
+      <c r="C4" s="16" t="inlineStr">
+        <is>
+          <t>#A894FF</t>
+        </is>
+      </c>
+      <c r="D4" s="1" t="inlineStr">
+        <is>
+          <t>hex</t>
+        </is>
+      </c>
+      <c r="E4" s="1" t="inlineStr">
+        <is>
+          <t>경제 메인 컬러</t>
+        </is>
+      </c>
+      <c r="F4" s="1" t="inlineStr">
+        <is>
+          <t>UI 강조 변경</t>
+        </is>
+      </c>
+      <c r="G4" s="1" t="inlineStr">
+        <is>
+          <t>UI 강조 완화</t>
+        </is>
+      </c>
+      <c r="H4" s="1" t="inlineStr">
+        <is>
+          <t>src/data/economy.ts</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="18" customHeight="1" s="24">
+      <c r="A5" s="1" t="inlineStr">
+        <is>
+          <t>제작티어</t>
+        </is>
+      </c>
+      <c r="B5" s="1" t="inlineStr">
+        <is>
+          <t>tier1_required_per_material</t>
+        </is>
+      </c>
+      <c r="C5" s="16" t="n">
+        <v>2</v>
+      </c>
+      <c r="D5" s="1" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="E5" s="1" t="inlineStr">
+        <is>
+          <t>Lv1~19 재료당 요구량</t>
+        </is>
+      </c>
+      <c r="F5" s="1" t="inlineStr">
+        <is>
+          <t>초반 난이도↑</t>
+        </is>
+      </c>
+      <c r="G5" s="1" t="inlineStr">
+        <is>
+          <t>초반 난이도↓</t>
+        </is>
+      </c>
+      <c r="H5" s="1" t="inlineStr">
+        <is>
+          <t>src/data/economy.ts</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="18" customHeight="1" s="24">
+      <c r="A6" s="1" t="inlineStr">
+        <is>
+          <t>제작티어</t>
+        </is>
+      </c>
+      <c r="B6" s="1" t="inlineStr">
+        <is>
+          <t>tier2_required_per_material</t>
+        </is>
+      </c>
+      <c r="C6" s="16" t="n">
+        <v>3</v>
+      </c>
+      <c r="D6" s="1" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="E6" s="1" t="inlineStr">
+        <is>
+          <t>Lv20~49 재료당 요구량</t>
+        </is>
+      </c>
+      <c r="F6" s="1" t="inlineStr">
+        <is>
+          <t>중반 난이도↑</t>
+        </is>
+      </c>
+      <c r="G6" s="1" t="inlineStr">
+        <is>
+          <t>중반 난이도↓</t>
+        </is>
+      </c>
+      <c r="H6" s="1" t="inlineStr">
+        <is>
+          <t>src/data/economy.ts</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="18" customHeight="1" s="24">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>제작티어</t>
+        </is>
+      </c>
+      <c r="B7" s="1" t="inlineStr">
+        <is>
+          <t>tier3_required_per_material</t>
+        </is>
+      </c>
+      <c r="C7" s="16" t="n">
+        <v>4</v>
+      </c>
+      <c r="D7" s="1" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="E7" s="1" t="inlineStr">
+        <is>
+          <t>Lv50~79 재료당 요구량</t>
+        </is>
+      </c>
+      <c r="F7" s="1" t="inlineStr">
+        <is>
+          <t>후반 난이도↑</t>
+        </is>
+      </c>
+      <c r="G7" s="1" t="inlineStr">
+        <is>
+          <t>후반 난이도↓</t>
+        </is>
+      </c>
+      <c r="H7" s="1" t="inlineStr">
+        <is>
+          <t>src/data/economy.ts</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="18" customHeight="1" s="24">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>제작티어</t>
+        </is>
+      </c>
+      <c r="B8" s="1" t="inlineStr">
+        <is>
+          <t>tier4_required_per_material</t>
+        </is>
+      </c>
+      <c r="C8" s="16" t="n">
+        <v>5</v>
+      </c>
+      <c r="D8" s="1" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="E8" s="1" t="inlineStr">
+        <is>
+          <t>Lv80~99 재료당 요구량</t>
+        </is>
+      </c>
+      <c r="F8" s="1" t="inlineStr">
+        <is>
+          <t>후반 난이도↑</t>
+        </is>
+      </c>
+      <c r="G8" s="1" t="inlineStr">
+        <is>
+          <t>후반 난이도↓</t>
+        </is>
+      </c>
+      <c r="H8" s="1" t="inlineStr">
+        <is>
+          <t>src/data/economy.ts</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="18" customHeight="1" s="24">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>제작공통</t>
+        </is>
+      </c>
+      <c r="B9" s="1" t="inlineStr">
+        <is>
+          <t>selected_material_kinds</t>
+        </is>
+      </c>
+      <c r="C9" s="16" t="n">
+        <v>3</v>
+      </c>
+      <c r="D9" s="1" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="E9" s="1" t="inlineStr">
+        <is>
+          <t>제작에 필요한 재료 종류 수</t>
+        </is>
+      </c>
+      <c r="F9" s="1" t="inlineStr">
+        <is>
+          <t>난이도↑</t>
+        </is>
+      </c>
+      <c r="G9" s="1" t="inlineStr">
+        <is>
+          <t>난이도↓</t>
+        </is>
+      </c>
+      <c r="H9" s="1" t="inlineStr">
+        <is>
+          <t>src/data/economy.ts</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="18" customHeight="1" s="24">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>패널티</t>
+        </is>
+      </c>
+      <c r="B10" s="1" t="inlineStr">
+        <is>
+          <t>quest_reject_penalty_gold</t>
+        </is>
+      </c>
+      <c r="C10" s="16" t="n">
+        <v>200</v>
+      </c>
+      <c r="D10" s="1" t="inlineStr">
+        <is>
+          <t>gold</t>
+        </is>
+      </c>
+      <c r="E10" s="1" t="inlineStr">
+        <is>
+          <t>의뢰 거절 패널티</t>
+        </is>
+      </c>
+      <c r="F10" s="1" t="inlineStr">
+        <is>
+          <t>거절 부담↑</t>
+        </is>
+      </c>
+      <c r="G10" s="1" t="inlineStr">
+        <is>
+          <t>거절 부담↓</t>
+        </is>
+      </c>
+      <c r="H10" s="1" t="inlineStr">
+        <is>
+          <t>src/components/CraftScreen.tsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>제작보상</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>craft_success_exp_min</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>20</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>exp</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>제작 성공 시 최소 경험치</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>성장 가속</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>성장 둔화</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>src/data/economy.ts</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>제작보상</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>craft_success_exp_max</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>30</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>exp</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>제작 성공 시 최대 경험치</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>성장 가속</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>성장 둔화</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>src/data/economy.ts</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>제작보상</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>craft_success_gold_min</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>20</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>gold</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>제작 성공 시 최소 골드</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>골드 수급 증가</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>골드 수급 감소</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>src/data/economy.ts</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>제작보상</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>craft_success_gold_max</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>40</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>gold</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>제작 성공 시 최대 골드</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>골드 수급 증가</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>골드 수급 감소</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>src/data/economy.ts</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>제작보상</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>craft_success_first_discovery_gem</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>1</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>item</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>첫 발견 성공 시 지급 보석 수</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>첫 발견 보상 강화</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>첫 발견 보상 약화</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>src/data/economy.ts</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>제작보상</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>craft_failure_fragment_amount</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>5</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>item</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>제작 실패 시 랜덤 정령 조각 수량</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>실패 보상 강화</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>실패 보상 약화</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>src/data/economy.ts</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>제작보상</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>craft_failure_exp</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>10</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>exp</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>제작 실패 시 경험치</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>실패 보상 강화</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>실패 보상 약화</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>src/data/economy.ts</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>제작보상</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>craft_failure_gold_min</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>5</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>gold</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>제작 실패 시 최소 골드</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>실패 보상 강화</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>실패 보상 약화</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>src/data/economy.ts</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>제작보상</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>craft_failure_gold_max</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>10</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>gold</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>제작 실패 시 최대 골드</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>실패 보상 강화</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>실패 보상 약화</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>src/data/economy.ts</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>제작힌트</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>craft_hint_gold_lv1</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>50</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>gold</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>힌트 1회 비용</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>힌트 사용 부담 증가</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>힌트 사용 부담 감소</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>src/data/economy.ts</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>제작힌트</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>craft_hint_gold_lv2</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>100</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>gold</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>힌트 2회 비용</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>힌트 사용 부담 증가</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>힌트 사용 부담 감소</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>src/data/economy.ts</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>제작힌트</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>craft_hint_gold_lv3</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>200</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>gold</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>힌트 3회 비용</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>힌트 사용 부담 증가</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>힌트 사용 부담 감소</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>src/data/economy.ts</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>레벨업보상</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>levelup_gold_lv1_19</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>100</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>gold</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Lv1~19 레벨업 1회당 골드</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>초반 골드 수급 증가</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>초반 골드 수급 감소</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>src/data/economy.ts</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>레벨업보상</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>levelup_gold_lv20_49</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>100</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>gold</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Lv20~49 레벨업 1회당 골드</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>중반 골드 수급 증가</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>중반 골드 수급 감소</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>src/data/economy.ts</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>레벨업보상</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>levelup_gold_lv50_79</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>100</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>gold</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Lv50~79 레벨업 1회당 골드</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>후반 골드 수급 증가</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>후반 골드 수급 감소</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>src/data/economy.ts</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>레벨업보상</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>levelup_gold_lv80_99</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>100</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>gold</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Lv80~99 레벨업 1회당 골드</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>최종 구간 골드 수급 증가</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>최종 구간 골드 수급 감소</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>src/data/economy.ts</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>레벨업보상</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>levelup_mana_lv1_19</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
+        <v>2</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>mana</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Lv1~19 레벨업 1회당 마나</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>초반 마나 수급 증가</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>초반 마나 수급 감소</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>src/data/economy.ts</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>레벨업보상</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>levelup_mana_lv20_49</t>
+        </is>
+      </c>
+      <c r="C28" t="n">
+        <v>2</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>mana</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Lv20~49 레벨업 1회당 마나</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>중반 마나 수급 증가</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>중반 마나 수급 감소</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>src/data/economy.ts</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>레벨업보상</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>levelup_mana_lv50_79</t>
+        </is>
+      </c>
+      <c r="C29" t="n">
+        <v>2</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>mana</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Lv50~79 레벨업 1회당 마나</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>후반 마나 수급 증가</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>후반 마나 수급 감소</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>src/data/economy.ts</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>레벨업보상</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>levelup_mana_lv80_99</t>
+        </is>
+      </c>
+      <c r="C30" t="n">
+        <v>2</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>mana</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Lv80~99 레벨업 1회당 마나</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>최종 구간 마나 수급 증가</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>최종 구간 마나 수급 감소</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>src/data/economy.ts</t>
         </is>
       </c>
     </row>
